--- a/data/vessels/2026-10-21.xlsx
+++ b/data/vessels/2026-10-21.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="443973" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72F2D45A-55D9-4255-9E2F-562C74400037}"/>
+  <xr:revisionPtr revIDLastSave="444546" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2E404F8-584C-44E6-B465-96961921F3B0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="215">
   <si>
     <t>Harbor</t>
   </si>
@@ -122,6 +122,24 @@
     <t>At berth</t>
   </si>
   <si>
+    <t>Seattle</t>
+  </si>
+  <si>
+    <t>T5</t>
+  </si>
+  <si>
+    <t>Chinook</t>
+  </si>
+  <si>
+    <t>MSC DENISSE X</t>
+  </si>
+  <si>
+    <t>UK641R</t>
+  </si>
+  <si>
+    <t>MSC</t>
+  </si>
+  <si>
     <t>WUT</t>
   </si>
   <si>
@@ -140,39 +158,21 @@
     <t>Inchcape</t>
   </si>
   <si>
+    <t>WC4/TP5</t>
+  </si>
+  <si>
+    <t>VIENNA EXPRESS</t>
+  </si>
+  <si>
+    <t>638E/641W</t>
+  </si>
+  <si>
+    <t>Hapag-Lloyd</t>
+  </si>
+  <si>
     <t>In transit</t>
   </si>
   <si>
-    <t>Seattle</t>
-  </si>
-  <si>
-    <t>T5</t>
-  </si>
-  <si>
-    <t>Chinook</t>
-  </si>
-  <si>
-    <t>MSC DENISSE X</t>
-  </si>
-  <si>
-    <t>UK641R</t>
-  </si>
-  <si>
-    <t>MSC</t>
-  </si>
-  <si>
-    <t>WC4/TP5</t>
-  </si>
-  <si>
-    <t>VIENNA EXPRESS</t>
-  </si>
-  <si>
-    <t>638E/641W</t>
-  </si>
-  <si>
-    <t>Hapag-Lloyd</t>
-  </si>
-  <si>
     <t>WST</t>
   </si>
   <si>
@@ -368,7 +368,7 @@
     <t>YM PLUM</t>
   </si>
   <si>
-    <t>PN12640E</t>
+    <t>198E</t>
   </si>
   <si>
     <t>EVER SALUTE</t>
@@ -512,7 +512,7 @@
     <t>ONE MAJESTY</t>
   </si>
   <si>
-    <t>PN12641E</t>
+    <t>JMJT0026E</t>
   </si>
   <si>
     <t>SM TIANJIN</t>
@@ -536,7 +536,7 @@
     <t>ONE FANTASTIC</t>
   </si>
   <si>
-    <t>FP22633C</t>
+    <t>FP22633B</t>
   </si>
   <si>
     <t>MSC YUKTA X</t>
@@ -551,6 +551,9 @@
     <t>641E</t>
   </si>
   <si>
+    <t>GLOVIS TREASURE</t>
+  </si>
+  <si>
     <t>TONGALA</t>
   </si>
   <si>
@@ -560,9 +563,6 @@
     <t>Jones Stevedoring Co</t>
   </si>
   <si>
-    <t>GLOVIS TREASURE</t>
-  </si>
-  <si>
     <t>MSC SABRINA</t>
   </si>
   <si>
@@ -572,7 +572,7 @@
     <t>CORNEILLE</t>
   </si>
   <si>
-    <t>PN12642W</t>
+    <t>JCLL0014E</t>
   </si>
   <si>
     <t>WESTWOOD COLUMBIA</t>
@@ -599,15 +599,12 @@
     <t>OOCL SEATTLE</t>
   </si>
   <si>
-    <t>DAH0C0E19</t>
+    <t>46E</t>
   </si>
   <si>
     <t>COSCO SANTOS</t>
   </si>
   <si>
-    <t>102N</t>
-  </si>
-  <si>
     <t>EVER MOST</t>
   </si>
   <si>
@@ -626,9 +623,6 @@
     <t>LOTUS A</t>
   </si>
   <si>
-    <t>CPN080S19</t>
-  </si>
-  <si>
     <t>SWIFT ACE</t>
   </si>
   <si>
@@ -641,7 +635,7 @@
     <t>ONE MODERN</t>
   </si>
   <si>
-    <t>PN32641E</t>
+    <t>JMOD0083E</t>
   </si>
   <si>
     <t>GLOVIS LEGEND</t>
@@ -653,16 +647,10 @@
     <t>497-134E</t>
   </si>
   <si>
-    <t>EVER SUMMIT</t>
-  </si>
-  <si>
-    <t>NWX0E0S19</t>
-  </si>
-  <si>
     <t>MSC LISBON IX</t>
   </si>
   <si>
-    <t>UK642A</t>
+    <t>UK641A</t>
   </si>
   <si>
     <t>SUPREME ACE</t>
@@ -683,7 +671,7 @@
     <t>YM MANDATE</t>
   </si>
   <si>
-    <t>PN12643W</t>
+    <t>606E</t>
   </si>
   <si>
     <t>XIN ZHAN JIANG</t>
@@ -695,7 +683,7 @@
     <t>OOCL OAKLAND</t>
   </si>
   <si>
-    <t>DAH0E0E19</t>
+    <t>145E</t>
   </si>
 </sst>
 </file>
@@ -768,10 +756,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L108" totalsRowShown="0">
-  <autoFilter ref="A1:L108" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L108">
-    <sortCondition ref="J2:J108"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L107" totalsRowShown="0">
+  <autoFilter ref="A1:L107" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L107">
+    <sortCondition ref="J2:J107"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1108,7 +1096,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L108"/>
+  <dimension ref="A1:L107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1232,25 +1220,25 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="I4" t="s">
         <v>18</v>
@@ -1259,33 +1247,33 @@
         <v>46315.666666666664</v>
       </c>
       <c r="K4" s="2">
-        <v>46317.75</v>
+        <v>46317.166666666664</v>
       </c>
       <c r="L4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
         <v>34</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
         <v>35</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="G5" t="s">
         <v>38</v>
-      </c>
-      <c r="F5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" t="s">
-        <v>17</v>
       </c>
       <c r="I5" t="s">
         <v>18</v>
@@ -1294,10 +1282,10 @@
         <v>46315.666666666664</v>
       </c>
       <c r="K5" s="2">
-        <v>46317.166666666664</v>
+        <v>46317.75</v>
       </c>
       <c r="L5" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1308,16 +1296,16 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" t="s">
         <v>40</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" t="s">
         <v>42</v>
-      </c>
-      <c r="F6" t="s">
-        <v>43</v>
       </c>
       <c r="G6" t="s">
         <v>17</v>
@@ -1332,7 +1320,7 @@
         <v>46322.166666666664</v>
       </c>
       <c r="L6" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1343,16 +1331,16 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
         <v>40</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" t="s">
         <v>42</v>
-      </c>
-      <c r="F7" t="s">
-        <v>43</v>
       </c>
       <c r="G7" t="s">
         <v>17</v>
@@ -1367,7 +1355,7 @@
         <v>46322.166666666664</v>
       </c>
       <c r="L7" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1405,7 +1393,7 @@
         <v>46316.916666666664</v>
       </c>
       <c r="L8" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1428,7 +1416,7 @@
         <v>16</v>
       </c>
       <c r="G9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I9" t="s">
         <v>52</v>
@@ -1513,7 +1501,7 @@
         <v>46317.041666666664</v>
       </c>
       <c r="L11" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1545,7 +1533,7 @@
         <v>46318.708333333336</v>
       </c>
       <c r="L12" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1655,7 +1643,7 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
         <v>68</v>
@@ -1673,7 +1661,7 @@
         <v>72</v>
       </c>
       <c r="G16" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H16" t="s">
         <v>49</v>
@@ -1688,7 +1676,7 @@
         <v>46319.166666666664</v>
       </c>
       <c r="L16" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1764,7 +1752,7 @@
         <v>46319.125</v>
       </c>
       <c r="L18" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1837,7 +1825,7 @@
         <v>46319.041666666664</v>
       </c>
       <c r="L20" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1869,7 +1857,7 @@
         <v>46319.204861111109</v>
       </c>
       <c r="L21" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1912,7 +1900,7 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
         <v>68</v>
@@ -1945,7 +1933,7 @@
         <v>46320.083333333336</v>
       </c>
       <c r="L23" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1965,7 +1953,7 @@
         <v>21</v>
       </c>
       <c r="F24" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G24" t="s">
         <v>17</v>
@@ -1980,7 +1968,7 @@
         <v>46325.75</v>
       </c>
       <c r="L24" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -2023,7 +2011,7 @@
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C26" t="s">
         <v>95</v>
@@ -2035,10 +2023,10 @@
         <v>97</v>
       </c>
       <c r="F26" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G26" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I26" t="s">
         <v>18</v>
@@ -2050,7 +2038,7 @@
         <v>46321.75</v>
       </c>
       <c r="L26" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -2090,7 +2078,7 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
         <v>68</v>
@@ -2120,12 +2108,12 @@
         <v>46322.75</v>
       </c>
       <c r="L28" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
         <v>68</v>
@@ -2155,7 +2143,7 @@
         <v>46322.166666666664</v>
       </c>
       <c r="L29" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2163,10 +2151,10 @@
         <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C30" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D30" t="s">
         <v>108</v>
@@ -2175,10 +2163,10 @@
         <v>109</v>
       </c>
       <c r="F30" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G30" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I30" t="s">
         <v>18</v>
@@ -2190,7 +2178,7 @@
         <v>46323.166666666664</v>
       </c>
       <c r="L30" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -2228,7 +2216,7 @@
         <v>46324.791666666664</v>
       </c>
       <c r="L31" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -2248,7 +2236,7 @@
         <v>116</v>
       </c>
       <c r="G32" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H32" t="s">
         <v>117</v>
@@ -2286,7 +2274,7 @@
         <v>116</v>
       </c>
       <c r="G33" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H33" t="s">
         <v>117</v>
@@ -2312,7 +2300,7 @@
         <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D34" t="s">
         <v>120</v>
@@ -2321,7 +2309,7 @@
         <v>121</v>
       </c>
       <c r="F34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G34" t="s">
         <v>17</v>
@@ -2336,7 +2324,7 @@
         <v>46325.75</v>
       </c>
       <c r="L34" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2371,7 +2359,7 @@
         <v>46323.916666666664</v>
       </c>
       <c r="L35" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -2411,7 +2399,7 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B37" t="s">
         <v>68</v>
@@ -2441,7 +2429,7 @@
         <v>46323.75</v>
       </c>
       <c r="L37" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -2479,18 +2467,18 @@
         <v>46324.041666666664</v>
       </c>
       <c r="L38" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B39" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C39" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D39" t="s">
         <v>128</v>
@@ -2499,7 +2487,7 @@
         <v>129</v>
       </c>
       <c r="F39" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G39" t="s">
         <v>17</v>
@@ -2517,7 +2505,7 @@
         <v>46325.166666666664</v>
       </c>
       <c r="L39" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2557,7 +2545,7 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B41" t="s">
         <v>68</v>
@@ -2590,7 +2578,7 @@
         <v>46325.166666666664</v>
       </c>
       <c r="L41" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2598,7 +2586,7 @@
         <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C42" t="s">
         <v>95</v>
@@ -2625,7 +2613,7 @@
         <v>46326.166666666664</v>
       </c>
       <c r="L42" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -2654,7 +2642,7 @@
         <v>46325.833333333336</v>
       </c>
       <c r="L43" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2692,7 +2680,7 @@
         <v>46326.041666666664</v>
       </c>
       <c r="L44" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2724,7 +2712,7 @@
         <v>46327.208333333336</v>
       </c>
       <c r="L45" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2756,12 +2744,12 @@
         <v>46327.208333333336</v>
       </c>
       <c r="L46" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B47" t="s">
         <v>68</v>
@@ -2791,7 +2779,7 @@
         <v>46327.416666666664</v>
       </c>
       <c r="L47" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2855,12 +2843,12 @@
         <v>46326.75</v>
       </c>
       <c r="L49" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B50" t="s">
         <v>68</v>
@@ -2890,7 +2878,7 @@
         <v>46328.75</v>
       </c>
       <c r="L50" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -2898,7 +2886,7 @@
         <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C51" t="s">
         <v>95</v>
@@ -2922,7 +2910,7 @@
         <v>46329.583333333336</v>
       </c>
       <c r="L51" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -2962,13 +2950,13 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B53" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C53" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D53" t="s">
         <v>150</v>
@@ -2977,7 +2965,7 @@
         <v>151</v>
       </c>
       <c r="F53" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G53" t="s">
         <v>17</v>
@@ -2992,7 +2980,7 @@
         <v>46329.166666666664</v>
       </c>
       <c r="L53" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -3027,15 +3015,15 @@
         <v>46331.75</v>
       </c>
       <c r="L54" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B55" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C55" t="s">
         <v>153</v>
@@ -3047,7 +3035,7 @@
         <v>155</v>
       </c>
       <c r="F55" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G55" t="s">
         <v>17</v>
@@ -3062,7 +3050,7 @@
         <v>46328.75</v>
       </c>
       <c r="L55" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -3070,10 +3058,10 @@
         <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C56" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D56" t="s">
         <v>156</v>
@@ -3094,12 +3082,12 @@
         <v>46331.196527777778</v>
       </c>
       <c r="L56" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B57" t="s">
         <v>68</v>
@@ -3129,7 +3117,7 @@
         <v>46328.75</v>
       </c>
       <c r="L57" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -3167,7 +3155,7 @@
         <v>46331.791666666664</v>
       </c>
       <c r="L58" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -3178,7 +3166,7 @@
         <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D59" t="s">
         <v>162</v>
@@ -3199,7 +3187,7 @@
         <v>46332.625</v>
       </c>
       <c r="L59" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3231,7 +3219,7 @@
         <v>46334</v>
       </c>
       <c r="L60" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3263,18 +3251,18 @@
         <v>46334</v>
       </c>
       <c r="L61" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B62" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C62" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D62" t="s">
         <v>166</v>
@@ -3283,7 +3271,7 @@
         <v>167</v>
       </c>
       <c r="F62" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G62" t="s">
         <v>17</v>
@@ -3298,7 +3286,7 @@
         <v>46332.166666666664</v>
       </c>
       <c r="L62" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -3327,7 +3315,7 @@
         <v>46331.125</v>
       </c>
       <c r="L63" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3338,7 +3326,7 @@
         <v>13</v>
       </c>
       <c r="C64" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D64" t="s">
         <v>168</v>
@@ -3359,7 +3347,7 @@
         <v>46333.925000000003</v>
       </c>
       <c r="L64" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -3370,7 +3358,7 @@
         <v>13</v>
       </c>
       <c r="C65" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D65" t="s">
         <v>168</v>
@@ -3391,7 +3379,7 @@
         <v>46333.925000000003</v>
       </c>
       <c r="L65" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -3420,7 +3408,7 @@
         <v>46331.204861111109</v>
       </c>
       <c r="L66" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -3436,18 +3424,15 @@
       <c r="D67" t="s">
         <v>170</v>
       </c>
-      <c r="E67" s="1" t="s">
-        <v>171</v>
+      <c r="E67" s="1">
+        <v>10</v>
       </c>
       <c r="F67" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="G67" t="s">
         <v>17</v>
       </c>
-      <c r="H67" t="s">
-        <v>172</v>
-      </c>
       <c r="I67" t="s">
         <v>52</v>
       </c>
@@ -3455,7 +3440,7 @@
         <v>46331.25</v>
       </c>
       <c r="K67" s="2">
-        <v>46331.75</v>
+        <v>46331.666666666664</v>
       </c>
       <c r="L67" t="s">
         <v>19</v>
@@ -3472,17 +3457,20 @@
         <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>173</v>
-      </c>
-      <c r="E68" s="1">
-        <v>10</v>
+        <v>171</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>172</v>
       </c>
       <c r="F68" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="G68" t="s">
         <v>17</v>
       </c>
+      <c r="H68" t="s">
+        <v>173</v>
+      </c>
       <c r="I68" t="s">
         <v>52</v>
       </c>
@@ -3490,7 +3478,7 @@
         <v>46331.25</v>
       </c>
       <c r="K68" s="2">
-        <v>46331.666666666664</v>
+        <v>46331.75</v>
       </c>
       <c r="L68" t="s">
         <v>19</v>
@@ -3498,10 +3486,10 @@
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B69" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C69" t="s">
         <v>153</v>
@@ -3513,7 +3501,7 @@
         <v>175</v>
       </c>
       <c r="F69" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G69" t="s">
         <v>17</v>
@@ -3528,7 +3516,7 @@
         <v>46332.166666666664</v>
       </c>
       <c r="L69" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3536,10 +3524,10 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C70" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D70" t="s">
         <v>176</v>
@@ -3560,7 +3548,7 @@
         <v>46334.746527777781</v>
       </c>
       <c r="L70" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -3568,10 +3556,10 @@
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C71" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D71" t="s">
         <v>176</v>
@@ -3592,7 +3580,7 @@
         <v>46334.746527777781</v>
       </c>
       <c r="L71" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -3606,7 +3594,7 @@
         <v>14</v>
       </c>
       <c r="D72" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E72" s="1">
         <v>10</v>
@@ -3641,10 +3629,10 @@
         <v>14</v>
       </c>
       <c r="D73" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F73" t="s">
         <v>75</v>
@@ -3653,7 +3641,7 @@
         <v>17</v>
       </c>
       <c r="H73" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I73" t="s">
         <v>52</v>
@@ -3670,7 +3658,7 @@
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B74" t="s">
         <v>68</v>
@@ -3697,7 +3685,7 @@
         <v>46332.597916666666</v>
       </c>
       <c r="L74" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -3737,10 +3725,10 @@
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B76" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C76" t="s">
         <v>153</v>
@@ -3752,7 +3740,7 @@
         <v>183</v>
       </c>
       <c r="F76" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G76" t="s">
         <v>17</v>
@@ -3767,7 +3755,7 @@
         <v>46333.166666666664</v>
       </c>
       <c r="L76" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -3796,12 +3784,12 @@
         <v>46332.791666666664</v>
       </c>
       <c r="L77" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B78" t="s">
         <v>68</v>
@@ -3822,12 +3810,12 @@
         <v>46333.5</v>
       </c>
       <c r="L78" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B79" t="s">
         <v>68</v>
@@ -3848,7 +3836,7 @@
         <v>46333.5</v>
       </c>
       <c r="L79" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -3877,7 +3865,7 @@
         <v>46333.041666666664</v>
       </c>
       <c r="L80" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -3917,7 +3905,7 @@
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B82" t="s">
         <v>68</v>
@@ -3944,12 +3932,12 @@
         <v>46334.25</v>
       </c>
       <c r="L82" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B83" t="s">
         <v>68</v>
@@ -3960,8 +3948,8 @@
       <c r="D83" t="s">
         <v>187</v>
       </c>
-      <c r="E83" s="1" t="s">
-        <v>188</v>
+      <c r="E83" s="1">
+        <v>102</v>
       </c>
       <c r="F83" t="s">
         <v>106</v>
@@ -3976,7 +3964,7 @@
         <v>46334</v>
       </c>
       <c r="L83" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -3987,10 +3975,10 @@
         <v>20</v>
       </c>
       <c r="D84" t="s">
+        <v>188</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>190</v>
       </c>
       <c r="F84" t="s">
         <v>24</v>
@@ -4005,7 +3993,7 @@
         <v>46335.041666666664</v>
       </c>
       <c r="L84" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -4019,13 +4007,13 @@
         <v>14</v>
       </c>
       <c r="D85" t="s">
+        <v>190</v>
+      </c>
+      <c r="E85" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="E85" s="1" t="s">
+      <c r="F85" t="s">
         <v>192</v>
-      </c>
-      <c r="F85" t="s">
-        <v>193</v>
       </c>
       <c r="G85" t="s">
         <v>17</v>
@@ -4069,12 +4057,12 @@
         <v>46333.75</v>
       </c>
       <c r="L86" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B87" t="s">
         <v>68</v>
@@ -4083,10 +4071,10 @@
         <v>99</v>
       </c>
       <c r="D87" t="s">
-        <v>194</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
+      </c>
+      <c r="E87" s="1">
+        <v>94</v>
       </c>
       <c r="F87" t="s">
         <v>102</v>
@@ -4101,7 +4089,7 @@
         <v>46335.041666666664</v>
       </c>
       <c r="L87" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -4115,10 +4103,10 @@
         <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F88" t="s">
         <v>16</v>
@@ -4150,7 +4138,7 @@
         <v>14</v>
       </c>
       <c r="D89" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E89" s="1">
         <v>11</v>
@@ -4185,10 +4173,10 @@
         <v>14</v>
       </c>
       <c r="D90" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F90" t="s">
         <v>16</v>
@@ -4214,16 +4202,16 @@
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C91" t="s">
         <v>95</v>
       </c>
       <c r="D91" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F91" t="s">
         <v>16</v>
@@ -4238,7 +4226,7 @@
         <v>46337.708333333336</v>
       </c>
       <c r="L91" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4252,7 +4240,7 @@
         <v>14</v>
       </c>
       <c r="D92" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E92" s="1">
         <v>1</v>
@@ -4287,7 +4275,7 @@
         <v>14</v>
       </c>
       <c r="D93" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E93" s="1">
         <v>1</v>
@@ -4322,10 +4310,10 @@
         <v>21</v>
       </c>
       <c r="D94" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F94" t="s">
         <v>24</v>
@@ -4340,7 +4328,7 @@
         <v>46339</v>
       </c>
       <c r="L94" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -4348,48 +4336,48 @@
         <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="C95" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="D95" t="s">
-        <v>204</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>205</v>
+        <v>46</v>
       </c>
       <c r="F95" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="I95" t="s">
         <v>18</v>
       </c>
       <c r="J95" s="2">
-        <v>46337.208333333336</v>
+        <v>46337.333333333336</v>
       </c>
       <c r="K95" s="2">
-        <v>46340.208333333336</v>
+        <v>46337.833333333336</v>
       </c>
       <c r="L95" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B96" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C96" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D96" t="s">
-        <v>46</v>
+        <v>202</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="F96" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="I96" t="s">
         <v>18</v>
@@ -4398,42 +4386,39 @@
         <v>46337.333333333336</v>
       </c>
       <c r="K96" s="2">
-        <v>46337.833333333336</v>
+        <v>46339.333333333336</v>
       </c>
       <c r="L96" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C97" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D97" t="s">
-        <v>206</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>207</v>
+        <v>58</v>
       </c>
       <c r="F97" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="I97" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="J97" s="2">
-        <v>46337.333333333336</v>
+        <v>46337.625</v>
       </c>
       <c r="K97" s="2">
-        <v>46339.333333333336</v>
+        <v>46338.125</v>
       </c>
       <c r="L97" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -4441,124 +4426,127 @@
         <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="C98" t="s">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="D98" t="s">
-        <v>58</v>
+        <v>204</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>205</v>
       </c>
       <c r="F98" t="s">
-        <v>59</v>
+        <v>16</v>
+      </c>
+      <c r="G98" t="s">
+        <v>17</v>
       </c>
       <c r="I98" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="J98" s="2">
-        <v>46337.625</v>
+        <v>46338.25</v>
       </c>
       <c r="K98" s="2">
-        <v>46338.125</v>
+        <v>46338.75</v>
       </c>
       <c r="L98" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B99" t="s">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="C99" t="s">
-        <v>14</v>
+        <v>137</v>
       </c>
       <c r="D99" t="s">
-        <v>208</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F99" t="s">
-        <v>16</v>
-      </c>
-      <c r="G99" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="I99" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J99" s="2">
-        <v>46338.25</v>
+        <v>46338.431250000001</v>
       </c>
       <c r="K99" s="2">
-        <v>46338.75</v>
+        <v>46339.472916666666</v>
       </c>
       <c r="L99" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B100" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="C100" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="D100" t="s">
-        <v>210</v>
+        <v>207</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="F100" t="s">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="I100" t="s">
         <v>18</v>
       </c>
       <c r="J100" s="2">
-        <v>46338.431250000001</v>
+        <v>46338.709027777775</v>
       </c>
       <c r="K100" s="2">
-        <v>46339.472916666666</v>
+        <v>46339.584027777775</v>
       </c>
       <c r="L100" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
+        <v>12</v>
+      </c>
+      <c r="B101" t="s">
+        <v>33</v>
+      </c>
+      <c r="C101" t="s">
         <v>34</v>
       </c>
-      <c r="B101" t="s">
-        <v>35</v>
-      </c>
-      <c r="C101" t="s">
-        <v>153</v>
-      </c>
       <c r="D101" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F101" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I101" t="s">
         <v>18</v>
       </c>
       <c r="J101" s="2">
-        <v>46338.709027777775</v>
+        <v>46338.958333333336</v>
       </c>
       <c r="K101" s="2">
-        <v>46339.584027777775</v>
+        <v>46342.208333333336</v>
       </c>
       <c r="L101" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="102" spans="1:12">
@@ -4566,19 +4554,19 @@
         <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C102" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D102" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="F102" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I102" t="s">
         <v>18</v>
@@ -4590,76 +4578,76 @@
         <v>46342.208333333336</v>
       </c>
       <c r="L102" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B103" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C103" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="D103" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F103" t="s">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c r="I103" t="s">
         <v>18</v>
       </c>
       <c r="J103" s="2">
-        <v>46338.958333333336</v>
+        <v>46339.083333333336</v>
       </c>
       <c r="K103" s="2">
-        <v>46342.208333333336</v>
+        <v>46340.291666666664</v>
       </c>
       <c r="L103" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B104" t="s">
         <v>68</v>
       </c>
       <c r="C104" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="D104" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F104" t="s">
-        <v>147</v>
+        <v>72</v>
       </c>
       <c r="I104" t="s">
         <v>18</v>
       </c>
       <c r="J104" s="2">
-        <v>46339.083333333336</v>
+        <v>46339.291666666664</v>
       </c>
       <c r="K104" s="2">
-        <v>46340.291666666664</v>
+        <v>46340.666666666664</v>
       </c>
       <c r="L104" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B105" t="s">
         <v>68</v>
@@ -4668,10 +4656,10 @@
         <v>69</v>
       </c>
       <c r="D105" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="F105" t="s">
         <v>72</v>
@@ -4686,39 +4674,36 @@
         <v>46340.666666666664</v>
       </c>
       <c r="L105" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="C106" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="D106" t="s">
-        <v>217</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="F106" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="I106" t="s">
         <v>18</v>
       </c>
       <c r="J106" s="2">
-        <v>46339.291666666664</v>
+        <v>46339.541666666664</v>
       </c>
       <c r="K106" s="2">
-        <v>46340.666666666664</v>
+        <v>46340.041666666664</v>
       </c>
       <c r="L106" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="107" spans="1:12">
@@ -4726,57 +4711,28 @@
         <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C107" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="D107" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F107" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="I107" t="s">
         <v>18</v>
       </c>
       <c r="J107" s="2">
-        <v>46339.541666666664</v>
+        <v>46339.704861111109</v>
       </c>
       <c r="K107" s="2">
-        <v>46340.041666666664</v>
+        <v>46340.204861111109</v>
       </c>
       <c r="L107" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12">
-      <c r="A108" t="s">
-        <v>12</v>
-      </c>
-      <c r="B108" t="s">
-        <v>44</v>
-      </c>
-      <c r="C108" t="s">
-        <v>45</v>
-      </c>
-      <c r="D108" t="s">
-        <v>84</v>
-      </c>
-      <c r="F108" t="s">
-        <v>48</v>
-      </c>
-      <c r="I108" t="s">
-        <v>18</v>
-      </c>
-      <c r="J108" s="2">
-        <v>46339.704861111109</v>
-      </c>
-      <c r="K108" s="2">
-        <v>46340.204861111109</v>
-      </c>
-      <c r="L108" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -4788,12 +4744,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
+  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
+</scriptIds>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -4931,35 +4904,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
-  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
-</scriptIds>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
--- a/data/vessels/2026-10-21.xlsx
+++ b/data/vessels/2026-10-21.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="444546" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2E404F8-584C-44E6-B465-96961921F3B0}"/>
+  <xr:revisionPtr revIDLastSave="445003" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E21A9FED-EEB7-43D3-BCAB-AEB29C44F485}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="214">
   <si>
     <t>Harbor</t>
   </si>
@@ -122,6 +122,24 @@
     <t>At berth</t>
   </si>
   <si>
+    <t>WUT</t>
+  </si>
+  <si>
+    <t>PN1</t>
+  </si>
+  <si>
+    <t>YM COSMOS</t>
+  </si>
+  <si>
+    <t>PN12639W</t>
+  </si>
+  <si>
+    <t>Yang Ming</t>
+  </si>
+  <si>
+    <t>Inchcape</t>
+  </si>
+  <si>
     <t>Seattle</t>
   </si>
   <si>
@@ -140,24 +158,6 @@
     <t>MSC</t>
   </si>
   <si>
-    <t>WUT</t>
-  </si>
-  <si>
-    <t>PN1</t>
-  </si>
-  <si>
-    <t>YM COSMOS</t>
-  </si>
-  <si>
-    <t>PN12639W</t>
-  </si>
-  <si>
-    <t>Yang Ming</t>
-  </si>
-  <si>
-    <t>Inchcape</t>
-  </si>
-  <si>
     <t>WC4/TP5</t>
   </si>
   <si>
@@ -170,72 +170,69 @@
     <t>Hapag-Lloyd</t>
   </si>
   <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>Matson - AK</t>
+  </si>
+  <si>
+    <t>MATSON ANCHORAGE</t>
+  </si>
+  <si>
+    <t>643S</t>
+  </si>
+  <si>
+    <t>Matson</t>
+  </si>
+  <si>
+    <t>SSA Marine</t>
+  </si>
+  <si>
     <t>In transit</t>
   </si>
   <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>Matson - AK</t>
-  </si>
-  <si>
-    <t>MATSON ANCHORAGE</t>
-  </si>
-  <si>
-    <t>643S</t>
-  </si>
-  <si>
-    <t>Matson</t>
-  </si>
-  <si>
-    <t>SSA Marine</t>
+    <t>EB1</t>
+  </si>
+  <si>
+    <t>MODERN LINK</t>
+  </si>
+  <si>
+    <t>Hyundai Glovis</t>
+  </si>
+  <si>
+    <t>Car Carrier</t>
+  </si>
+  <si>
+    <t>TOTE</t>
+  </si>
+  <si>
+    <t>Tote - AK1</t>
+  </si>
+  <si>
+    <t>MIDNIGHT SUN</t>
+  </si>
+  <si>
+    <t>Tote</t>
+  </si>
+  <si>
+    <t>Tote Maritime Alaska Inc</t>
+  </si>
+  <si>
+    <t>Multipurpose</t>
+  </si>
+  <si>
+    <t>EVER MACH</t>
+  </si>
+  <si>
+    <t>018W</t>
+  </si>
+  <si>
+    <t>BEN LINE</t>
   </si>
   <si>
     <t>T7</t>
   </si>
   <si>
-    <t>THEMIS LEADER</t>
-  </si>
-  <si>
-    <t>Car Carrier</t>
-  </si>
-  <si>
-    <t>EB1</t>
-  </si>
-  <si>
-    <t>MODERN LINK</t>
-  </si>
-  <si>
-    <t>Hyundai Glovis</t>
-  </si>
-  <si>
-    <t>TOTE</t>
-  </si>
-  <si>
-    <t>Tote - AK1</t>
-  </si>
-  <si>
-    <t>MIDNIGHT SUN</t>
-  </si>
-  <si>
-    <t>Tote</t>
-  </si>
-  <si>
-    <t>Tote Maritime Alaska Inc</t>
-  </si>
-  <si>
-    <t>Multipurpose</t>
-  </si>
-  <si>
-    <t>EVER MACH</t>
-  </si>
-  <si>
-    <t>018W</t>
-  </si>
-  <si>
-    <t>BEN LINE</t>
-  </si>
-  <si>
     <t>ARC INDEPENDENCE</t>
   </si>
   <si>
@@ -551,16 +548,16 @@
     <t>641E</t>
   </si>
   <si>
+    <t>TONGALA</t>
+  </si>
+  <si>
+    <t>KW666</t>
+  </si>
+  <si>
+    <t>Jones Stevedoring Co</t>
+  </si>
+  <si>
     <t>GLOVIS TREASURE</t>
-  </si>
-  <si>
-    <t>TONGALA</t>
-  </si>
-  <si>
-    <t>KW666</t>
-  </si>
-  <si>
-    <t>Jones Stevedoring Co</t>
   </si>
   <si>
     <t>MSC SABRINA</t>
@@ -756,10 +753,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L107" totalsRowShown="0">
-  <autoFilter ref="A1:L107" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L107">
-    <sortCondition ref="J2:J107"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L106" totalsRowShown="0">
+  <autoFilter ref="A1:L106" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L106">
+    <sortCondition ref="J2:J106"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1096,7 +1093,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L107"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1220,25 +1217,25 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
         <v>27</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>28</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>29</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" t="s">
         <v>31</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>32</v>
-      </c>
-      <c r="G4" t="s">
-        <v>17</v>
       </c>
       <c r="I4" t="s">
         <v>18</v>
@@ -1247,7 +1244,7 @@
         <v>46315.666666666664</v>
       </c>
       <c r="K4" s="2">
-        <v>46317.166666666664</v>
+        <v>46317.75</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -1255,25 +1252,25 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I5" t="s">
         <v>18</v>
@@ -1282,7 +1279,7 @@
         <v>46315.666666666664</v>
       </c>
       <c r="K5" s="2">
-        <v>46317.75</v>
+        <v>46317.166666666664</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -1320,7 +1317,7 @@
         <v>46322.166666666664</v>
       </c>
       <c r="L6" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1355,7 +1352,7 @@
         <v>46322.166666666664</v>
       </c>
       <c r="L7" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1363,25 +1360,25 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
         <v>44</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>45</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" t="s">
         <v>47</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" t="s">
         <v>48</v>
-      </c>
-      <c r="G8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" t="s">
-        <v>49</v>
       </c>
       <c r="I8" t="s">
         <v>18</v>
@@ -1393,7 +1390,7 @@
         <v>46316.916666666664</v>
       </c>
       <c r="L8" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1410,22 +1407,22 @@
         <v>51</v>
       </c>
       <c r="E9" s="1">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="G9" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J9" s="2">
-        <v>46316.25</v>
+        <v>46316.520833333336</v>
       </c>
       <c r="K9" s="2">
-        <v>46316.75</v>
+        <v>46317.166666666664</v>
       </c>
       <c r="L9" t="s">
         <v>19</v>
@@ -1436,34 +1433,37 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E10" s="1">
-        <v>2</v>
+        <v>26169</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G10" t="s">
-        <v>17</v>
+        <v>58</v>
+      </c>
+      <c r="H10" t="s">
+        <v>58</v>
       </c>
       <c r="I10" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="J10" s="2">
-        <v>46316.520833333336</v>
+        <v>46316.625</v>
       </c>
       <c r="K10" s="2">
-        <v>46317.166666666664</v>
+        <v>46317.041666666664</v>
       </c>
       <c r="L10" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1471,37 +1471,31 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" s="1">
-        <v>26169</v>
+        <v>60</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="G11" t="s">
-        <v>60</v>
-      </c>
-      <c r="H11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I11" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="J11" s="2">
-        <v>46316.625</v>
+        <v>46317.208333333336</v>
       </c>
       <c r="K11" s="2">
-        <v>46317.041666666664</v>
+        <v>46318.708333333336</v>
       </c>
       <c r="L11" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1509,31 +1503,34 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="G12" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="I12" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="J12" s="2">
-        <v>46317.208333333336</v>
+        <v>46317.875</v>
       </c>
       <c r="K12" s="2">
-        <v>46318.708333333336</v>
+        <v>46321.75</v>
       </c>
       <c r="L12" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1541,25 +1538,25 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G13" t="s">
         <v>17</v>
       </c>
       <c r="I13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J13" s="2">
         <v>46317.875</v>
@@ -1576,31 +1573,31 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
-      </c>
-      <c r="E14" s="1">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="G14" t="s">
-        <v>17</v>
+        <v>47</v>
+      </c>
+      <c r="H14" t="s">
+        <v>48</v>
       </c>
       <c r="I14" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J14" s="2">
-        <v>46317.875</v>
+        <v>46318.125</v>
       </c>
       <c r="K14" s="2">
-        <v>46321.75</v>
+        <v>46318.916666666664</v>
       </c>
       <c r="L14" t="s">
         <v>19</v>
@@ -1608,75 +1605,78 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
+        <v>69</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="F15" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" t="s">
         <v>48</v>
       </c>
-      <c r="G15" t="s">
-        <v>48</v>
-      </c>
-      <c r="H15" t="s">
-        <v>49</v>
-      </c>
       <c r="I15" t="s">
         <v>18</v>
       </c>
       <c r="J15" s="2">
-        <v>46318.125</v>
+        <v>46318.25</v>
       </c>
       <c r="K15" s="2">
-        <v>46318.916666666664</v>
+        <v>46319.166666666664</v>
       </c>
       <c r="L15" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F16" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G16" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H16" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="I16" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="J16" s="2">
-        <v>46318.25</v>
+        <v>46318.291666666664</v>
       </c>
       <c r="K16" s="2">
-        <v>46319.166666666664</v>
+        <v>46318.791666666664</v>
       </c>
       <c r="L16" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1684,37 +1684,37 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F17" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="G17" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="H17" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="I17" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J17" s="2">
-        <v>46318.291666666664</v>
+        <v>46318.416666666664</v>
       </c>
       <c r="K17" s="2">
-        <v>46318.791666666664</v>
+        <v>46319.125</v>
       </c>
       <c r="L17" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1722,37 +1722,34 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F18" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="G18" t="s">
-        <v>48</v>
-      </c>
-      <c r="H18" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="I18" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="J18" s="2">
-        <v>46318.416666666664</v>
+        <v>46318.583333333336</v>
       </c>
       <c r="K18" s="2">
-        <v>46319.125</v>
+        <v>46319.041666666664</v>
       </c>
       <c r="L18" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1760,28 +1757,31 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="E19" s="1">
+        <v>26168</v>
       </c>
       <c r="F19" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
-        <v>17</v>
+        <v>58</v>
+      </c>
+      <c r="H19" t="s">
+        <v>58</v>
       </c>
       <c r="I19" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="J19" s="2">
-        <v>46318.583333333336</v>
+        <v>46318.625</v>
       </c>
       <c r="K19" s="2">
         <v>46319.041666666664</v>
@@ -1795,37 +1795,31 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s">
         <v>83</v>
       </c>
-      <c r="E20" s="1">
-        <v>26168</v>
+      <c r="E20" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="F20" t="s">
-        <v>59</v>
-      </c>
-      <c r="G20" t="s">
-        <v>60</v>
-      </c>
-      <c r="H20" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="I20" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="J20" s="2">
-        <v>46318.625</v>
+        <v>46318.704861111109</v>
       </c>
       <c r="K20" s="2">
-        <v>46319.041666666664</v>
+        <v>46319.204861111109</v>
       </c>
       <c r="L20" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1833,107 +1827,110 @@
         <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D21" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="F21" t="s">
-        <v>48</v>
+        <v>74</v>
+      </c>
+      <c r="G21" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" t="s">
+        <v>75</v>
       </c>
       <c r="I21" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="J21" s="2">
-        <v>46318.704861111109</v>
+        <v>46318.833333333336</v>
       </c>
       <c r="K21" s="2">
-        <v>46319.204861111109</v>
+        <v>46319.791666666664</v>
       </c>
       <c r="L21" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="D22" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F22" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="G22" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="I22" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J22" s="2">
-        <v>46318.833333333336</v>
+        <v>46318.916666666664</v>
       </c>
       <c r="K22" s="2">
-        <v>46319.791666666664</v>
+        <v>46320.083333333336</v>
       </c>
       <c r="L22" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
+      </c>
+      <c r="E23" s="1">
+        <v>21</v>
       </c>
       <c r="F23" t="s">
-        <v>89</v>
+        <v>31</v>
       </c>
       <c r="G23" t="s">
-        <v>90</v>
-      </c>
-      <c r="H23" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="I23" t="s">
         <v>18</v>
       </c>
       <c r="J23" s="2">
-        <v>46318.916666666664</v>
+        <v>46319.208333333336</v>
       </c>
       <c r="K23" s="2">
-        <v>46320.083333333336</v>
+        <v>46325.75</v>
       </c>
       <c r="L23" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1941,34 +1938,34 @@
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="D24" t="s">
         <v>92</v>
       </c>
-      <c r="E24" s="1">
-        <v>21</v>
+      <c r="E24" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="F24" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="G24" t="s">
         <v>17</v>
       </c>
       <c r="I24" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="J24" s="2">
-        <v>46319.208333333336</v>
+        <v>46319.25</v>
       </c>
       <c r="K24" s="2">
-        <v>46325.75</v>
+        <v>46319.75</v>
       </c>
       <c r="L24" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1976,34 +1973,34 @@
         <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="D25" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F25" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="G25" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="I25" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J25" s="2">
-        <v>46319.25</v>
+        <v>46319.666666666664</v>
       </c>
       <c r="K25" s="2">
-        <v>46319.75</v>
+        <v>46321.75</v>
       </c>
       <c r="L25" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2011,139 +2008,139 @@
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>96</v>
-      </c>
-      <c r="E26" s="1" t="s">
         <v>97</v>
       </c>
+      <c r="E26" s="1">
+        <v>4</v>
+      </c>
       <c r="F26" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="G26" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I26" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="J26" s="2">
-        <v>46319.666666666664</v>
+        <v>46320.166666666664</v>
       </c>
       <c r="K26" s="2">
-        <v>46321.75</v>
+        <v>46320.75</v>
       </c>
       <c r="L26" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="D27" t="s">
-        <v>98</v>
-      </c>
-      <c r="E27" s="1">
-        <v>4</v>
+        <v>99</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="F27" t="s">
-        <v>55</v>
+        <v>101</v>
       </c>
       <c r="G27" t="s">
         <v>17</v>
       </c>
       <c r="I27" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J27" s="2">
-        <v>46320.166666666664</v>
+        <v>46320.625</v>
       </c>
       <c r="K27" s="2">
-        <v>46320.75</v>
+        <v>46322.75</v>
       </c>
       <c r="L27" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D28" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F28" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G28" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="I28" t="s">
         <v>18</v>
       </c>
       <c r="J28" s="2">
-        <v>46320.625</v>
+        <v>46321.208333333336</v>
       </c>
       <c r="K28" s="2">
-        <v>46322.75</v>
+        <v>46322.166666666664</v>
       </c>
       <c r="L28" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s">
         <v>27</v>
       </c>
-      <c r="B29" t="s">
-        <v>68</v>
-      </c>
       <c r="C29" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="D29" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F29" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="G29" t="s">
-        <v>107</v>
+        <v>32</v>
       </c>
       <c r="I29" t="s">
         <v>18</v>
       </c>
       <c r="J29" s="2">
-        <v>46321.208333333336</v>
+        <v>46321.25</v>
       </c>
       <c r="K29" s="2">
-        <v>46322.166666666664</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L29" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2151,34 +2148,37 @@
         <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C30" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F30" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="G30" t="s">
-        <v>38</v>
+        <v>111</v>
+      </c>
+      <c r="H30" t="s">
+        <v>112</v>
       </c>
       <c r="I30" t="s">
         <v>18</v>
       </c>
       <c r="J30" s="2">
-        <v>46321.25</v>
+        <v>46322.208333333336</v>
       </c>
       <c r="K30" s="2">
-        <v>46323.166666666664</v>
+        <v>46324.791666666664</v>
       </c>
       <c r="L30" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -2186,37 +2186,34 @@
         <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="C31" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>110</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F31" t="s">
-        <v>24</v>
+        <v>115</v>
       </c>
       <c r="G31" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="H31" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I31" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="J31" s="2">
-        <v>46322.208333333336</v>
+        <v>46322.25</v>
       </c>
       <c r="K31" s="2">
-        <v>46324.791666666664</v>
+        <v>46322.75</v>
       </c>
       <c r="L31" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -2224,31 +2221,34 @@
         <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>114</v>
+        <v>63</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
       </c>
       <c r="D32" t="s">
+        <v>117</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F32" t="s">
         <v>115</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
+        <v>32</v>
+      </c>
+      <c r="H32" t="s">
         <v>116</v>
       </c>
-      <c r="G32" t="s">
-        <v>38</v>
-      </c>
-      <c r="H32" t="s">
-        <v>117</v>
-      </c>
       <c r="I32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J32" s="2">
         <v>46322.25</v>
       </c>
       <c r="K32" s="2">
-        <v>46322.75</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L32" t="s">
         <v>19</v>
@@ -2259,37 +2259,34 @@
         <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="D33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F33" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="G33" t="s">
-        <v>38</v>
-      </c>
-      <c r="H33" t="s">
-        <v>117</v>
+        <v>17</v>
       </c>
       <c r="I33" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J33" s="2">
-        <v>46322.25</v>
+        <v>46322.625</v>
       </c>
       <c r="K33" s="2">
-        <v>46323.166666666664</v>
+        <v>46325.75</v>
       </c>
       <c r="L33" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -2297,34 +2294,34 @@
         <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C34" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D34" t="s">
-        <v>120</v>
-      </c>
-      <c r="E34" s="1" t="s">
         <v>121</v>
       </c>
       <c r="F34" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G34" t="s">
-        <v>17</v>
+        <v>47</v>
+      </c>
+      <c r="H34" t="s">
+        <v>48</v>
       </c>
       <c r="I34" t="s">
         <v>18</v>
       </c>
       <c r="J34" s="2">
-        <v>46322.625</v>
+        <v>46323.104166666664</v>
       </c>
       <c r="K34" s="2">
-        <v>46325.75</v>
+        <v>46323.916666666664</v>
       </c>
       <c r="L34" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2332,60 +2329,60 @@
         <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D35" t="s">
         <v>122</v>
       </c>
+      <c r="E35" s="1" t="s">
+        <v>123</v>
+      </c>
       <c r="F35" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="G35" t="s">
-        <v>48</v>
-      </c>
-      <c r="H35" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="I35" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="J35" s="2">
-        <v>46323.104166666664</v>
+        <v>46323.25</v>
       </c>
       <c r="K35" s="2">
-        <v>46323.916666666664</v>
+        <v>46323.75</v>
       </c>
       <c r="L35" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
-      </c>
-      <c r="C36" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="D36" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F36" t="s">
-        <v>16</v>
+        <v>126</v>
       </c>
       <c r="G36" t="s">
         <v>17</v>
       </c>
+      <c r="H36" t="s">
+        <v>48</v>
+      </c>
       <c r="I36" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J36" s="2">
         <v>46323.25</v>
@@ -2394,180 +2391,180 @@
         <v>46323.75</v>
       </c>
       <c r="L36" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>68</v>
+        <v>54</v>
+      </c>
+      <c r="C37" t="s">
+        <v>55</v>
       </c>
       <c r="D37" t="s">
-        <v>125</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>126</v>
+        <v>56</v>
+      </c>
+      <c r="E37" s="1">
+        <v>26173</v>
       </c>
       <c r="F37" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="G37" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="H37" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="I37" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="J37" s="2">
-        <v>46323.25</v>
+        <v>46323.625</v>
       </c>
       <c r="K37" s="2">
-        <v>46323.75</v>
+        <v>46324.041666666664</v>
       </c>
       <c r="L37" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="C38" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="D38" t="s">
-        <v>58</v>
-      </c>
-      <c r="E38" s="1">
-        <v>26173</v>
+        <v>127</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="F38" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="G38" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="H38" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="I38" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="J38" s="2">
-        <v>46323.625</v>
+        <v>46323.708333333336</v>
       </c>
       <c r="K38" s="2">
-        <v>46324.041666666664</v>
+        <v>46325.166666666664</v>
       </c>
       <c r="L38" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>28</v>
+        <v>113</v>
       </c>
       <c r="C39" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="F39" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G39" t="s">
         <v>17</v>
       </c>
-      <c r="H39" t="s">
-        <v>49</v>
-      </c>
       <c r="I39" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="J39" s="2">
-        <v>46323.708333333336</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="K39" s="2">
-        <v>46325.166666666664</v>
+        <v>46324.75</v>
       </c>
       <c r="L39" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B40" t="s">
-        <v>114</v>
+        <v>67</v>
       </c>
       <c r="C40" t="s">
-        <v>14</v>
+        <v>129</v>
       </c>
       <c r="D40" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F40" t="s">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="G40" t="s">
         <v>17</v>
       </c>
+      <c r="H40" t="s">
+        <v>48</v>
+      </c>
       <c r="I40" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J40" s="2">
-        <v>46323.791666666664</v>
+        <v>46324.25</v>
       </c>
       <c r="K40" s="2">
-        <v>46324.75</v>
+        <v>46325.166666666664</v>
       </c>
       <c r="L40" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" t="s">
         <v>27</v>
       </c>
-      <c r="B41" t="s">
-        <v>68</v>
-      </c>
       <c r="C41" t="s">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="D41" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F41" t="s">
-        <v>102</v>
+        <v>16</v>
       </c>
       <c r="G41" t="s">
         <v>17</v>
       </c>
-      <c r="H41" t="s">
-        <v>49</v>
-      </c>
       <c r="I41" t="s">
         <v>18</v>
       </c>
@@ -2575,10 +2572,10 @@
         <v>46324.25</v>
       </c>
       <c r="K41" s="2">
-        <v>46325.166666666664</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="L41" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2586,34 +2583,28 @@
         <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C42" t="s">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="D42" t="s">
-        <v>133</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>134</v>
+        <v>45</v>
       </c>
       <c r="F42" t="s">
-        <v>16</v>
-      </c>
-      <c r="G42" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="I42" t="s">
         <v>18</v>
       </c>
       <c r="J42" s="2">
-        <v>46324.25</v>
+        <v>46325.333333333336</v>
       </c>
       <c r="K42" s="2">
-        <v>46326.166666666664</v>
+        <v>46325.833333333336</v>
       </c>
       <c r="L42" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -2621,28 +2612,37 @@
         <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C43" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="D43" t="s">
-        <v>46</v>
+        <v>82</v>
+      </c>
+      <c r="E43" s="1">
+        <v>26172</v>
       </c>
       <c r="F43" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="G43" t="s">
+        <v>58</v>
+      </c>
+      <c r="H43" t="s">
+        <v>58</v>
       </c>
       <c r="I43" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="J43" s="2">
-        <v>46325.333333333336</v>
+        <v>46325.625</v>
       </c>
       <c r="K43" s="2">
-        <v>46325.833333333336</v>
+        <v>46326.041666666664</v>
       </c>
       <c r="L43" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2650,37 +2650,31 @@
         <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
-      </c>
-      <c r="C44" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D44" t="s">
-        <v>83</v>
-      </c>
-      <c r="E44" s="1">
-        <v>26172</v>
+        <v>134</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="F44" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="G44" t="s">
-        <v>60</v>
-      </c>
-      <c r="H44" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I44" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="J44" s="2">
-        <v>46325.625</v>
+        <v>46325.708333333336</v>
       </c>
       <c r="K44" s="2">
-        <v>46326.041666666664</v>
+        <v>46327.208333333336</v>
       </c>
       <c r="L44" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2691,16 +2685,16 @@
         <v>20</v>
       </c>
       <c r="D45" t="s">
+        <v>134</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="F45" t="s">
         <v>24</v>
       </c>
       <c r="G45" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I45" t="s">
         <v>18</v>
@@ -2712,74 +2706,77 @@
         <v>46327.208333333336</v>
       </c>
       <c r="L45" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B46" t="s">
-        <v>20</v>
+        <v>67</v>
+      </c>
+      <c r="C46" t="s">
+        <v>136</v>
       </c>
       <c r="D46" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F46" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="G46" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="I46" t="s">
         <v>18</v>
       </c>
       <c r="J46" s="2">
-        <v>46325.708333333336</v>
+        <v>46325.958333333336</v>
       </c>
       <c r="K46" s="2">
-        <v>46327.208333333336</v>
+        <v>46327.416666666664</v>
       </c>
       <c r="L46" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>68</v>
+        <v>113</v>
       </c>
       <c r="C47" t="s">
-        <v>137</v>
+        <v>14</v>
       </c>
       <c r="D47" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F47" t="s">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="G47" t="s">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="I47" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="J47" s="2">
-        <v>46325.958333333336</v>
+        <v>46326.25</v>
       </c>
       <c r="K47" s="2">
-        <v>46327.416666666664</v>
+        <v>46326.75</v>
       </c>
       <c r="L47" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2787,98 +2784,95 @@
         <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c r="C48" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="D48" t="s">
-        <v>140</v>
-      </c>
-      <c r="E48" s="1" t="s">
         <v>141</v>
       </c>
       <c r="F48" t="s">
-        <v>16</v>
-      </c>
-      <c r="G48" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="I48" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J48" s="2">
-        <v>46326.25</v>
+        <v>46326.416666666664</v>
       </c>
       <c r="K48" s="2">
         <v>46326.75</v>
       </c>
       <c r="L48" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B49" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C49" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="D49" t="s">
         <v>142</v>
       </c>
+      <c r="E49" s="1" t="s">
+        <v>143</v>
+      </c>
       <c r="F49" t="s">
-        <v>48</v>
+        <v>101</v>
+      </c>
+      <c r="G49" t="s">
+        <v>17</v>
       </c>
       <c r="I49" t="s">
         <v>18</v>
       </c>
       <c r="J49" s="2">
-        <v>46326.416666666664</v>
+        <v>46326.625</v>
       </c>
       <c r="K49" s="2">
-        <v>46326.75</v>
+        <v>46328.75</v>
       </c>
       <c r="L49" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" t="s">
         <v>27</v>
       </c>
-      <c r="B50" t="s">
-        <v>68</v>
-      </c>
       <c r="C50" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F50" t="s">
-        <v>102</v>
-      </c>
-      <c r="G50" t="s">
-        <v>17</v>
+        <v>146</v>
       </c>
       <c r="I50" t="s">
         <v>18</v>
       </c>
       <c r="J50" s="2">
-        <v>46326.625</v>
+        <v>46326.833333333336</v>
       </c>
       <c r="K50" s="2">
-        <v>46328.75</v>
+        <v>46329.583333333336</v>
       </c>
       <c r="L50" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -2886,86 +2880,89 @@
         <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="C51" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="D51" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F51" t="s">
-        <v>147</v>
+        <v>16</v>
+      </c>
+      <c r="G51" t="s">
+        <v>17</v>
       </c>
       <c r="I51" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="J51" s="2">
-        <v>46326.833333333336</v>
+        <v>46327.25</v>
       </c>
       <c r="K51" s="2">
-        <v>46329.583333333336</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="L51" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>114</v>
+        <v>34</v>
       </c>
       <c r="C52" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D52" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F52" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="G52" t="s">
         <v>17</v>
       </c>
       <c r="I52" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J52" s="2">
-        <v>46327.25</v>
+        <v>46327.291666666664</v>
       </c>
       <c r="K52" s="2">
-        <v>46327.708333333336</v>
+        <v>46329.166666666664</v>
       </c>
       <c r="L52" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="D53" t="s">
-        <v>150</v>
-      </c>
-      <c r="E53" s="1" t="s">
         <v>151</v>
       </c>
+      <c r="E53" s="1">
+        <v>2</v>
+      </c>
       <c r="F53" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G53" t="s">
         <v>17</v>
@@ -2974,33 +2971,33 @@
         <v>18</v>
       </c>
       <c r="J53" s="2">
-        <v>46327.291666666664</v>
+        <v>46327.625</v>
       </c>
       <c r="K53" s="2">
-        <v>46329.166666666664</v>
+        <v>46331.75</v>
       </c>
       <c r="L53" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B54" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C54" t="s">
-        <v>91</v>
+        <v>152</v>
       </c>
       <c r="D54" t="s">
-        <v>152</v>
-      </c>
-      <c r="E54" s="1">
-        <v>2</v>
+        <v>153</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="F54" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="G54" t="s">
         <v>17</v>
@@ -3009,115 +3006,118 @@
         <v>18</v>
       </c>
       <c r="J54" s="2">
-        <v>46327.625</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K54" s="2">
-        <v>46331.75</v>
+        <v>46328.75</v>
       </c>
       <c r="L54" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
+        <v>12</v>
+      </c>
+      <c r="B55" t="s">
         <v>27</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>28</v>
       </c>
-      <c r="C55" t="s">
-        <v>153</v>
-      </c>
       <c r="D55" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F55" t="s">
-        <v>32</v>
-      </c>
-      <c r="G55" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I55" t="s">
         <v>18</v>
       </c>
       <c r="J55" s="2">
-        <v>46327.708333333336</v>
+        <v>46327.904861111114</v>
       </c>
       <c r="K55" s="2">
-        <v>46328.75</v>
+        <v>46331.196527777778</v>
       </c>
       <c r="L55" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B56" t="s">
-        <v>33</v>
-      </c>
-      <c r="C56" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="D56" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F56" t="s">
-        <v>16</v>
+        <v>126</v>
+      </c>
+      <c r="G56" t="s">
+        <v>17</v>
+      </c>
+      <c r="H56" t="s">
+        <v>48</v>
       </c>
       <c r="I56" t="s">
         <v>18</v>
       </c>
       <c r="J56" s="2">
-        <v>46327.904861111114</v>
+        <v>46328.25</v>
       </c>
       <c r="K56" s="2">
-        <v>46331.196527777778</v>
+        <v>46328.75</v>
       </c>
       <c r="L56" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>68</v>
+        <v>20</v>
+      </c>
+      <c r="C57" t="s">
+        <v>21</v>
       </c>
       <c r="D57" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F57" t="s">
-        <v>127</v>
+        <v>24</v>
       </c>
       <c r="G57" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="H57" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="I57" t="s">
         <v>18</v>
       </c>
       <c r="J57" s="2">
-        <v>46328.25</v>
+        <v>46329.208333333336</v>
       </c>
       <c r="K57" s="2">
-        <v>46328.75</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="L57" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -3125,37 +3125,31 @@
         <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="D58" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F58" t="s">
-        <v>24</v>
-      </c>
-      <c r="G58" t="s">
-        <v>64</v>
-      </c>
-      <c r="H58" t="s">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="I58" t="s">
         <v>18</v>
       </c>
       <c r="J58" s="2">
-        <v>46329.208333333336</v>
+        <v>46329.333333333336</v>
       </c>
       <c r="K58" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.625</v>
       </c>
       <c r="L58" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -3166,28 +3160,28 @@
         <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="D59" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F59" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="I59" t="s">
         <v>18</v>
       </c>
       <c r="J59" s="2">
-        <v>46329.333333333336</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K59" s="2">
-        <v>46332.625</v>
+        <v>46334</v>
       </c>
       <c r="L59" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3198,13 +3192,13 @@
         <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D60" t="s">
+        <v>163</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>165</v>
       </c>
       <c r="F60" t="s">
         <v>16</v>
@@ -3219,74 +3213,71 @@
         <v>46334</v>
       </c>
       <c r="L60" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B61" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C61" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="D61" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F61" t="s">
-        <v>16</v>
+        <v>38</v>
+      </c>
+      <c r="G61" t="s">
+        <v>17</v>
       </c>
       <c r="I61" t="s">
         <v>18</v>
       </c>
       <c r="J61" s="2">
-        <v>46330.208333333336</v>
+        <v>46330.291666666664</v>
       </c>
       <c r="K61" s="2">
-        <v>46334</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L61" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="C62" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="D62" t="s">
-        <v>166</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>167</v>
+        <v>56</v>
       </c>
       <c r="F62" t="s">
-        <v>32</v>
-      </c>
-      <c r="G62" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="I62" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="J62" s="2">
-        <v>46330.291666666664</v>
+        <v>46330.625</v>
       </c>
       <c r="K62" s="2">
-        <v>46332.166666666664</v>
+        <v>46331.125</v>
       </c>
       <c r="L62" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -3294,28 +3285,31 @@
         <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="C63" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="D63" t="s">
-        <v>58</v>
+        <v>167</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>168</v>
       </c>
       <c r="F63" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="I63" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="J63" s="2">
-        <v>46330.625</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K63" s="2">
-        <v>46331.125</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L63" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3329,13 +3323,13 @@
         <v>39</v>
       </c>
       <c r="D64" t="s">
+        <v>167</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E64" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="F64" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I64" t="s">
         <v>18</v>
@@ -3347,7 +3341,7 @@
         <v>46333.925000000003</v>
       </c>
       <c r="L64" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -3355,31 +3349,28 @@
         <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C65" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D65" t="s">
-        <v>168</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>169</v>
+        <v>83</v>
       </c>
       <c r="F65" t="s">
-        <v>147</v>
+        <v>47</v>
       </c>
       <c r="I65" t="s">
         <v>18</v>
       </c>
       <c r="J65" s="2">
-        <v>46330.633333333331</v>
+        <v>46330.704861111109</v>
       </c>
       <c r="K65" s="2">
-        <v>46333.925000000003</v>
+        <v>46331.204861111109</v>
       </c>
       <c r="L65" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -3387,28 +3378,37 @@
         <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C66" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>84</v>
+        <v>169</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="F66" t="s">
-        <v>48</v>
+        <v>74</v>
+      </c>
+      <c r="G66" t="s">
+        <v>17</v>
+      </c>
+      <c r="H66" t="s">
+        <v>171</v>
       </c>
       <c r="I66" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="J66" s="2">
-        <v>46330.704861111109</v>
+        <v>46331.25</v>
       </c>
       <c r="K66" s="2">
-        <v>46331.204861111109</v>
+        <v>46331.75</v>
       </c>
       <c r="L66" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -3416,25 +3416,25 @@
         <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C67" t="s">
         <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E67" s="1">
         <v>10</v>
       </c>
       <c r="F67" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G67" t="s">
         <v>17</v>
       </c>
       <c r="I67" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J67" s="2">
         <v>46331.25</v>
@@ -3448,75 +3448,69 @@
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B68" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="C68" t="s">
-        <v>14</v>
+        <v>152</v>
       </c>
       <c r="D68" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F68" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="G68" t="s">
         <v>17</v>
       </c>
-      <c r="H68" t="s">
-        <v>173</v>
-      </c>
       <c r="I68" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J68" s="2">
-        <v>46331.25</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K68" s="2">
-        <v>46331.75</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L68" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
+        <v>12</v>
+      </c>
+      <c r="B69" t="s">
         <v>27</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>28</v>
       </c>
-      <c r="C69" t="s">
-        <v>153</v>
-      </c>
       <c r="D69" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F69" t="s">
-        <v>32</v>
-      </c>
-      <c r="G69" t="s">
-        <v>17</v>
+        <v>146</v>
       </c>
       <c r="I69" t="s">
         <v>18</v>
       </c>
       <c r="J69" s="2">
-        <v>46331.291666666664</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K69" s="2">
-        <v>46332.166666666664</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L69" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3524,19 +3518,19 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C70" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D70" t="s">
+        <v>175</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="E70" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="F70" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I70" t="s">
         <v>18</v>
@@ -3548,7 +3542,7 @@
         <v>46334.746527777781</v>
       </c>
       <c r="L70" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -3556,31 +3550,34 @@
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="C71" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D71" t="s">
-        <v>176</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
+      </c>
+      <c r="E71" s="1">
+        <v>10</v>
       </c>
       <c r="F71" t="s">
-        <v>147</v>
+        <v>52</v>
+      </c>
+      <c r="G71" t="s">
+        <v>17</v>
       </c>
       <c r="I71" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="J71" s="2">
-        <v>46331.496527777781</v>
+        <v>46331.708333333336</v>
       </c>
       <c r="K71" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L71" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -3588,31 +3585,34 @@
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C72" t="s">
         <v>14</v>
       </c>
       <c r="D72" t="s">
+        <v>169</v>
+      </c>
+      <c r="E72" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E72" s="1">
-        <v>10</v>
-      </c>
       <c r="F72" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="G72" t="s">
         <v>17</v>
       </c>
+      <c r="H72" t="s">
+        <v>171</v>
+      </c>
       <c r="I72" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J72" s="2">
-        <v>46331.708333333336</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K72" s="2">
-        <v>46332.166666666664</v>
+        <v>46332.75</v>
       </c>
       <c r="L72" t="s">
         <v>19</v>
@@ -3620,130 +3620,121 @@
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B73" t="s">
-        <v>114</v>
+        <v>67</v>
       </c>
       <c r="C73" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="D73" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="F73" t="s">
-        <v>75</v>
-      </c>
-      <c r="G73" t="s">
-        <v>17</v>
-      </c>
-      <c r="H73" t="s">
-        <v>173</v>
+        <v>88</v>
       </c>
       <c r="I73" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J73" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K73" s="2">
-        <v>46332.75</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L73" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C74" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F74" t="s">
-        <v>89</v>
+        <v>74</v>
+      </c>
+      <c r="G74" t="s">
+        <v>17</v>
       </c>
       <c r="I74" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="J74" s="2">
-        <v>46332.056250000001</v>
+        <v>46332.25</v>
       </c>
       <c r="K74" s="2">
-        <v>46332.597916666666</v>
+        <v>46332.75</v>
       </c>
       <c r="L74" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B75" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="C75" t="s">
-        <v>14</v>
+        <v>152</v>
       </c>
       <c r="D75" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F75" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="G75" t="s">
         <v>17</v>
       </c>
       <c r="I75" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J75" s="2">
-        <v>46332.25</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K75" s="2">
-        <v>46332.75</v>
+        <v>46333.166666666664</v>
       </c>
       <c r="L75" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="C76" t="s">
-        <v>153</v>
+        <v>44</v>
       </c>
       <c r="D76" t="s">
-        <v>182</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>183</v>
+        <v>121</v>
       </c>
       <c r="F76" t="s">
-        <v>32</v>
-      </c>
-      <c r="G76" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="I76" t="s">
         <v>18</v>
@@ -3752,53 +3743,50 @@
         <v>46332.291666666664</v>
       </c>
       <c r="K76" s="2">
-        <v>46333.166666666664</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="L76" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B77" t="s">
-        <v>44</v>
-      </c>
-      <c r="C77" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="D77" t="s">
-        <v>122</v>
+        <v>183</v>
       </c>
       <c r="F77" t="s">
-        <v>48</v>
+        <v>126</v>
       </c>
       <c r="I77" t="s">
         <v>18</v>
       </c>
       <c r="J77" s="2">
-        <v>46332.291666666664</v>
+        <v>46332.375</v>
       </c>
       <c r="K77" s="2">
-        <v>46332.791666666664</v>
+        <v>46333.5</v>
       </c>
       <c r="L77" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B78" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D78" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F78" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I78" t="s">
         <v>18</v>
@@ -3810,33 +3798,36 @@
         <v>46333.5</v>
       </c>
       <c r="L78" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>68</v>
+        <v>54</v>
+      </c>
+      <c r="C79" t="s">
+        <v>81</v>
       </c>
       <c r="D79" t="s">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="F79" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="I79" t="s">
         <v>18</v>
       </c>
       <c r="J79" s="2">
-        <v>46332.375</v>
+        <v>46332.541666666664</v>
       </c>
       <c r="K79" s="2">
-        <v>46333.5</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="L79" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -3844,127 +3835,127 @@
         <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="C80" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>83</v>
+        <v>179</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>180</v>
       </c>
       <c r="F80" t="s">
-        <v>59</v>
+        <v>74</v>
+      </c>
+      <c r="G80" t="s">
+        <v>17</v>
       </c>
       <c r="I80" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="J80" s="2">
-        <v>46332.541666666664</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="K80" s="2">
-        <v>46333.041666666664</v>
+        <v>46333.75</v>
       </c>
       <c r="L80" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B81" t="s">
-        <v>114</v>
+        <v>67</v>
       </c>
       <c r="C81" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="D81" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F81" t="s">
-        <v>75</v>
-      </c>
-      <c r="G81" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="I81" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J81" s="2">
-        <v>46332.791666666664</v>
+        <v>46332.875</v>
       </c>
       <c r="K81" s="2">
-        <v>46333.75</v>
+        <v>46334.25</v>
       </c>
       <c r="L81" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B82" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C82" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="D82" t="s">
-        <v>185</v>
-      </c>
-      <c r="E82" s="1" t="s">
         <v>186</v>
       </c>
+      <c r="E82" s="1">
+        <v>102</v>
+      </c>
       <c r="F82" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="I82" t="s">
         <v>18</v>
       </c>
       <c r="J82" s="2">
-        <v>46332.875</v>
+        <v>46333</v>
       </c>
       <c r="K82" s="2">
-        <v>46334.25</v>
+        <v>46334</v>
       </c>
       <c r="L82" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>68</v>
-      </c>
-      <c r="C83" t="s">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="D83" t="s">
         <v>187</v>
       </c>
-      <c r="E83" s="1">
-        <v>102</v>
+      <c r="E83" s="1" t="s">
+        <v>188</v>
       </c>
       <c r="F83" t="s">
-        <v>106</v>
+        <v>24</v>
       </c>
       <c r="I83" t="s">
         <v>18</v>
       </c>
       <c r="J83" s="2">
-        <v>46333</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="K83" s="2">
-        <v>46334</v>
+        <v>46335.041666666664</v>
       </c>
       <c r="L83" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -3972,28 +3963,34 @@
         <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>20</v>
+        <v>50</v>
+      </c>
+      <c r="C84" t="s">
+        <v>14</v>
       </c>
       <c r="D84" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F84" t="s">
-        <v>24</v>
+        <v>191</v>
+      </c>
+      <c r="G84" t="s">
+        <v>17</v>
       </c>
       <c r="I84" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="J84" s="2">
-        <v>46333.041666666664</v>
+        <v>46333.25</v>
       </c>
       <c r="K84" s="2">
-        <v>46335.041666666664</v>
+        <v>46333.75</v>
       </c>
       <c r="L84" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -4001,95 +3998,95 @@
         <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C85" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="D85" t="s">
-        <v>190</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>191</v>
+        <v>77</v>
       </c>
       <c r="F85" t="s">
-        <v>192</v>
-      </c>
-      <c r="G85" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="I85" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J85" s="2">
-        <v>46333.25</v>
+        <v>46333.416666666664</v>
       </c>
       <c r="K85" s="2">
         <v>46333.75</v>
       </c>
       <c r="L85" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B86" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C86" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="D86" t="s">
-        <v>78</v>
+        <v>192</v>
+      </c>
+      <c r="E86" s="1">
+        <v>94</v>
       </c>
       <c r="F86" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="I86" t="s">
         <v>18</v>
       </c>
       <c r="J86" s="2">
-        <v>46333.416666666664</v>
+        <v>46333.666666666664</v>
       </c>
       <c r="K86" s="2">
-        <v>46333.75</v>
+        <v>46335.041666666664</v>
       </c>
       <c r="L86" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C87" t="s">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="D87" t="s">
         <v>193</v>
       </c>
-      <c r="E87" s="1">
-        <v>94</v>
+      <c r="E87" s="1" t="s">
+        <v>194</v>
       </c>
       <c r="F87" t="s">
-        <v>102</v>
+        <v>16</v>
+      </c>
+      <c r="G87" t="s">
+        <v>17</v>
       </c>
       <c r="I87" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="J87" s="2">
-        <v>46333.666666666664</v>
+        <v>46334.25</v>
       </c>
       <c r="K87" s="2">
-        <v>46335.041666666664</v>
+        <v>46334.75</v>
       </c>
       <c r="L87" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -4097,25 +4094,25 @@
         <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C88" t="s">
         <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>194</v>
-      </c>
-      <c r="E88" s="1" t="s">
         <v>195</v>
       </c>
+      <c r="E88" s="1">
+        <v>11</v>
+      </c>
       <c r="F88" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="G88" t="s">
         <v>17</v>
       </c>
       <c r="I88" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J88" s="2">
         <v>46334.25</v>
@@ -4132,31 +4129,31 @@
         <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="C89" t="s">
         <v>14</v>
       </c>
       <c r="D89" t="s">
-        <v>196</v>
-      </c>
-      <c r="E89" s="1">
-        <v>11</v>
+        <v>193</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>194</v>
       </c>
       <c r="F89" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="G89" t="s">
         <v>17</v>
       </c>
       <c r="I89" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J89" s="2">
-        <v>46334.25</v>
+        <v>46334.791666666664</v>
       </c>
       <c r="K89" s="2">
-        <v>46334.75</v>
+        <v>46335.75</v>
       </c>
       <c r="L89" t="s">
         <v>19</v>
@@ -4167,34 +4164,31 @@
         <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c r="C90" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="D90" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F90" t="s">
         <v>16</v>
       </c>
-      <c r="G90" t="s">
-        <v>17</v>
-      </c>
       <c r="I90" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J90" s="2">
-        <v>46334.791666666664</v>
+        <v>46334.958333333336</v>
       </c>
       <c r="K90" s="2">
-        <v>46335.75</v>
+        <v>46337.708333333336</v>
       </c>
       <c r="L90" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -4202,31 +4196,34 @@
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="C91" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>197</v>
-      </c>
-      <c r="E91" s="1" t="s">
         <v>198</v>
       </c>
+      <c r="E91" s="1">
+        <v>1</v>
+      </c>
       <c r="F91" t="s">
-        <v>16</v>
+        <v>52</v>
+      </c>
+      <c r="G91" t="s">
+        <v>17</v>
       </c>
       <c r="I91" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="J91" s="2">
-        <v>46334.958333333336</v>
+        <v>46335.25</v>
       </c>
       <c r="K91" s="2">
-        <v>46337.708333333336</v>
+        <v>46335.75</v>
       </c>
       <c r="L91" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4234,31 +4231,31 @@
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="C92" t="s">
         <v>14</v>
       </c>
       <c r="D92" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E92" s="1">
         <v>1</v>
       </c>
       <c r="F92" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G92" t="s">
         <v>17</v>
       </c>
       <c r="I92" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J92" s="2">
-        <v>46335.25</v>
+        <v>46335.791666666664</v>
       </c>
       <c r="K92" s="2">
-        <v>46335.75</v>
+        <v>46336.75</v>
       </c>
       <c r="L92" t="s">
         <v>19</v>
@@ -4269,34 +4266,31 @@
         <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="C93" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D93" t="s">
         <v>199</v>
       </c>
-      <c r="E93" s="1">
-        <v>1</v>
+      <c r="E93" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="F93" t="s">
-        <v>55</v>
-      </c>
-      <c r="G93" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I93" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J93" s="2">
-        <v>46335.791666666664</v>
+        <v>46337</v>
       </c>
       <c r="K93" s="2">
-        <v>46336.75</v>
+        <v>46339</v>
       </c>
       <c r="L93" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -4304,48 +4298,48 @@
         <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C94" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="D94" t="s">
-        <v>200</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>201</v>
+        <v>45</v>
       </c>
       <c r="F94" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="I94" t="s">
         <v>18</v>
       </c>
       <c r="J94" s="2">
-        <v>46337</v>
+        <v>46337.333333333336</v>
       </c>
       <c r="K94" s="2">
-        <v>46339</v>
+        <v>46337.833333333336</v>
       </c>
       <c r="L94" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B95" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C95" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D95" t="s">
-        <v>46</v>
+        <v>201</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="F95" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="I95" t="s">
         <v>18</v>
@@ -4354,42 +4348,39 @@
         <v>46337.333333333336</v>
       </c>
       <c r="K95" s="2">
-        <v>46337.833333333336</v>
+        <v>46339.333333333336</v>
       </c>
       <c r="L95" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="C96" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="D96" t="s">
-        <v>202</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>203</v>
+        <v>56</v>
       </c>
       <c r="F96" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="I96" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="J96" s="2">
-        <v>46337.333333333336</v>
+        <v>46337.625</v>
       </c>
       <c r="K96" s="2">
-        <v>46339.333333333336</v>
+        <v>46338.125</v>
       </c>
       <c r="L96" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -4397,124 +4388,127 @@
         <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="C97" t="s">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="D97" t="s">
-        <v>58</v>
+        <v>203</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>204</v>
       </c>
       <c r="F97" t="s">
-        <v>59</v>
+        <v>16</v>
+      </c>
+      <c r="G97" t="s">
+        <v>17</v>
       </c>
       <c r="I97" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="J97" s="2">
-        <v>46337.625</v>
+        <v>46338.25</v>
       </c>
       <c r="K97" s="2">
-        <v>46338.125</v>
+        <v>46338.75</v>
       </c>
       <c r="L97" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B98" t="s">
-        <v>114</v>
+        <v>67</v>
       </c>
       <c r="C98" t="s">
-        <v>14</v>
+        <v>136</v>
       </c>
       <c r="D98" t="s">
-        <v>204</v>
-      </c>
-      <c r="E98" s="1" t="s">
         <v>205</v>
       </c>
       <c r="F98" t="s">
-        <v>16</v>
-      </c>
-      <c r="G98" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="I98" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J98" s="2">
-        <v>46338.25</v>
+        <v>46338.431250000001</v>
       </c>
       <c r="K98" s="2">
-        <v>46338.75</v>
+        <v>46339.472916666666</v>
       </c>
       <c r="L98" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B99" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="C99" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="D99" t="s">
         <v>206</v>
       </c>
+      <c r="E99" s="1" t="s">
+        <v>207</v>
+      </c>
       <c r="F99" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="I99" t="s">
         <v>18</v>
       </c>
       <c r="J99" s="2">
-        <v>46338.431250000001</v>
+        <v>46338.709027777775</v>
       </c>
       <c r="K99" s="2">
-        <v>46339.472916666666</v>
+        <v>46339.584027777775</v>
       </c>
       <c r="L99" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
+        <v>12</v>
+      </c>
+      <c r="B100" t="s">
         <v>27</v>
       </c>
-      <c r="B100" t="s">
+      <c r="C100" t="s">
         <v>28</v>
       </c>
-      <c r="C100" t="s">
-        <v>153</v>
-      </c>
       <c r="D100" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F100" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I100" t="s">
         <v>18</v>
       </c>
       <c r="J100" s="2">
-        <v>46338.709027777775</v>
+        <v>46338.958333333336</v>
       </c>
       <c r="K100" s="2">
-        <v>46339.584027777775</v>
+        <v>46342.208333333336</v>
       </c>
       <c r="L100" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="101" spans="1:12">
@@ -4522,19 +4516,19 @@
         <v>12</v>
       </c>
       <c r="B101" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C101" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D101" t="s">
+        <v>208</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E101" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="F101" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I101" t="s">
         <v>18</v>
@@ -4546,91 +4540,91 @@
         <v>46342.208333333336</v>
       </c>
       <c r="L101" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B102" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="C102" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="D102" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F102" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="I102" t="s">
         <v>18</v>
       </c>
       <c r="J102" s="2">
-        <v>46338.958333333336</v>
+        <v>46339.083333333336</v>
       </c>
       <c r="K102" s="2">
-        <v>46342.208333333336</v>
+        <v>46340.291666666664</v>
       </c>
       <c r="L102" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B103" t="s">
+        <v>67</v>
+      </c>
+      <c r="C103" t="s">
         <v>68</v>
       </c>
-      <c r="C103" t="s">
-        <v>103</v>
-      </c>
       <c r="D103" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F103" t="s">
-        <v>147</v>
+        <v>71</v>
       </c>
       <c r="I103" t="s">
         <v>18</v>
       </c>
       <c r="J103" s="2">
-        <v>46339.083333333336</v>
+        <v>46339.291666666664</v>
       </c>
       <c r="K103" s="2">
-        <v>46340.291666666664</v>
+        <v>46340.666666666664</v>
       </c>
       <c r="L103" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B104" t="s">
+        <v>67</v>
+      </c>
+      <c r="C104" t="s">
         <v>68</v>
       </c>
-      <c r="C104" t="s">
-        <v>69</v>
-      </c>
       <c r="D104" t="s">
+        <v>212</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E104" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="F104" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I104" t="s">
         <v>18</v>
@@ -4642,39 +4636,36 @@
         <v>46340.666666666664</v>
       </c>
       <c r="L104" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="C105" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D105" t="s">
-        <v>213</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="F105" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="I105" t="s">
         <v>18</v>
       </c>
       <c r="J105" s="2">
-        <v>46339.291666666664</v>
+        <v>46339.541666666664</v>
       </c>
       <c r="K105" s="2">
-        <v>46340.666666666664</v>
+        <v>46340.041666666664</v>
       </c>
       <c r="L105" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106" spans="1:12">
@@ -4682,57 +4673,28 @@
         <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C106" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="D106" t="s">
         <v>83</v>
       </c>
       <c r="F106" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="I106" t="s">
         <v>18</v>
       </c>
       <c r="J106" s="2">
-        <v>46339.541666666664</v>
+        <v>46339.704861111109</v>
       </c>
       <c r="K106" s="2">
-        <v>46340.041666666664</v>
+        <v>46340.204861111109</v>
       </c>
       <c r="L106" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12">
-      <c r="A107" t="s">
-        <v>12</v>
-      </c>
-      <c r="B107" t="s">
-        <v>44</v>
-      </c>
-      <c r="C107" t="s">
-        <v>45</v>
-      </c>
-      <c r="D107" t="s">
-        <v>84</v>
-      </c>
-      <c r="F107" t="s">
-        <v>48</v>
-      </c>
-      <c r="I107" t="s">
-        <v>18</v>
-      </c>
-      <c r="J107" s="2">
-        <v>46339.704861111109</v>
-      </c>
-      <c r="K107" s="2">
-        <v>46340.204861111109</v>
-      </c>
-      <c r="L107" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -4744,29 +4706,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
-  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
-</scriptIds>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -4904,18 +4849,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
+  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
+</scriptIds>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
 </file>
--- a/data/vessels/2026-10-21.xlsx
+++ b/data/vessels/2026-10-21.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30611"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="445003" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E21A9FED-EEB7-43D3-BCAB-AEB29C44F485}"/>
+  <xr:revisionPtr revIDLastSave="445454" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{861725EE-4CC3-49BC-94B7-0800DED93175}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="210">
   <si>
     <t>Harbor</t>
   </si>
@@ -101,348 +101,336 @@
     <t>Not available</t>
   </si>
   <si>
+    <t>WUT</t>
+  </si>
+  <si>
+    <t>PN1</t>
+  </si>
+  <si>
+    <t>YM COSMOS</t>
+  </si>
+  <si>
+    <t>PN12639W</t>
+  </si>
+  <si>
+    <t>Yang Ming</t>
+  </si>
+  <si>
+    <t>Inchcape</t>
+  </si>
+  <si>
+    <t>At berth</t>
+  </si>
+  <si>
+    <t>Seattle</t>
+  </si>
+  <si>
+    <t>T5</t>
+  </si>
+  <si>
+    <t>Chinook</t>
+  </si>
+  <si>
+    <t>MSC DENISSE X</t>
+  </si>
+  <si>
+    <t>UK641R</t>
+  </si>
+  <si>
+    <t>MSC</t>
+  </si>
+  <si>
+    <t>WC4/TP5</t>
+  </si>
+  <si>
+    <t>VIENNA EXPRESS</t>
+  </si>
+  <si>
+    <t>638E/641W</t>
+  </si>
+  <si>
+    <t>Hapag-Lloyd</t>
+  </si>
+  <si>
+    <t>EB1</t>
+  </si>
+  <si>
+    <t>MODERN LINK</t>
+  </si>
+  <si>
+    <t>Hyundai Glovis</t>
+  </si>
+  <si>
+    <t>Car Carrier</t>
+  </si>
+  <si>
+    <t>TOTE</t>
+  </si>
+  <si>
+    <t>Tote - AK1</t>
+  </si>
+  <si>
+    <t>MIDNIGHT SUN</t>
+  </si>
+  <si>
+    <t>Tote</t>
+  </si>
+  <si>
+    <t>Tote Maritime Alaska Inc</t>
+  </si>
+  <si>
+    <t>Multipurpose</t>
+  </si>
+  <si>
+    <t>In transit</t>
+  </si>
+  <si>
     <t>PCT</t>
   </si>
   <si>
+    <t>EVER MACH</t>
+  </si>
+  <si>
+    <t>018W</t>
+  </si>
+  <si>
+    <t>Evergreen</t>
+  </si>
+  <si>
+    <t>BEN LINE</t>
+  </si>
+  <si>
+    <t>T7</t>
+  </si>
+  <si>
+    <t>ARC INDEPENDENCE</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>R.J. PFEIFFER</t>
+  </si>
+  <si>
+    <t>Matson</t>
+  </si>
+  <si>
+    <t>SSA Marine</t>
+  </si>
+  <si>
+    <t>T18</t>
+  </si>
+  <si>
+    <t>PNW1</t>
+  </si>
+  <si>
+    <t>OOCL SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>199E/199W</t>
+  </si>
+  <si>
+    <t>OOCL</t>
+  </si>
+  <si>
+    <t>ARC ENDEAVOR</t>
+  </si>
+  <si>
+    <t>A6180</t>
+  </si>
+  <si>
+    <t>Wallenius</t>
+  </si>
+  <si>
+    <t>Ports America Group/Pct</t>
+  </si>
+  <si>
+    <t>Matson - HI2</t>
+  </si>
+  <si>
+    <t>MAUNAWILI</t>
+  </si>
+  <si>
+    <t>642S</t>
+  </si>
+  <si>
+    <t>CARNATION ACE</t>
+  </si>
+  <si>
+    <t>107A</t>
+  </si>
+  <si>
+    <t>Tote - AK2</t>
+  </si>
+  <si>
+    <t>NORTH STAR</t>
+  </si>
+  <si>
+    <t>Matson - AK</t>
+  </si>
+  <si>
+    <t>RJ PFEIFFER</t>
+  </si>
+  <si>
+    <t>KW664</t>
+  </si>
+  <si>
+    <t>EB Service 1</t>
+  </si>
+  <si>
+    <t>WESTWOOD RAINIER</t>
+  </si>
+  <si>
+    <t>159E/160W</t>
+  </si>
+  <si>
+    <t>Swire</t>
+  </si>
+  <si>
+    <t>Talon Marine Services LLC</t>
+  </si>
+  <si>
+    <t>FP2</t>
+  </si>
+  <si>
+    <t>YM TUTORIAL</t>
+  </si>
+  <si>
+    <t>ARC HONOR</t>
+  </si>
+  <si>
+    <t>ED616</t>
+  </si>
+  <si>
+    <t>PN3</t>
+  </si>
+  <si>
+    <t>YM WEALTH</t>
+  </si>
+  <si>
+    <t>PN32637W</t>
+  </si>
+  <si>
+    <t>CPNW</t>
+  </si>
+  <si>
+    <t>CMA CGM FORT JAMES</t>
+  </si>
+  <si>
+    <t>CPN04/CPN05</t>
+  </si>
+  <si>
+    <t>CMA CGM</t>
+  </si>
+  <si>
+    <t>CPV</t>
+  </si>
+  <si>
+    <t>COSCO VENICE</t>
+  </si>
+  <si>
+    <t>081N/081S</t>
+  </si>
+  <si>
+    <t>COSCO</t>
+  </si>
+  <si>
+    <t>COSCO SHIPPING LINES</t>
+  </si>
+  <si>
+    <t>POLARIS MILA</t>
+  </si>
+  <si>
+    <t>YM PLUM</t>
+  </si>
+  <si>
+    <t>198E</t>
+  </si>
+  <si>
     <t>TPN</t>
   </si>
   <si>
-    <t>EVER ELITE</t>
-  </si>
-  <si>
-    <t>186W</t>
-  </si>
-  <si>
-    <t>Evergreen</t>
-  </si>
-  <si>
-    <t>BEN LINES</t>
-  </si>
-  <si>
-    <t>At berth</t>
-  </si>
-  <si>
-    <t>WUT</t>
-  </si>
-  <si>
-    <t>PN1</t>
-  </si>
-  <si>
-    <t>YM COSMOS</t>
-  </si>
-  <si>
-    <t>PN12639W</t>
-  </si>
-  <si>
-    <t>Yang Ming</t>
-  </si>
-  <si>
-    <t>Inchcape</t>
-  </si>
-  <si>
-    <t>Seattle</t>
-  </si>
-  <si>
-    <t>T5</t>
-  </si>
-  <si>
-    <t>Chinook</t>
-  </si>
-  <si>
-    <t>MSC DENISSE X</t>
-  </si>
-  <si>
-    <t>UK641R</t>
-  </si>
-  <si>
-    <t>MSC</t>
-  </si>
-  <si>
-    <t>WC4/TP5</t>
-  </si>
-  <si>
-    <t>VIENNA EXPRESS</t>
-  </si>
-  <si>
-    <t>638E/641W</t>
-  </si>
-  <si>
-    <t>Hapag-Lloyd</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>Matson - AK</t>
+    <t>EVER SALUTE</t>
+  </si>
+  <si>
+    <t>129W</t>
+  </si>
+  <si>
+    <t>ACGI</t>
+  </si>
+  <si>
+    <t>Everport Terminal Services</t>
+  </si>
+  <si>
+    <t>LIBERTY PEACE</t>
+  </si>
+  <si>
+    <t>086S</t>
+  </si>
+  <si>
+    <t>Liberty</t>
+  </si>
+  <si>
+    <t>Pacific Terminals</t>
+  </si>
+  <si>
+    <t>FRANKFURT EXPRESS</t>
+  </si>
+  <si>
+    <t>640E/643W</t>
+  </si>
+  <si>
+    <t>Blair</t>
+  </si>
+  <si>
+    <t>LIBERTY PASSION</t>
+  </si>
+  <si>
+    <t>MATSON KODIAK</t>
+  </si>
+  <si>
+    <t>PATARA</t>
+  </si>
+  <si>
+    <t>005A</t>
+  </si>
+  <si>
+    <t>SM PORTLAND</t>
+  </si>
+  <si>
+    <t>2607E/2607W</t>
+  </si>
+  <si>
+    <t>SM Line</t>
+  </si>
+  <si>
+    <t>MSC IVANA</t>
+  </si>
+  <si>
+    <t>UK642R</t>
+  </si>
+  <si>
+    <t>ONE DURBAN</t>
+  </si>
+  <si>
+    <t>PN32639E</t>
+  </si>
+  <si>
+    <t>Oceania</t>
+  </si>
+  <si>
+    <t>CMA CGM DUTCH HARBOR</t>
+  </si>
+  <si>
+    <t>0Y1N2/0T1N3</t>
   </si>
   <si>
     <t>MATSON ANCHORAGE</t>
   </si>
   <si>
-    <t>643S</t>
-  </si>
-  <si>
-    <t>Matson</t>
-  </si>
-  <si>
-    <t>SSA Marine</t>
-  </si>
-  <si>
-    <t>In transit</t>
-  </si>
-  <si>
-    <t>EB1</t>
-  </si>
-  <si>
-    <t>MODERN LINK</t>
-  </si>
-  <si>
-    <t>Hyundai Glovis</t>
-  </si>
-  <si>
-    <t>Car Carrier</t>
-  </si>
-  <si>
-    <t>TOTE</t>
-  </si>
-  <si>
-    <t>Tote - AK1</t>
-  </si>
-  <si>
-    <t>MIDNIGHT SUN</t>
-  </si>
-  <si>
-    <t>Tote</t>
-  </si>
-  <si>
-    <t>Tote Maritime Alaska Inc</t>
-  </si>
-  <si>
-    <t>Multipurpose</t>
-  </si>
-  <si>
-    <t>EVER MACH</t>
-  </si>
-  <si>
-    <t>018W</t>
-  </si>
-  <si>
-    <t>BEN LINE</t>
-  </si>
-  <si>
-    <t>T7</t>
-  </si>
-  <si>
-    <t>ARC INDEPENDENCE</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>R.J. PFEIFFER</t>
-  </si>
-  <si>
-    <t>T18</t>
-  </si>
-  <si>
-    <t>PNW1</t>
-  </si>
-  <si>
-    <t>OOCL SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>199E/199W</t>
-  </si>
-  <si>
-    <t>OOCL</t>
-  </si>
-  <si>
-    <t>ARC ENDEAVOR</t>
-  </si>
-  <si>
-    <t>A6180</t>
-  </si>
-  <si>
-    <t>Wallenius</t>
-  </si>
-  <si>
-    <t>Ports America Group/Pct</t>
-  </si>
-  <si>
-    <t>Matson - HI2</t>
-  </si>
-  <si>
-    <t>MAUNAWILI</t>
-  </si>
-  <si>
-    <t>642S</t>
-  </si>
-  <si>
-    <t>CARNATION ACE</t>
-  </si>
-  <si>
-    <t>107A</t>
-  </si>
-  <si>
-    <t>Tote - AK2</t>
-  </si>
-  <si>
-    <t>NORTH STAR</t>
-  </si>
-  <si>
-    <t>RJ PFEIFFER</t>
-  </si>
-  <si>
-    <t>KW664</t>
-  </si>
-  <si>
-    <t>EB Service 1</t>
-  </si>
-  <si>
-    <t>WESTWOOD RAINIER</t>
-  </si>
-  <si>
-    <t>159E/160W</t>
-  </si>
-  <si>
-    <t>Swire</t>
-  </si>
-  <si>
-    <t>Talon Marine Services LLC</t>
-  </si>
-  <si>
-    <t>FP2</t>
-  </si>
-  <si>
-    <t>YM TUTORIAL</t>
-  </si>
-  <si>
-    <t>ARC HONOR</t>
-  </si>
-  <si>
-    <t>ED616</t>
-  </si>
-  <si>
-    <t>PN3</t>
-  </si>
-  <si>
-    <t>YM WEALTH</t>
-  </si>
-  <si>
-    <t>PN32637W</t>
-  </si>
-  <si>
-    <t>POLARIS MILA</t>
-  </si>
-  <si>
-    <t>CPNW</t>
-  </si>
-  <si>
-    <t>CMA CGM FORT JAMES</t>
-  </si>
-  <si>
-    <t>CPN04/CPN05</t>
-  </si>
-  <si>
-    <t>CMA CGM</t>
-  </si>
-  <si>
-    <t>CPV</t>
-  </si>
-  <si>
-    <t>COSCO VENICE</t>
-  </si>
-  <si>
-    <t>081N/081S</t>
-  </si>
-  <si>
-    <t>COSCO</t>
-  </si>
-  <si>
-    <t>COSCO SHIPPING LINES</t>
-  </si>
-  <si>
-    <t>YM PLUM</t>
-  </si>
-  <si>
-    <t>198E</t>
-  </si>
-  <si>
-    <t>EVER SALUTE</t>
-  </si>
-  <si>
-    <t>129W</t>
-  </si>
-  <si>
-    <t>ACGI</t>
-  </si>
-  <si>
-    <t>Everport Terminal Services</t>
-  </si>
-  <si>
-    <t>Blair</t>
-  </si>
-  <si>
-    <t>LIBERTY PASSION</t>
-  </si>
-  <si>
-    <t>Liberty</t>
-  </si>
-  <si>
-    <t>Pacific Terminals</t>
-  </si>
-  <si>
-    <t>LIBERTY PEACE</t>
-  </si>
-  <si>
-    <t>086S</t>
-  </si>
-  <si>
-    <t>FRANKFURT EXPRESS</t>
-  </si>
-  <si>
-    <t>640E/643W</t>
-  </si>
-  <si>
-    <t>MATSON KODIAK</t>
-  </si>
-  <si>
-    <t>PATARA</t>
-  </si>
-  <si>
-    <t>005A</t>
-  </si>
-  <si>
-    <t>SM PORTLAND</t>
-  </si>
-  <si>
-    <t>2607E/2607W</t>
-  </si>
-  <si>
-    <t>SM Line</t>
-  </si>
-  <si>
-    <t>MSC IVANA</t>
-  </si>
-  <si>
-    <t>UK642R</t>
-  </si>
-  <si>
-    <t>Oceania</t>
-  </si>
-  <si>
-    <t>CMA CGM DUTCH HARBOR</t>
-  </si>
-  <si>
-    <t>0Y1N2/0T1N3</t>
-  </si>
-  <si>
-    <t>ONE DURBAN</t>
-  </si>
-  <si>
-    <t>PN32639E</t>
-  </si>
-  <si>
     <t>EVER MODE</t>
   </si>
   <si>
@@ -488,15 +476,15 @@
     <t>285A</t>
   </si>
   <si>
+    <t>ONE SYNERGY</t>
+  </si>
+  <si>
     <t>MSC SOLA</t>
   </si>
   <si>
     <t>UK643R</t>
   </si>
   <si>
-    <t>ONE SYNERGY</t>
-  </si>
-  <si>
     <t>CLX</t>
   </si>
   <si>
@@ -536,36 +524,42 @@
     <t>FP22633B</t>
   </si>
   <si>
+    <t>MSC FLORA</t>
+  </si>
+  <si>
+    <t>MC644R</t>
+  </si>
+  <si>
+    <t>BUDAPEST EXPRESS</t>
+  </si>
+  <si>
+    <t>641E</t>
+  </si>
+  <si>
+    <t>TONGALA</t>
+  </si>
+  <si>
+    <t>KW666</t>
+  </si>
+  <si>
+    <t>Jones Stevedoring Co</t>
+  </si>
+  <si>
+    <t>GLOVIS TREASURE</t>
+  </si>
+  <si>
+    <t>MSC SABRINA</t>
+  </si>
+  <si>
+    <t>MC645R</t>
+  </si>
+  <si>
     <t>MSC YUKTA X</t>
   </si>
   <si>
     <t>UK644R</t>
   </si>
   <si>
-    <t>BUDAPEST EXPRESS</t>
-  </si>
-  <si>
-    <t>641E</t>
-  </si>
-  <si>
-    <t>TONGALA</t>
-  </si>
-  <si>
-    <t>KW666</t>
-  </si>
-  <si>
-    <t>Jones Stevedoring Co</t>
-  </si>
-  <si>
-    <t>GLOVIS TREASURE</t>
-  </si>
-  <si>
-    <t>MSC SABRINA</t>
-  </si>
-  <si>
-    <t>MC645R</t>
-  </si>
-  <si>
     <t>CORNEILLE</t>
   </si>
   <si>
@@ -582,12 +576,6 @@
   </si>
   <si>
     <t>KW665</t>
-  </si>
-  <si>
-    <t>MSC FLORA</t>
-  </si>
-  <si>
-    <t>MC644R</t>
   </si>
   <si>
     <t>SM MUMBAI</t>
@@ -753,10 +741,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L106" totalsRowShown="0">
-  <autoFilter ref="A1:L106" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L106">
-    <sortCondition ref="J2:J106"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L104" totalsRowShown="0">
+  <autoFilter ref="A1:L104" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L104">
+    <sortCondition ref="J2:J104"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1093,7 +1081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L106"/>
+  <dimension ref="A1:L104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1174,7 +1162,7 @@
         <v>46314.625</v>
       </c>
       <c r="K2" s="2">
-        <v>46319.166666666664</v>
+        <v>46319.125</v>
       </c>
       <c r="L2" t="s">
         <v>19</v>
@@ -1206,10 +1194,10 @@
         <v>18</v>
       </c>
       <c r="J3" s="2">
-        <v>46315.208333333336</v>
+        <v>46315.666666666664</v>
       </c>
       <c r="K3" s="2">
-        <v>46316.791666666664</v>
+        <v>46317.75</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -1217,25 +1205,25 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="I4" t="s">
         <v>18</v>
@@ -1244,7 +1232,7 @@
         <v>46315.666666666664</v>
       </c>
       <c r="K4" s="2">
-        <v>46317.75</v>
+        <v>46317.375</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -1252,22 +1240,22 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
         <v>33</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
         <v>34</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>36</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" t="s">
-        <v>38</v>
       </c>
       <c r="G5" t="s">
         <v>17</v>
@@ -1276,10 +1264,10 @@
         <v>18</v>
       </c>
       <c r="J5" s="2">
-        <v>46315.666666666664</v>
+        <v>46315.916666666664</v>
       </c>
       <c r="K5" s="2">
-        <v>46317.166666666664</v>
+        <v>46322.166666666664</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -1293,16 +1281,16 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F6" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G6" t="s">
         <v>17</v>
@@ -1325,34 +1313,34 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2</v>
+      </c>
+      <c r="F7" t="s">
         <v>39</v>
-      </c>
-      <c r="D7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" t="s">
-        <v>42</v>
       </c>
       <c r="G7" t="s">
         <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J7" s="2">
-        <v>46315.916666666664</v>
+        <v>46316.520833333336</v>
       </c>
       <c r="K7" s="2">
-        <v>46322.166666666664</v>
+        <v>46317.166666666664</v>
       </c>
       <c r="L7" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1360,37 +1348,37 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
         <v>43</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" s="1">
+        <v>26169</v>
+      </c>
+      <c r="F8" t="s">
         <v>44</v>
       </c>
-      <c r="D8" t="s">
+      <c r="G8" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="H8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" t="s">
         <v>46</v>
       </c>
-      <c r="F8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I8" t="s">
-        <v>18</v>
-      </c>
       <c r="J8" s="2">
-        <v>46316.125</v>
+        <v>46316.625</v>
       </c>
       <c r="K8" s="2">
-        <v>46316.916666666664</v>
+        <v>46317.041666666664</v>
       </c>
       <c r="L8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1398,34 +1386,31 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="1">
-        <v>2</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>52</v>
       </c>
-      <c r="G9" t="s">
-        <v>17</v>
-      </c>
       <c r="I9" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J9" s="2">
-        <v>46316.520833333336</v>
+        <v>46317.208333333336</v>
       </c>
       <c r="K9" s="2">
-        <v>46317.166666666664</v>
+        <v>46318.708333333336</v>
       </c>
       <c r="L9" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1433,37 +1418,34 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s">
         <v>54</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
         <v>55</v>
       </c>
-      <c r="D10" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" s="1">
-        <v>26169</v>
-      </c>
-      <c r="F10" t="s">
-        <v>57</v>
-      </c>
       <c r="G10" t="s">
-        <v>58</v>
-      </c>
-      <c r="H10" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="I10" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="J10" s="2">
-        <v>46316.625</v>
+        <v>46317.875</v>
       </c>
       <c r="K10" s="2">
-        <v>46317.041666666664</v>
+        <v>46321.75</v>
       </c>
       <c r="L10" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1471,31 +1453,34 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>53</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>61</v>
+        <v>54</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="G11" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="I11" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J11" s="2">
-        <v>46317.208333333336</v>
+        <v>46317.875</v>
       </c>
       <c r="K11" s="2">
-        <v>46318.708333333336</v>
+        <v>46321.75</v>
       </c>
       <c r="L11" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1503,31 +1488,31 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" s="1">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G12" t="s">
-        <v>17</v>
+        <v>58</v>
+      </c>
+      <c r="H12" t="s">
+        <v>59</v>
       </c>
       <c r="I12" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J12" s="2">
-        <v>46317.875</v>
+        <v>46318.125</v>
       </c>
       <c r="K12" s="2">
-        <v>46321.75</v>
+        <v>46318.916666666664</v>
       </c>
       <c r="L12" t="s">
         <v>19</v>
@@ -1535,37 +1520,40 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="F13" t="s">
         <v>64</v>
       </c>
-      <c r="E13" s="1">
-        <v>1</v>
-      </c>
-      <c r="F13" t="s">
-        <v>65</v>
-      </c>
       <c r="G13" t="s">
-        <v>17</v>
+        <v>25</v>
+      </c>
+      <c r="H13" t="s">
+        <v>59</v>
       </c>
       <c r="I13" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J13" s="2">
-        <v>46317.875</v>
+        <v>46318.25</v>
       </c>
       <c r="K13" s="2">
-        <v>46321.75</v>
+        <v>46319.166666666664</v>
       </c>
       <c r="L13" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1573,31 +1561,34 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
       </c>
       <c r="D14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>66</v>
       </c>
       <c r="F14" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="G14" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="H14" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="I14" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J14" s="2">
-        <v>46318.125</v>
+        <v>46318.291666666664</v>
       </c>
       <c r="K14" s="2">
-        <v>46318.916666666664</v>
+        <v>46318.791666666664</v>
       </c>
       <c r="L14" t="s">
         <v>19</v>
@@ -1605,40 +1596,40 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F15" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="G15" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="H15" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="I15" t="s">
         <v>18</v>
       </c>
       <c r="J15" s="2">
-        <v>46318.25</v>
+        <v>46318.416666666664</v>
       </c>
       <c r="K15" s="2">
-        <v>46319.166666666664</v>
+        <v>46319.125</v>
       </c>
       <c r="L15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1646,7 +1637,7 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
@@ -1658,22 +1649,19 @@
         <v>73</v>
       </c>
       <c r="F16" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="G16" t="s">
         <v>17</v>
       </c>
-      <c r="H16" t="s">
-        <v>75</v>
-      </c>
       <c r="I16" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="J16" s="2">
-        <v>46318.291666666664</v>
+        <v>46318.583333333336</v>
       </c>
       <c r="K16" s="2">
-        <v>46318.791666666664</v>
+        <v>46319.041666666664</v>
       </c>
       <c r="L16" t="s">
         <v>19</v>
@@ -1684,37 +1672,37 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D17" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
+      </c>
+      <c r="E17" s="1">
+        <v>26168</v>
       </c>
       <c r="F17" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H17" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I17" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="J17" s="2">
-        <v>46318.416666666664</v>
+        <v>46318.625</v>
       </c>
       <c r="K17" s="2">
-        <v>46319.125</v>
+        <v>46319.041666666664</v>
       </c>
       <c r="L17" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1722,34 +1710,31 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="I18" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J18" s="2">
-        <v>46318.583333333336</v>
+        <v>46318.704861111109</v>
       </c>
       <c r="K18" s="2">
-        <v>46319.041666666664</v>
+        <v>46319.204861111109</v>
       </c>
       <c r="L18" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1757,34 +1742,34 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
-      </c>
-      <c r="E19" s="1">
-        <v>26168</v>
+        <v>65</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="G19" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="H19" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="I19" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="J19" s="2">
-        <v>46318.625</v>
+        <v>46318.833333333336</v>
       </c>
       <c r="K19" s="2">
-        <v>46319.041666666664</v>
+        <v>46319.791666666664</v>
       </c>
       <c r="L19" t="s">
         <v>19</v>
@@ -1792,34 +1777,40 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F20" t="s">
+        <v>82</v>
+      </c>
+      <c r="G20" t="s">
         <v>83</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F20" t="s">
-        <v>47</v>
+      <c r="H20" t="s">
+        <v>59</v>
       </c>
       <c r="I20" t="s">
         <v>18</v>
       </c>
       <c r="J20" s="2">
-        <v>46318.704861111109</v>
+        <v>46318.916666666664</v>
       </c>
       <c r="K20" s="2">
-        <v>46319.204861111109</v>
+        <v>46320.083333333336</v>
       </c>
       <c r="L20" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1827,48 +1818,45 @@
         <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="D21" t="s">
-        <v>72</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="E21" s="1">
+        <v>21</v>
       </c>
       <c r="F21" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="G21" t="s">
         <v>17</v>
       </c>
-      <c r="H21" t="s">
-        <v>75</v>
-      </c>
       <c r="I21" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J21" s="2">
-        <v>46318.833333333336</v>
+        <v>46319.208333333336</v>
       </c>
       <c r="K21" s="2">
-        <v>46319.791666666664</v>
+        <v>46325.75</v>
       </c>
       <c r="L21" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s">
         <v>86</v>
@@ -1877,25 +1865,22 @@
         <v>87</v>
       </c>
       <c r="F22" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="G22" t="s">
-        <v>89</v>
-      </c>
-      <c r="H22" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I22" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J22" s="2">
-        <v>46318.916666666664</v>
+        <v>46319.25</v>
       </c>
       <c r="K22" s="2">
-        <v>46320.083333333336</v>
+        <v>46319.75</v>
       </c>
       <c r="L22" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1903,45 +1888,45 @@
         <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C23" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D23" t="s">
-        <v>91</v>
-      </c>
-      <c r="E23" s="1">
-        <v>21</v>
-      </c>
       <c r="F23" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G23" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I23" t="s">
         <v>18</v>
       </c>
       <c r="J23" s="2">
-        <v>46319.208333333336</v>
+        <v>46319.666666666664</v>
       </c>
       <c r="K23" s="2">
-        <v>46325.75</v>
+        <v>46321.75</v>
       </c>
       <c r="L23" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="D24" t="s">
         <v>92</v>
@@ -1950,57 +1935,57 @@
         <v>93</v>
       </c>
       <c r="F24" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="G24" t="s">
         <v>17</v>
       </c>
       <c r="I24" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J24" s="2">
-        <v>46319.25</v>
+        <v>46320.625</v>
       </c>
       <c r="K24" s="2">
-        <v>46319.75</v>
+        <v>46322.75</v>
       </c>
       <c r="L24" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F25" t="s">
-        <v>31</v>
+        <v>98</v>
       </c>
       <c r="G25" t="s">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="I25" t="s">
         <v>18</v>
       </c>
       <c r="J25" s="2">
-        <v>46319.666666666664</v>
+        <v>46321.208333333336</v>
       </c>
       <c r="K25" s="2">
-        <v>46321.75</v>
+        <v>46322.166666666664</v>
       </c>
       <c r="L25" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2008,31 +1993,31 @@
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C26" t="s">
         <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E26" s="1">
         <v>4</v>
       </c>
       <c r="F26" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="G26" t="s">
         <v>17</v>
       </c>
       <c r="I26" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="J26" s="2">
-        <v>46320.166666666664</v>
+        <v>46321.25</v>
       </c>
       <c r="K26" s="2">
-        <v>46320.75</v>
+        <v>46321.75</v>
       </c>
       <c r="L26" t="s">
         <v>19</v>
@@ -2040,72 +2025,75 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="C27" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="D27" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F27" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G27" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I27" t="s">
         <v>18</v>
       </c>
       <c r="J27" s="2">
-        <v>46320.625</v>
+        <v>46321.25</v>
       </c>
       <c r="K27" s="2">
-        <v>46322.75</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L27" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F28" t="s">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="G28" t="s">
         <v>106</v>
       </c>
+      <c r="H28" t="s">
+        <v>107</v>
+      </c>
       <c r="I28" t="s">
         <v>18</v>
       </c>
       <c r="J28" s="2">
-        <v>46321.208333333336</v>
+        <v>46322.208333333336</v>
       </c>
       <c r="K28" s="2">
-        <v>46322.166666666664</v>
+        <v>46324.791666666664</v>
       </c>
       <c r="L28" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -2113,34 +2101,37 @@
         <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C29" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F29" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="G29" t="s">
-        <v>32</v>
+        <v>25</v>
+      </c>
+      <c r="H29" t="s">
+        <v>111</v>
       </c>
       <c r="I29" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J29" s="2">
-        <v>46321.25</v>
+        <v>46322.25</v>
       </c>
       <c r="K29" s="2">
         <v>46323.166666666664</v>
       </c>
       <c r="L29" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2148,37 +2139,34 @@
         <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D30" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F30" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G30" t="s">
-        <v>111</v>
-      </c>
-      <c r="H30" t="s">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="I30" t="s">
         <v>18</v>
       </c>
       <c r="J30" s="2">
-        <v>46322.208333333336</v>
+        <v>46322.625</v>
       </c>
       <c r="K30" s="2">
-        <v>46324.791666666664</v>
+        <v>46325.75</v>
       </c>
       <c r="L30" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -2186,31 +2174,31 @@
         <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C31" t="s">
         <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F31" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G31" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H31" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="I31" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="J31" s="2">
-        <v>46322.25</v>
+        <v>46322.708333333336</v>
       </c>
       <c r="K31" s="2">
-        <v>46322.75</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L31" t="s">
         <v>19</v>
@@ -2221,37 +2209,34 @@
         <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="D32" t="s">
-        <v>117</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F32" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="G32" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="H32" t="s">
-        <v>116</v>
+        <v>59</v>
       </c>
       <c r="I32" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J32" s="2">
-        <v>46322.25</v>
+        <v>46323.104166666664</v>
       </c>
       <c r="K32" s="2">
-        <v>46323.166666666664</v>
+        <v>46323.916666666664</v>
       </c>
       <c r="L32" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -2259,69 +2244,69 @@
         <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F33" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="G33" t="s">
         <v>17</v>
       </c>
       <c r="I33" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J33" s="2">
-        <v>46322.625</v>
+        <v>46323.25</v>
       </c>
       <c r="K33" s="2">
-        <v>46325.75</v>
+        <v>46323.75</v>
       </c>
       <c r="L33" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D34" t="s">
+        <v>119</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F34" t="s">
         <v>121</v>
       </c>
-      <c r="F34" t="s">
-        <v>47</v>
-      </c>
       <c r="G34" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="H34" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="I34" t="s">
         <v>18</v>
       </c>
       <c r="J34" s="2">
-        <v>46323.104166666664</v>
+        <v>46323.25</v>
       </c>
       <c r="K34" s="2">
-        <v>46323.916666666664</v>
+        <v>46323.75</v>
       </c>
       <c r="L34" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2329,69 +2314,75 @@
         <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="C35" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D35" t="s">
-        <v>122</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>123</v>
+        <v>43</v>
+      </c>
+      <c r="E35" s="1">
+        <v>26173</v>
       </c>
       <c r="F35" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="G35" t="s">
-        <v>17</v>
+        <v>45</v>
+      </c>
+      <c r="H35" t="s">
+        <v>45</v>
       </c>
       <c r="I35" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="J35" s="2">
-        <v>46323.25</v>
+        <v>46323.625</v>
       </c>
       <c r="K35" s="2">
-        <v>46323.75</v>
+        <v>46324.041666666664</v>
       </c>
       <c r="L35" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>67</v>
+        <v>28</v>
+      </c>
+      <c r="C36" t="s">
+        <v>29</v>
       </c>
       <c r="D36" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F36" t="s">
-        <v>126</v>
+        <v>32</v>
       </c>
       <c r="G36" t="s">
         <v>17</v>
       </c>
       <c r="H36" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="I36" t="s">
         <v>18</v>
       </c>
       <c r="J36" s="2">
-        <v>46323.25</v>
+        <v>46323.708333333336</v>
       </c>
       <c r="K36" s="2">
-        <v>46323.75</v>
+        <v>46325.75</v>
       </c>
       <c r="L36" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -2399,148 +2390,136 @@
         <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="C37" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>56</v>
-      </c>
-      <c r="E37" s="1">
-        <v>26173</v>
+        <v>117</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="F37" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="G37" t="s">
-        <v>58</v>
-      </c>
-      <c r="H37" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="I37" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="J37" s="2">
-        <v>46323.625</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="K37" s="2">
-        <v>46324.041666666664</v>
+        <v>46324.75</v>
       </c>
       <c r="L37" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B38" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C38" t="s">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="D38" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F38" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="G38" t="s">
         <v>17</v>
       </c>
-      <c r="H38" t="s">
-        <v>48</v>
-      </c>
       <c r="I38" t="s">
         <v>18</v>
       </c>
       <c r="J38" s="2">
-        <v>46323.708333333336</v>
+        <v>46324.25</v>
       </c>
       <c r="K38" s="2">
-        <v>46325.166666666664</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="L38" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B39" t="s">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="C39" t="s">
-        <v>14</v>
+        <v>126</v>
       </c>
       <c r="D39" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F39" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G39" t="s">
         <v>17</v>
       </c>
+      <c r="H39" t="s">
+        <v>59</v>
+      </c>
       <c r="I39" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J39" s="2">
-        <v>46323.791666666664</v>
+        <v>46324.25</v>
       </c>
       <c r="K39" s="2">
-        <v>46324.75</v>
+        <v>46325.166666666664</v>
       </c>
       <c r="L39" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C40" t="s">
+        <v>76</v>
+      </c>
+      <c r="D40" t="s">
         <v>129</v>
       </c>
-      <c r="D40" t="s">
-        <v>130</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="F40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G40" t="s">
-        <v>17</v>
-      </c>
-      <c r="H40" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="I40" t="s">
         <v>18</v>
       </c>
       <c r="J40" s="2">
-        <v>46324.25</v>
+        <v>46325.333333333336</v>
       </c>
       <c r="K40" s="2">
-        <v>46325.166666666664</v>
+        <v>46325.833333333336</v>
       </c>
       <c r="L40" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2548,34 +2527,37 @@
         <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C41" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="D41" t="s">
-        <v>132</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>133</v>
+        <v>75</v>
+      </c>
+      <c r="E41" s="1">
+        <v>26172</v>
       </c>
       <c r="F41" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="G41" t="s">
-        <v>17</v>
+        <v>45</v>
+      </c>
+      <c r="H41" t="s">
+        <v>45</v>
       </c>
       <c r="I41" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="J41" s="2">
-        <v>46324.25</v>
+        <v>46325.625</v>
       </c>
       <c r="K41" s="2">
-        <v>46326.166666666664</v>
+        <v>46326.041666666664</v>
       </c>
       <c r="L41" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2583,28 +2565,31 @@
         <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>43</v>
-      </c>
-      <c r="C42" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D42" t="s">
-        <v>45</v>
+        <v>130</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="F42" t="s">
-        <v>47</v>
+        <v>51</v>
+      </c>
+      <c r="G42" t="s">
+        <v>52</v>
       </c>
       <c r="I42" t="s">
         <v>18</v>
       </c>
       <c r="J42" s="2">
-        <v>46325.333333333336</v>
+        <v>46325.708333333336</v>
       </c>
       <c r="K42" s="2">
-        <v>46325.833333333336</v>
+        <v>46327.208333333336</v>
       </c>
       <c r="L42" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -2612,69 +2597,66 @@
         <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>54</v>
-      </c>
-      <c r="C43" t="s">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="D43" t="s">
-        <v>82</v>
-      </c>
-      <c r="E43" s="1">
-        <v>26172</v>
+        <v>130</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="F43" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G43" t="s">
-        <v>58</v>
-      </c>
-      <c r="H43" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="I43" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="J43" s="2">
-        <v>46325.625</v>
+        <v>46325.708333333336</v>
       </c>
       <c r="K43" s="2">
-        <v>46326.041666666664</v>
+        <v>46327.208333333336</v>
       </c>
       <c r="L43" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B44" t="s">
-        <v>20</v>
+        <v>60</v>
+      </c>
+      <c r="C44" t="s">
+        <v>132</v>
       </c>
       <c r="D44" t="s">
+        <v>133</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="F44" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="G44" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="I44" t="s">
         <v>18</v>
       </c>
       <c r="J44" s="2">
-        <v>46325.708333333336</v>
+        <v>46325.958333333336</v>
       </c>
       <c r="K44" s="2">
-        <v>46327.208333333336</v>
+        <v>46327.416666666664</v>
       </c>
       <c r="L44" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2682,101 +2664,98 @@
         <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>20</v>
+        <v>114</v>
+      </c>
+      <c r="C45" t="s">
+        <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F45" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G45" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="I45" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J45" s="2">
-        <v>46325.708333333336</v>
+        <v>46326.25</v>
       </c>
       <c r="K45" s="2">
-        <v>46327.208333333336</v>
+        <v>46326.75</v>
       </c>
       <c r="L45" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C46" t="s">
-        <v>136</v>
+        <v>69</v>
       </c>
       <c r="D46" t="s">
         <v>137</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="F46" t="s">
-        <v>88</v>
-      </c>
-      <c r="G46" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="I46" t="s">
         <v>18</v>
       </c>
       <c r="J46" s="2">
-        <v>46325.958333333336</v>
+        <v>46326.416666666664</v>
       </c>
       <c r="K46" s="2">
-        <v>46327.416666666664</v>
+        <v>46326.75</v>
       </c>
       <c r="L46" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B47" t="s">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="C47" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="D47" t="s">
+        <v>138</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="F47" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G47" t="s">
         <v>17</v>
       </c>
       <c r="I47" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J47" s="2">
-        <v>46326.25</v>
+        <v>46326.625</v>
       </c>
       <c r="K47" s="2">
-        <v>46326.75</v>
+        <v>46328.75</v>
       </c>
       <c r="L47" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2784,63 +2763,66 @@
         <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="C48" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="D48" t="s">
+        <v>140</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>141</v>
       </c>
       <c r="F48" t="s">
-        <v>47</v>
+        <v>142</v>
       </c>
       <c r="I48" t="s">
         <v>18</v>
       </c>
       <c r="J48" s="2">
-        <v>46326.416666666664</v>
+        <v>46326.833333333336</v>
       </c>
       <c r="K48" s="2">
-        <v>46326.75</v>
+        <v>46329.583333333336</v>
       </c>
       <c r="L48" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="C49" t="s">
-        <v>98</v>
+        <v>14</v>
       </c>
       <c r="D49" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F49" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="G49" t="s">
         <v>17</v>
       </c>
       <c r="I49" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J49" s="2">
-        <v>46326.625</v>
+        <v>46327.25</v>
       </c>
       <c r="K49" s="2">
-        <v>46328.75</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="L49" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -2848,77 +2830,80 @@
         <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C50" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D50" t="s">
-        <v>144</v>
-      </c>
-      <c r="E50" s="1" t="s">
         <v>145</v>
       </c>
+      <c r="E50" s="1">
+        <v>2</v>
+      </c>
       <c r="F50" t="s">
-        <v>146</v>
+        <v>16</v>
+      </c>
+      <c r="G50" t="s">
+        <v>17</v>
       </c>
       <c r="I50" t="s">
         <v>18</v>
       </c>
       <c r="J50" s="2">
-        <v>46326.833333333336</v>
+        <v>46327.625</v>
       </c>
       <c r="K50" s="2">
-        <v>46329.583333333336</v>
+        <v>46331.75</v>
       </c>
       <c r="L50" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B51" t="s">
-        <v>113</v>
+        <v>28</v>
       </c>
       <c r="C51" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D51" t="s">
+        <v>146</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="F51" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G51" t="s">
         <v>17</v>
       </c>
       <c r="I51" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J51" s="2">
-        <v>46327.25</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K51" s="2">
-        <v>46327.708333333336</v>
+        <v>46329.75</v>
       </c>
       <c r="L51" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B52" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C52" t="s">
-        <v>35</v>
+        <v>148</v>
       </c>
       <c r="D52" t="s">
         <v>149</v>
@@ -2927,7 +2912,7 @@
         <v>150</v>
       </c>
       <c r="F52" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G52" t="s">
         <v>17</v>
@@ -2936,13 +2921,13 @@
         <v>18</v>
       </c>
       <c r="J52" s="2">
-        <v>46327.291666666664</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K52" s="2">
-        <v>46329.166666666664</v>
+        <v>46328.75</v>
       </c>
       <c r="L52" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -2950,45 +2935,39 @@
         <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C53" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="D53" t="s">
         <v>151</v>
       </c>
-      <c r="E53" s="1">
-        <v>2</v>
+      <c r="E53" s="1" t="s">
+        <v>152</v>
       </c>
       <c r="F53" t="s">
         <v>16</v>
       </c>
-      <c r="G53" t="s">
-        <v>17</v>
-      </c>
       <c r="I53" t="s">
         <v>18</v>
       </c>
       <c r="J53" s="2">
-        <v>46327.625</v>
+        <v>46327.904861111114</v>
       </c>
       <c r="K53" s="2">
-        <v>46331.75</v>
+        <v>46331.196527777778</v>
       </c>
       <c r="L53" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>34</v>
-      </c>
-      <c r="C54" t="s">
-        <v>152</v>
+        <v>60</v>
       </c>
       <c r="D54" t="s">
         <v>153</v>
@@ -2997,22 +2976,25 @@
         <v>154</v>
       </c>
       <c r="F54" t="s">
-        <v>38</v>
+        <v>121</v>
       </c>
       <c r="G54" t="s">
         <v>17</v>
       </c>
+      <c r="H54" t="s">
+        <v>59</v>
+      </c>
       <c r="I54" t="s">
         <v>18</v>
       </c>
       <c r="J54" s="2">
-        <v>46327.708333333336</v>
+        <v>46328.25</v>
       </c>
       <c r="K54" s="2">
         <v>46328.75</v>
       </c>
       <c r="L54" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -3020,10 +3002,10 @@
         <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C55" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="D55" t="s">
         <v>155</v>
@@ -3032,27 +3014,36 @@
         <v>156</v>
       </c>
       <c r="F55" t="s">
-        <v>16</v>
+        <v>51</v>
+      </c>
+      <c r="G55" t="s">
+        <v>52</v>
+      </c>
+      <c r="H55" t="s">
+        <v>107</v>
       </c>
       <c r="I55" t="s">
         <v>18</v>
       </c>
       <c r="J55" s="2">
-        <v>46327.904861111114</v>
+        <v>46329.208333333336</v>
       </c>
       <c r="K55" s="2">
-        <v>46331.196527777778</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="L55" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" t="s">
         <v>33</v>
-      </c>
-      <c r="B56" t="s">
-        <v>67</v>
       </c>
       <c r="D56" t="s">
         <v>157</v>
@@ -3061,25 +3052,19 @@
         <v>158</v>
       </c>
       <c r="F56" t="s">
-        <v>126</v>
-      </c>
-      <c r="G56" t="s">
-        <v>17</v>
-      </c>
-      <c r="H56" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="I56" t="s">
         <v>18</v>
       </c>
       <c r="J56" s="2">
-        <v>46328.25</v>
+        <v>46329.333333333336</v>
       </c>
       <c r="K56" s="2">
-        <v>46328.75</v>
+        <v>46332.625</v>
       </c>
       <c r="L56" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -3087,10 +3072,10 @@
         <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="D57" t="s">
         <v>159</v>
@@ -3099,25 +3084,19 @@
         <v>160</v>
       </c>
       <c r="F57" t="s">
-        <v>24</v>
-      </c>
-      <c r="G57" t="s">
-        <v>62</v>
-      </c>
-      <c r="H57" t="s">
-        <v>112</v>
+        <v>16</v>
       </c>
       <c r="I57" t="s">
         <v>18</v>
       </c>
       <c r="J57" s="2">
-        <v>46329.208333333336</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K57" s="2">
-        <v>46331.791666666664</v>
+        <v>46334</v>
       </c>
       <c r="L57" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -3128,60 +3107,63 @@
         <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="D58" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F58" t="s">
-        <v>146</v>
+        <v>16</v>
       </c>
       <c r="I58" t="s">
         <v>18</v>
       </c>
       <c r="J58" s="2">
-        <v>46329.333333333336</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K58" s="2">
-        <v>46332.625</v>
+        <v>46334</v>
       </c>
       <c r="L58" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B59" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C59" t="s">
-        <v>90</v>
+        <v>148</v>
       </c>
       <c r="D59" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F59" t="s">
-        <v>16</v>
+        <v>32</v>
+      </c>
+      <c r="G59" t="s">
+        <v>17</v>
       </c>
       <c r="I59" t="s">
         <v>18</v>
       </c>
       <c r="J59" s="2">
-        <v>46330.208333333336</v>
+        <v>46330.291666666664</v>
       </c>
       <c r="K59" s="2">
-        <v>46334</v>
+        <v>46331.166666666664</v>
       </c>
       <c r="L59" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3189,66 +3171,60 @@
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="C60" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="D60" t="s">
-        <v>163</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>164</v>
+        <v>43</v>
       </c>
       <c r="F60" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="I60" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="J60" s="2">
-        <v>46330.208333333336</v>
+        <v>46330.625</v>
       </c>
       <c r="K60" s="2">
-        <v>46334</v>
+        <v>46331.125</v>
       </c>
       <c r="L60" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
+        <v>12</v>
+      </c>
+      <c r="B61" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" t="s">
         <v>33</v>
       </c>
-      <c r="B61" t="s">
-        <v>34</v>
-      </c>
-      <c r="C61" t="s">
-        <v>35</v>
-      </c>
       <c r="D61" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F61" t="s">
-        <v>38</v>
-      </c>
-      <c r="G61" t="s">
-        <v>17</v>
+        <v>142</v>
       </c>
       <c r="I61" t="s">
         <v>18</v>
       </c>
       <c r="J61" s="2">
-        <v>46330.291666666664</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K61" s="2">
-        <v>46332.166666666664</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L61" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3256,28 +3232,31 @@
         <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C62" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="D62" t="s">
-        <v>56</v>
+        <v>163</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="F62" t="s">
-        <v>57</v>
+        <v>142</v>
       </c>
       <c r="I62" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="J62" s="2">
-        <v>46330.625</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K62" s="2">
-        <v>46331.125</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L62" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -3285,31 +3264,28 @@
         <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="C63" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="D63" t="s">
-        <v>167</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>168</v>
+        <v>77</v>
       </c>
       <c r="F63" t="s">
-        <v>146</v>
+        <v>58</v>
       </c>
       <c r="I63" t="s">
         <v>18</v>
       </c>
       <c r="J63" s="2">
-        <v>46330.633333333331</v>
+        <v>46330.704861111109</v>
       </c>
       <c r="K63" s="2">
-        <v>46333.925000000003</v>
+        <v>46331.204861111109</v>
       </c>
       <c r="L63" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3317,31 +3293,37 @@
         <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C64" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="D64" t="s">
+        <v>165</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F64" t="s">
+        <v>67</v>
+      </c>
+      <c r="G64" t="s">
+        <v>17</v>
+      </c>
+      <c r="H64" t="s">
         <v>167</v>
       </c>
-      <c r="E64" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F64" t="s">
-        <v>146</v>
-      </c>
       <c r="I64" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J64" s="2">
-        <v>46330.633333333331</v>
+        <v>46331.25</v>
       </c>
       <c r="K64" s="2">
-        <v>46333.925000000003</v>
+        <v>46331.75</v>
       </c>
       <c r="L64" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -3349,39 +3331,45 @@
         <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C65" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D65" t="s">
-        <v>83</v>
+        <v>168</v>
+      </c>
+      <c r="E65" s="1">
+        <v>10</v>
       </c>
       <c r="F65" t="s">
-        <v>47</v>
+        <v>39</v>
+      </c>
+      <c r="G65" t="s">
+        <v>17</v>
       </c>
       <c r="I65" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J65" s="2">
-        <v>46330.704861111109</v>
+        <v>46331.25</v>
       </c>
       <c r="K65" s="2">
-        <v>46331.204861111109</v>
+        <v>46331.666666666664</v>
       </c>
       <c r="L65" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B66" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="C66" t="s">
-        <v>14</v>
+        <v>148</v>
       </c>
       <c r="D66" t="s">
         <v>169</v>
@@ -3390,71 +3378,68 @@
         <v>170</v>
       </c>
       <c r="F66" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="G66" t="s">
         <v>17</v>
       </c>
-      <c r="H66" t="s">
-        <v>171</v>
-      </c>
       <c r="I66" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J66" s="2">
-        <v>46331.25</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K66" s="2">
-        <v>46331.75</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L66" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B67" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="C67" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D67" t="s">
+        <v>171</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E67" s="1">
-        <v>10</v>
-      </c>
       <c r="F67" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="G67" t="s">
         <v>17</v>
       </c>
       <c r="I67" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J67" s="2">
-        <v>46331.25</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K67" s="2">
-        <v>46331.666666666664</v>
+        <v>46333.166666666664</v>
       </c>
       <c r="L67" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C68" t="s">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="D68" t="s">
         <v>173</v>
@@ -3463,22 +3448,19 @@
         <v>174</v>
       </c>
       <c r="F68" t="s">
-        <v>38</v>
-      </c>
-      <c r="G68" t="s">
-        <v>17</v>
+        <v>142</v>
       </c>
       <c r="I68" t="s">
         <v>18</v>
       </c>
       <c r="J68" s="2">
-        <v>46331.291666666664</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K68" s="2">
-        <v>46332.166666666664</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L68" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3486,19 +3468,19 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C69" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D69" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F69" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I69" t="s">
         <v>18</v>
@@ -3510,7 +3492,7 @@
         <v>46334.746527777781</v>
       </c>
       <c r="L69" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3518,31 +3500,34 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c r="C70" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>175</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>176</v>
+        <v>168</v>
+      </c>
+      <c r="E70" s="1">
+        <v>10</v>
       </c>
       <c r="F70" t="s">
-        <v>146</v>
+        <v>39</v>
+      </c>
+      <c r="G70" t="s">
+        <v>17</v>
       </c>
       <c r="I70" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J70" s="2">
-        <v>46331.496527777781</v>
+        <v>46331.708333333336</v>
       </c>
       <c r="K70" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L70" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -3550,31 +3535,34 @@
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C71" t="s">
         <v>14</v>
       </c>
       <c r="D71" t="s">
-        <v>172</v>
-      </c>
-      <c r="E71" s="1">
-        <v>10</v>
+        <v>165</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="F71" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="G71" t="s">
         <v>17</v>
       </c>
+      <c r="H71" t="s">
+        <v>167</v>
+      </c>
       <c r="I71" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="J71" s="2">
-        <v>46331.708333333336</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K71" s="2">
-        <v>46332.166666666664</v>
+        <v>46332.75</v>
       </c>
       <c r="L71" t="s">
         <v>19</v>
@@ -3582,51 +3570,45 @@
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B72" t="s">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="C72" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="D72" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="F72" t="s">
-        <v>74</v>
-      </c>
-      <c r="G72" t="s">
-        <v>17</v>
-      </c>
-      <c r="H72" t="s">
-        <v>171</v>
+        <v>82</v>
       </c>
       <c r="I72" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J72" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K72" s="2">
-        <v>46332.75</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L72" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="C73" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="D73" t="s">
         <v>177</v>
@@ -3635,19 +3617,22 @@
         <v>178</v>
       </c>
       <c r="F73" t="s">
-        <v>88</v>
+        <v>67</v>
+      </c>
+      <c r="G73" t="s">
+        <v>17</v>
       </c>
       <c r="I73" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J73" s="2">
-        <v>46332.056250000001</v>
+        <v>46332.25</v>
       </c>
       <c r="K73" s="2">
-        <v>46332.597916666666</v>
+        <v>46332.75</v>
       </c>
       <c r="L73" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -3655,278 +3640,272 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C74" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="D74" t="s">
-        <v>179</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>180</v>
+        <v>116</v>
       </c>
       <c r="F74" t="s">
-        <v>74</v>
-      </c>
-      <c r="G74" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="I74" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J74" s="2">
-        <v>46332.25</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K74" s="2">
-        <v>46332.75</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="L74" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B75" t="s">
-        <v>34</v>
-      </c>
-      <c r="C75" t="s">
-        <v>152</v>
+        <v>60</v>
       </c>
       <c r="D75" t="s">
-        <v>181</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F75" t="s">
-        <v>38</v>
-      </c>
-      <c r="G75" t="s">
-        <v>17</v>
+        <v>121</v>
       </c>
       <c r="I75" t="s">
         <v>18</v>
       </c>
       <c r="J75" s="2">
-        <v>46332.291666666664</v>
+        <v>46332.375</v>
       </c>
       <c r="K75" s="2">
-        <v>46333.166666666664</v>
+        <v>46333.5</v>
       </c>
       <c r="L75" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B76" t="s">
-        <v>43</v>
-      </c>
-      <c r="C76" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D76" t="s">
+        <v>179</v>
+      </c>
+      <c r="F76" t="s">
         <v>121</v>
       </c>
-      <c r="F76" t="s">
-        <v>47</v>
-      </c>
       <c r="I76" t="s">
         <v>18</v>
       </c>
       <c r="J76" s="2">
-        <v>46332.291666666664</v>
+        <v>46332.375</v>
       </c>
       <c r="K76" s="2">
-        <v>46332.791666666664</v>
+        <v>46333.5</v>
       </c>
       <c r="L76" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>67</v>
+        <v>41</v>
+      </c>
+      <c r="C77" t="s">
+        <v>74</v>
       </c>
       <c r="D77" t="s">
-        <v>183</v>
+        <v>75</v>
       </c>
       <c r="F77" t="s">
-        <v>126</v>
+        <v>44</v>
       </c>
       <c r="I77" t="s">
         <v>18</v>
       </c>
       <c r="J77" s="2">
-        <v>46332.375</v>
+        <v>46332.541666666664</v>
       </c>
       <c r="K77" s="2">
-        <v>46333.5</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="L77" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B78" t="s">
+        <v>114</v>
+      </c>
+      <c r="C78" t="s">
+        <v>14</v>
+      </c>
+      <c r="D78" t="s">
+        <v>177</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F78" t="s">
         <v>67</v>
       </c>
-      <c r="D78" t="s">
-        <v>183</v>
-      </c>
-      <c r="F78" t="s">
-        <v>126</v>
+      <c r="G78" t="s">
+        <v>17</v>
       </c>
       <c r="I78" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J78" s="2">
-        <v>46332.375</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="K78" s="2">
-        <v>46333.5</v>
+        <v>46333.75</v>
       </c>
       <c r="L78" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B79" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C79" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="D79" t="s">
-        <v>82</v>
+        <v>180</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>181</v>
       </c>
       <c r="F79" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="I79" t="s">
         <v>18</v>
       </c>
       <c r="J79" s="2">
-        <v>46332.541666666664</v>
+        <v>46332.875</v>
       </c>
       <c r="K79" s="2">
-        <v>46333.041666666664</v>
+        <v>46334.25</v>
       </c>
       <c r="L79" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B80" t="s">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="C80" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="D80" t="s">
-        <v>179</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
+      </c>
+      <c r="E80" s="1">
+        <v>102</v>
       </c>
       <c r="F80" t="s">
-        <v>74</v>
-      </c>
-      <c r="G80" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="I80" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J80" s="2">
-        <v>46332.791666666664</v>
+        <v>46333</v>
       </c>
       <c r="K80" s="2">
-        <v>46333.75</v>
+        <v>46334</v>
       </c>
       <c r="L80" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>67</v>
-      </c>
-      <c r="C81" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="D81" t="s">
+        <v>183</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E81" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="F81" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="I81" t="s">
         <v>18</v>
       </c>
       <c r="J81" s="2">
-        <v>46332.875</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="K81" s="2">
-        <v>46334.25</v>
+        <v>46335.041666666664</v>
       </c>
       <c r="L81" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="C82" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D82" t="s">
+        <v>185</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E82" s="1">
-        <v>102</v>
-      </c>
       <c r="F82" t="s">
-        <v>105</v>
+        <v>187</v>
+      </c>
+      <c r="G82" t="s">
+        <v>17</v>
       </c>
       <c r="I82" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J82" s="2">
-        <v>46333</v>
+        <v>46333.25</v>
       </c>
       <c r="K82" s="2">
-        <v>46334</v>
+        <v>46333.75</v>
       </c>
       <c r="L82" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -3934,63 +3913,60 @@
         <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>20</v>
+        <v>56</v>
+      </c>
+      <c r="C83" t="s">
+        <v>69</v>
       </c>
       <c r="D83" t="s">
-        <v>187</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>188</v>
+        <v>70</v>
       </c>
       <c r="F83" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="I83" t="s">
         <v>18</v>
       </c>
       <c r="J83" s="2">
-        <v>46333.041666666664</v>
+        <v>46333.416666666664</v>
       </c>
       <c r="K83" s="2">
-        <v>46335.041666666664</v>
+        <v>46333.75</v>
       </c>
       <c r="L83" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B84" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C84" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="D84" t="s">
-        <v>189</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
+      </c>
+      <c r="E84" s="1">
+        <v>94</v>
       </c>
       <c r="F84" t="s">
-        <v>191</v>
-      </c>
-      <c r="G84" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="I84" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J84" s="2">
-        <v>46333.25</v>
+        <v>46333.666666666664</v>
       </c>
       <c r="K84" s="2">
-        <v>46333.75</v>
+        <v>46335.041666666664</v>
       </c>
       <c r="L84" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -3998,60 +3974,69 @@
         <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C85" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>77</v>
+        <v>189</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>190</v>
       </c>
       <c r="F85" t="s">
-        <v>47</v>
+        <v>16</v>
+      </c>
+      <c r="G85" t="s">
+        <v>17</v>
       </c>
       <c r="I85" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J85" s="2">
-        <v>46333.416666666664</v>
+        <v>46334.25</v>
       </c>
       <c r="K85" s="2">
-        <v>46333.75</v>
+        <v>46334.75</v>
       </c>
       <c r="L85" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="C86" t="s">
-        <v>98</v>
+        <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E86" s="1">
-        <v>94</v>
+        <v>11</v>
       </c>
       <c r="F86" t="s">
-        <v>101</v>
+        <v>39</v>
+      </c>
+      <c r="G86" t="s">
+        <v>17</v>
       </c>
       <c r="I86" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J86" s="2">
-        <v>46333.666666666664</v>
+        <v>46334.25</v>
       </c>
       <c r="K86" s="2">
-        <v>46335.041666666664</v>
+        <v>46334.75</v>
       </c>
       <c r="L86" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -4059,16 +4044,16 @@
         <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>50</v>
+        <v>114</v>
       </c>
       <c r="C87" t="s">
         <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F87" t="s">
         <v>16</v>
@@ -4077,13 +4062,13 @@
         <v>17</v>
       </c>
       <c r="I87" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="J87" s="2">
-        <v>46334.25</v>
+        <v>46334.791666666664</v>
       </c>
       <c r="K87" s="2">
-        <v>46334.75</v>
+        <v>46335.75</v>
       </c>
       <c r="L87" t="s">
         <v>19</v>
@@ -4094,34 +4079,31 @@
         <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C88" t="s">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="D88" t="s">
-        <v>195</v>
-      </c>
-      <c r="E88" s="1">
-        <v>11</v>
+        <v>192</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="F88" t="s">
-        <v>52</v>
-      </c>
-      <c r="G88" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I88" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J88" s="2">
-        <v>46334.25</v>
+        <v>46334.958333333336</v>
       </c>
       <c r="K88" s="2">
-        <v>46334.75</v>
+        <v>46337.708333333336</v>
       </c>
       <c r="L88" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -4129,28 +4111,28 @@
         <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C89" t="s">
         <v>14</v>
       </c>
       <c r="D89" t="s">
-        <v>193</v>
-      </c>
-      <c r="E89" s="1" t="s">
         <v>194</v>
       </c>
+      <c r="E89" s="1">
+        <v>1</v>
+      </c>
       <c r="F89" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G89" t="s">
         <v>17</v>
       </c>
       <c r="I89" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="J89" s="2">
-        <v>46334.791666666664</v>
+        <v>46335.25</v>
       </c>
       <c r="K89" s="2">
         <v>46335.75</v>
@@ -4164,31 +4146,34 @@
         <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C90" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="D90" t="s">
-        <v>196</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
+      </c>
+      <c r="E90" s="1">
+        <v>1</v>
       </c>
       <c r="F90" t="s">
-        <v>16</v>
+        <v>39</v>
+      </c>
+      <c r="G90" t="s">
+        <v>17</v>
       </c>
       <c r="I90" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J90" s="2">
-        <v>46334.958333333336</v>
+        <v>46335.791666666664</v>
       </c>
       <c r="K90" s="2">
-        <v>46337.708333333336</v>
+        <v>46336.75</v>
       </c>
       <c r="L90" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -4196,34 +4181,31 @@
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="C91" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="D91" t="s">
-        <v>198</v>
-      </c>
-      <c r="E91" s="1">
-        <v>1</v>
+        <v>195</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="F91" t="s">
-        <v>52</v>
-      </c>
-      <c r="G91" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="I91" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J91" s="2">
-        <v>46335.25</v>
+        <v>46337</v>
       </c>
       <c r="K91" s="2">
-        <v>46335.75</v>
+        <v>46339</v>
       </c>
       <c r="L91" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4231,66 +4213,60 @@
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C92" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="D92" t="s">
-        <v>198</v>
-      </c>
-      <c r="E92" s="1">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="F92" t="s">
-        <v>52</v>
-      </c>
-      <c r="G92" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="I92" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J92" s="2">
-        <v>46335.791666666664</v>
+        <v>46337.333333333336</v>
       </c>
       <c r="K92" s="2">
-        <v>46336.75</v>
+        <v>46337.833333333336</v>
       </c>
       <c r="L92" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B93" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C93" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D93" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F93" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I93" t="s">
         <v>18</v>
       </c>
       <c r="J93" s="2">
-        <v>46337</v>
+        <v>46337.333333333336</v>
       </c>
       <c r="K93" s="2">
-        <v>46339</v>
+        <v>46339.333333333336</v>
       </c>
       <c r="L93" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -4298,228 +4274,231 @@
         <v>12</v>
       </c>
       <c r="B94" t="s">
+        <v>41</v>
+      </c>
+      <c r="C94" t="s">
+        <v>42</v>
+      </c>
+      <c r="D94" t="s">
         <v>43</v>
       </c>
-      <c r="C94" t="s">
+      <c r="F94" t="s">
         <v>44</v>
       </c>
-      <c r="D94" t="s">
-        <v>45</v>
-      </c>
-      <c r="F94" t="s">
-        <v>47</v>
-      </c>
       <c r="I94" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="J94" s="2">
-        <v>46337.333333333336</v>
+        <v>46337.625</v>
       </c>
       <c r="K94" s="2">
-        <v>46337.833333333336</v>
+        <v>46338.125</v>
       </c>
       <c r="L94" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="C95" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D95" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F95" t="s">
-        <v>38</v>
+        <v>16</v>
+      </c>
+      <c r="G95" t="s">
+        <v>17</v>
       </c>
       <c r="I95" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J95" s="2">
-        <v>46337.333333333336</v>
+        <v>46338.25</v>
       </c>
       <c r="K95" s="2">
-        <v>46339.333333333336</v>
+        <v>46338.75</v>
       </c>
       <c r="L95" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B96" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C96" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="D96" t="s">
-        <v>56</v>
+        <v>201</v>
       </c>
       <c r="F96" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="I96" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="J96" s="2">
-        <v>46337.625</v>
+        <v>46338.431250000001</v>
       </c>
       <c r="K96" s="2">
-        <v>46338.125</v>
+        <v>46339.472916666666</v>
       </c>
       <c r="L96" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B97" t="s">
-        <v>113</v>
+        <v>28</v>
       </c>
       <c r="C97" t="s">
-        <v>14</v>
+        <v>148</v>
       </c>
       <c r="D97" t="s">
+        <v>202</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E97" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="F97" t="s">
-        <v>16</v>
-      </c>
-      <c r="G97" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="I97" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="J97" s="2">
-        <v>46338.25</v>
+        <v>46338.709027777775</v>
       </c>
       <c r="K97" s="2">
-        <v>46338.75</v>
+        <v>46339.584027777775</v>
       </c>
       <c r="L97" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="C98" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="D98" t="s">
+        <v>204</v>
+      </c>
+      <c r="E98" s="1" t="s">
         <v>205</v>
       </c>
       <c r="F98" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="I98" t="s">
         <v>18</v>
       </c>
       <c r="J98" s="2">
-        <v>46338.431250000001</v>
+        <v>46338.958333333336</v>
       </c>
       <c r="K98" s="2">
-        <v>46339.472916666666</v>
+        <v>46342.208333333336</v>
       </c>
       <c r="L98" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C99" t="s">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="D99" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F99" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="I99" t="s">
         <v>18</v>
       </c>
       <c r="J99" s="2">
-        <v>46338.709027777775</v>
+        <v>46338.958333333336</v>
       </c>
       <c r="K99" s="2">
-        <v>46339.584027777775</v>
+        <v>46342.208333333336</v>
       </c>
       <c r="L99" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B100" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="C100" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="D100" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F100" t="s">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="I100" t="s">
         <v>18</v>
       </c>
       <c r="J100" s="2">
-        <v>46338.958333333336</v>
+        <v>46339.083333333336</v>
       </c>
       <c r="K100" s="2">
-        <v>46342.208333333336</v>
+        <v>46340.291666666664</v>
       </c>
       <c r="L100" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B101" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="C101" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="D101" t="s">
         <v>208</v>
@@ -4528,173 +4507,109 @@
         <v>209</v>
       </c>
       <c r="F101" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="I101" t="s">
         <v>18</v>
       </c>
       <c r="J101" s="2">
-        <v>46338.958333333336</v>
+        <v>46339.291666666664</v>
       </c>
       <c r="K101" s="2">
-        <v>46342.208333333336</v>
+        <v>46340.666666666664</v>
       </c>
       <c r="L101" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B102" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C102" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="D102" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F102" t="s">
-        <v>146</v>
+        <v>64</v>
       </c>
       <c r="I102" t="s">
         <v>18</v>
       </c>
       <c r="J102" s="2">
-        <v>46339.083333333336</v>
+        <v>46339.291666666664</v>
       </c>
       <c r="K102" s="2">
-        <v>46340.291666666664</v>
+        <v>46340.666666666664</v>
       </c>
       <c r="L102" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="C103" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D103" t="s">
-        <v>212</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>213</v>
+        <v>75</v>
       </c>
       <c r="F103" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="I103" t="s">
         <v>18</v>
       </c>
       <c r="J103" s="2">
-        <v>46339.291666666664</v>
+        <v>46339.541666666664</v>
       </c>
       <c r="K103" s="2">
-        <v>46340.666666666664</v>
+        <v>46340.041666666664</v>
       </c>
       <c r="L103" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C104" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D104" t="s">
-        <v>212</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>213</v>
+        <v>77</v>
       </c>
       <c r="F104" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="I104" t="s">
         <v>18</v>
       </c>
       <c r="J104" s="2">
-        <v>46339.291666666664</v>
+        <v>46339.704861111109</v>
       </c>
       <c r="K104" s="2">
-        <v>46340.666666666664</v>
+        <v>46340.204861111109</v>
       </c>
       <c r="L104" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12">
-      <c r="A105" t="s">
-        <v>12</v>
-      </c>
-      <c r="B105" t="s">
-        <v>54</v>
-      </c>
-      <c r="C105" t="s">
-        <v>81</v>
-      </c>
-      <c r="D105" t="s">
-        <v>82</v>
-      </c>
-      <c r="F105" t="s">
-        <v>57</v>
-      </c>
-      <c r="I105" t="s">
-        <v>18</v>
-      </c>
-      <c r="J105" s="2">
-        <v>46339.541666666664</v>
-      </c>
-      <c r="K105" s="2">
-        <v>46340.041666666664</v>
-      </c>
-      <c r="L105" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12">
-      <c r="A106" t="s">
-        <v>12</v>
-      </c>
-      <c r="B106" t="s">
-        <v>43</v>
-      </c>
-      <c r="C106" t="s">
-        <v>44</v>
-      </c>
-      <c r="D106" t="s">
-        <v>83</v>
-      </c>
-      <c r="F106" t="s">
-        <v>47</v>
-      </c>
-      <c r="I106" t="s">
-        <v>18</v>
-      </c>
-      <c r="J106" s="2">
-        <v>46339.704861111109</v>
-      </c>
-      <c r="K106" s="2">
-        <v>46340.204861111109</v>
-      </c>
-      <c r="L106" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/data/vessels/2026-10-21.xlsx
+++ b/data/vessels/2026-10-21.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="445454" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{861725EE-4CC3-49BC-94B7-0800DED93175}"/>
+  <xr:revisionPtr revIDLastSave="446011" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF5633C0-68C0-4ACA-83FB-0040EC5922F5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="210">
   <si>
     <t>Harbor</t>
   </si>
@@ -101,6 +101,27 @@
     <t>Not available</t>
   </si>
   <si>
+    <t>Seattle</t>
+  </si>
+  <si>
+    <t>T5</t>
+  </si>
+  <si>
+    <t>Chinook</t>
+  </si>
+  <si>
+    <t>MSC DENISSE X</t>
+  </si>
+  <si>
+    <t>UK641R</t>
+  </si>
+  <si>
+    <t>MSC</t>
+  </si>
+  <si>
+    <t>At berth</t>
+  </si>
+  <si>
     <t>WUT</t>
   </si>
   <si>
@@ -119,27 +140,6 @@
     <t>Inchcape</t>
   </si>
   <si>
-    <t>At berth</t>
-  </si>
-  <si>
-    <t>Seattle</t>
-  </si>
-  <si>
-    <t>T5</t>
-  </si>
-  <si>
-    <t>Chinook</t>
-  </si>
-  <si>
-    <t>MSC DENISSE X</t>
-  </si>
-  <si>
-    <t>UK641R</t>
-  </si>
-  <si>
-    <t>MSC</t>
-  </si>
-  <si>
     <t>WC4/TP5</t>
   </si>
   <si>
@@ -164,270 +164,270 @@
     <t>Car Carrier</t>
   </si>
   <si>
+    <t>PCT</t>
+  </si>
+  <si>
+    <t>EVER MACH</t>
+  </si>
+  <si>
+    <t>018W</t>
+  </si>
+  <si>
+    <t>Evergreen</t>
+  </si>
+  <si>
+    <t>BEN LINE</t>
+  </si>
+  <si>
+    <t>In transit</t>
+  </si>
+  <si>
+    <t>T7</t>
+  </si>
+  <si>
+    <t>ARC INDEPENDENCE</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>R.J. PFEIFFER</t>
+  </si>
+  <si>
+    <t>Matson</t>
+  </si>
+  <si>
+    <t>SSA Marine</t>
+  </si>
+  <si>
+    <t>T18</t>
+  </si>
+  <si>
+    <t>PNW1</t>
+  </si>
+  <si>
+    <t>OOCL SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>199E/199W</t>
+  </si>
+  <si>
+    <t>OOCL</t>
+  </si>
+  <si>
+    <t>ARC ENDEAVOR</t>
+  </si>
+  <si>
+    <t>A6180</t>
+  </si>
+  <si>
+    <t>Wallenius</t>
+  </si>
+  <si>
+    <t>Ports America Group/Pct</t>
+  </si>
+  <si>
+    <t>Matson - HI2</t>
+  </si>
+  <si>
+    <t>MAUNAWILI</t>
+  </si>
+  <si>
+    <t>642S</t>
+  </si>
+  <si>
+    <t>CARNATION ACE</t>
+  </si>
+  <si>
+    <t>107A</t>
+  </si>
+  <si>
     <t>TOTE</t>
   </si>
   <si>
+    <t>Tote - AK2</t>
+  </si>
+  <si>
+    <t>NORTH STAR</t>
+  </si>
+  <si>
+    <t>Tote</t>
+  </si>
+  <si>
+    <t>Tote Maritime Alaska Inc</t>
+  </si>
+  <si>
+    <t>Multipurpose</t>
+  </si>
+  <si>
+    <t>Matson - AK</t>
+  </si>
+  <si>
+    <t>RJ PFEIFFER</t>
+  </si>
+  <si>
+    <t>KW664</t>
+  </si>
+  <si>
+    <t>EB Service 1</t>
+  </si>
+  <si>
+    <t>WESTWOOD RAINIER</t>
+  </si>
+  <si>
+    <t>159E/160W</t>
+  </si>
+  <si>
+    <t>Swire</t>
+  </si>
+  <si>
+    <t>Talon Marine Services LLC</t>
+  </si>
+  <si>
+    <t>FP2</t>
+  </si>
+  <si>
+    <t>YM TUTORIAL</t>
+  </si>
+  <si>
+    <t>ARC HONOR</t>
+  </si>
+  <si>
+    <t>ED616</t>
+  </si>
+  <si>
+    <t>PN3</t>
+  </si>
+  <si>
+    <t>YM WEALTH</t>
+  </si>
+  <si>
+    <t>PN32637W</t>
+  </si>
+  <si>
+    <t>CPNW</t>
+  </si>
+  <si>
+    <t>CMA CGM FORT JAMES</t>
+  </si>
+  <si>
+    <t>CPN04/CPN05</t>
+  </si>
+  <si>
+    <t>CMA CGM</t>
+  </si>
+  <si>
+    <t>CPV</t>
+  </si>
+  <si>
+    <t>COSCO VENICE</t>
+  </si>
+  <si>
+    <t>081N/081S</t>
+  </si>
+  <si>
+    <t>COSCO</t>
+  </si>
+  <si>
+    <t>COSCO SHIPPING LINES</t>
+  </si>
+  <si>
+    <t>POLARIS MILA</t>
+  </si>
+  <si>
+    <t>YM PLUM</t>
+  </si>
+  <si>
+    <t>198E</t>
+  </si>
+  <si>
+    <t>TPN</t>
+  </si>
+  <si>
+    <t>EVER SALUTE</t>
+  </si>
+  <si>
+    <t>129W</t>
+  </si>
+  <si>
+    <t>ACGI</t>
+  </si>
+  <si>
+    <t>Everport Terminal Services</t>
+  </si>
+  <si>
+    <t>LIBERTY PEACE</t>
+  </si>
+  <si>
+    <t>086S</t>
+  </si>
+  <si>
+    <t>Liberty</t>
+  </si>
+  <si>
+    <t>Pacific Terminals</t>
+  </si>
+  <si>
+    <t>FRANKFURT EXPRESS</t>
+  </si>
+  <si>
+    <t>640E/643W</t>
+  </si>
+  <si>
+    <t>Blair</t>
+  </si>
+  <si>
+    <t>LIBERTY PASSION</t>
+  </si>
+  <si>
+    <t>MATSON KODIAK</t>
+  </si>
+  <si>
+    <t>PATARA</t>
+  </si>
+  <si>
+    <t>005A</t>
+  </si>
+  <si>
+    <t>SM PORTLAND</t>
+  </si>
+  <si>
+    <t>2607E/2607W</t>
+  </si>
+  <si>
+    <t>SM Line</t>
+  </si>
+  <si>
     <t>Tote - AK1</t>
   </si>
   <si>
     <t>MIDNIGHT SUN</t>
   </si>
   <si>
-    <t>Tote</t>
-  </si>
-  <si>
-    <t>Tote Maritime Alaska Inc</t>
-  </si>
-  <si>
-    <t>Multipurpose</t>
-  </si>
-  <si>
-    <t>In transit</t>
-  </si>
-  <si>
-    <t>PCT</t>
-  </si>
-  <si>
-    <t>EVER MACH</t>
-  </si>
-  <si>
-    <t>018W</t>
-  </si>
-  <si>
-    <t>Evergreen</t>
-  </si>
-  <si>
-    <t>BEN LINE</t>
-  </si>
-  <si>
-    <t>T7</t>
-  </si>
-  <si>
-    <t>ARC INDEPENDENCE</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>R.J. PFEIFFER</t>
-  </si>
-  <si>
-    <t>Matson</t>
-  </si>
-  <si>
-    <t>SSA Marine</t>
-  </si>
-  <si>
-    <t>T18</t>
-  </si>
-  <si>
-    <t>PNW1</t>
-  </si>
-  <si>
-    <t>OOCL SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>199E/199W</t>
-  </si>
-  <si>
-    <t>OOCL</t>
-  </si>
-  <si>
-    <t>ARC ENDEAVOR</t>
-  </si>
-  <si>
-    <t>A6180</t>
-  </si>
-  <si>
-    <t>Wallenius</t>
-  </si>
-  <si>
-    <t>Ports America Group/Pct</t>
-  </si>
-  <si>
-    <t>Matson - HI2</t>
-  </si>
-  <si>
-    <t>MAUNAWILI</t>
-  </si>
-  <si>
-    <t>642S</t>
-  </si>
-  <si>
-    <t>CARNATION ACE</t>
-  </si>
-  <si>
-    <t>107A</t>
-  </si>
-  <si>
-    <t>Tote - AK2</t>
-  </si>
-  <si>
-    <t>NORTH STAR</t>
-  </si>
-  <si>
-    <t>Matson - AK</t>
-  </si>
-  <si>
-    <t>RJ PFEIFFER</t>
-  </si>
-  <si>
-    <t>KW664</t>
-  </si>
-  <si>
-    <t>EB Service 1</t>
-  </si>
-  <si>
-    <t>WESTWOOD RAINIER</t>
-  </si>
-  <si>
-    <t>159E/160W</t>
-  </si>
-  <si>
-    <t>Swire</t>
-  </si>
-  <si>
-    <t>Talon Marine Services LLC</t>
-  </si>
-  <si>
-    <t>FP2</t>
-  </si>
-  <si>
-    <t>YM TUTORIAL</t>
-  </si>
-  <si>
-    <t>ARC HONOR</t>
-  </si>
-  <si>
-    <t>ED616</t>
-  </si>
-  <si>
-    <t>PN3</t>
-  </si>
-  <si>
-    <t>YM WEALTH</t>
-  </si>
-  <si>
-    <t>PN32637W</t>
-  </si>
-  <si>
-    <t>CPNW</t>
-  </si>
-  <si>
-    <t>CMA CGM FORT JAMES</t>
-  </si>
-  <si>
-    <t>CPN04/CPN05</t>
-  </si>
-  <si>
-    <t>CMA CGM</t>
-  </si>
-  <si>
-    <t>CPV</t>
-  </si>
-  <si>
-    <t>COSCO VENICE</t>
-  </si>
-  <si>
-    <t>081N/081S</t>
-  </si>
-  <si>
-    <t>COSCO</t>
-  </si>
-  <si>
-    <t>COSCO SHIPPING LINES</t>
-  </si>
-  <si>
-    <t>POLARIS MILA</t>
-  </si>
-  <si>
-    <t>YM PLUM</t>
-  </si>
-  <si>
-    <t>198E</t>
-  </si>
-  <si>
-    <t>TPN</t>
-  </si>
-  <si>
-    <t>EVER SALUTE</t>
-  </si>
-  <si>
-    <t>129W</t>
-  </si>
-  <si>
-    <t>ACGI</t>
-  </si>
-  <si>
-    <t>Everport Terminal Services</t>
-  </si>
-  <si>
-    <t>LIBERTY PEACE</t>
-  </si>
-  <si>
-    <t>086S</t>
-  </si>
-  <si>
-    <t>Liberty</t>
-  </si>
-  <si>
-    <t>Pacific Terminals</t>
-  </si>
-  <si>
-    <t>FRANKFURT EXPRESS</t>
-  </si>
-  <si>
-    <t>640E/643W</t>
-  </si>
-  <si>
-    <t>Blair</t>
-  </si>
-  <si>
-    <t>LIBERTY PASSION</t>
-  </si>
-  <si>
-    <t>MATSON KODIAK</t>
-  </si>
-  <si>
-    <t>PATARA</t>
-  </si>
-  <si>
-    <t>005A</t>
-  </si>
-  <si>
-    <t>SM PORTLAND</t>
-  </si>
-  <si>
-    <t>2607E/2607W</t>
-  </si>
-  <si>
-    <t>SM Line</t>
-  </si>
-  <si>
     <t>MSC IVANA</t>
   </si>
   <si>
     <t>UK642R</t>
   </si>
   <si>
+    <t>Oceania</t>
+  </si>
+  <si>
+    <t>CMA CGM DUTCH HARBOR</t>
+  </si>
+  <si>
+    <t>0Y1N2/0T1N3</t>
+  </si>
+  <si>
     <t>ONE DURBAN</t>
   </si>
   <si>
     <t>PN32639E</t>
   </si>
   <si>
-    <t>Oceania</t>
-  </si>
-  <si>
-    <t>CMA CGM DUTCH HARBOR</t>
-  </si>
-  <si>
-    <t>0Y1N2/0T1N3</t>
-  </si>
-  <si>
     <t>MATSON ANCHORAGE</t>
   </si>
   <si>
@@ -479,21 +479,21 @@
     <t>ONE SYNERGY</t>
   </si>
   <si>
+    <t>CLX</t>
+  </si>
+  <si>
+    <t>MSC NITYA B</t>
+  </si>
+  <si>
+    <t>MC643R</t>
+  </si>
+  <si>
     <t>MSC SOLA</t>
   </si>
   <si>
     <t>UK643R</t>
   </si>
   <si>
-    <t>CLX</t>
-  </si>
-  <si>
-    <t>MSC NITYA B</t>
-  </si>
-  <si>
-    <t>MC643R</t>
-  </si>
-  <si>
     <t>ONE MAJESTY</t>
   </si>
   <si>
@@ -608,13 +608,13 @@
     <t>LOTUS A</t>
   </si>
   <si>
+    <t>GLOVIS TRUST</t>
+  </si>
+  <si>
     <t>SWIFT ACE</t>
   </si>
   <si>
     <t>152A</t>
-  </si>
-  <si>
-    <t>GLOVIS TRUST</t>
   </si>
   <si>
     <t>ONE MODERN</t>
@@ -741,10 +741,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L104" totalsRowShown="0">
-  <autoFilter ref="A1:L104" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L104">
-    <sortCondition ref="J2:J104"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L103" totalsRowShown="0">
+  <autoFilter ref="A1:L103" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L101">
+    <sortCondition ref="J2:J101"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1081,7 +1081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L104"/>
+  <dimension ref="A1:L103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1170,25 +1170,25 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I3" t="s">
         <v>18</v>
@@ -1197,7 +1197,7 @@
         <v>46315.666666666664</v>
       </c>
       <c r="K3" s="2">
-        <v>46317.75</v>
+        <v>46317.375</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -1205,25 +1205,25 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
         <v>27</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>28</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>29</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" t="s">
         <v>31</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>32</v>
-      </c>
-      <c r="G4" t="s">
-        <v>17</v>
       </c>
       <c r="I4" t="s">
         <v>18</v>
@@ -1232,7 +1232,7 @@
         <v>46315.666666666664</v>
       </c>
       <c r="K4" s="2">
-        <v>46317.375</v>
+        <v>46317.75</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -1350,14 +1350,11 @@
       <c r="B8" t="s">
         <v>41</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>42</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="E8" s="1">
-        <v>26169</v>
       </c>
       <c r="F8" t="s">
         <v>44</v>
@@ -1365,20 +1362,17 @@
       <c r="G8" t="s">
         <v>45</v>
       </c>
-      <c r="H8" t="s">
-        <v>45</v>
-      </c>
       <c r="I8" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="J8" s="2">
-        <v>46316.625</v>
+        <v>46317.208333333336</v>
       </c>
       <c r="K8" s="2">
-        <v>46317.041666666664</v>
+        <v>46318.708333333336</v>
       </c>
       <c r="L8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1386,31 +1380,34 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
         <v>48</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" t="s">
-        <v>51</v>
-      </c>
       <c r="G9" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="I9" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J9" s="2">
-        <v>46317.208333333336</v>
+        <v>46317.875</v>
       </c>
       <c r="K9" s="2">
-        <v>46318.708333333336</v>
+        <v>46321.75</v>
       </c>
       <c r="L9" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1418,19 +1415,19 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G10" t="s">
         <v>17</v>
@@ -1453,31 +1450,31 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G11" t="s">
-        <v>17</v>
+        <v>52</v>
+      </c>
+      <c r="H11" t="s">
+        <v>53</v>
       </c>
       <c r="I11" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J11" s="2">
-        <v>46317.875</v>
+        <v>46318.125</v>
       </c>
       <c r="K11" s="2">
-        <v>46321.75</v>
+        <v>46318.916666666664</v>
       </c>
       <c r="L11" t="s">
         <v>19</v>
@@ -1485,75 +1482,78 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" t="s">
         <v>56</v>
       </c>
-      <c r="C12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="E12" s="1" t="s">
         <v>57</v>
       </c>
       <c r="F12" t="s">
         <v>58</v>
       </c>
       <c r="G12" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="H12" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="I12" t="s">
         <v>18</v>
       </c>
       <c r="J12" s="2">
-        <v>46318.125</v>
+        <v>46318.25</v>
       </c>
       <c r="K12" s="2">
-        <v>46318.916666666664</v>
+        <v>46319.166666666664</v>
       </c>
       <c r="L12" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C13" t="s">
+      <c r="F13" t="s">
         <v>61</v>
       </c>
-      <c r="D13" t="s">
+      <c r="G13" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" t="s">
         <v>62</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
-      </c>
-      <c r="G13" t="s">
-        <v>25</v>
-      </c>
-      <c r="H13" t="s">
-        <v>59</v>
-      </c>
       <c r="I13" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J13" s="2">
-        <v>46318.25</v>
+        <v>46318.291666666664</v>
       </c>
       <c r="K13" s="2">
-        <v>46319.166666666664</v>
+        <v>46318.791666666664</v>
       </c>
       <c r="L13" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1561,37 +1561,37 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="G14" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="H14" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="I14" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J14" s="2">
-        <v>46318.291666666664</v>
+        <v>46318.416666666664</v>
       </c>
       <c r="K14" s="2">
-        <v>46318.791666666664</v>
+        <v>46319.125</v>
       </c>
       <c r="L14" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1599,37 +1599,34 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="G15" t="s">
-        <v>58</v>
-      </c>
-      <c r="H15" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="I15" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J15" s="2">
-        <v>46318.416666666664</v>
+        <v>46318.583333333336</v>
       </c>
       <c r="K15" s="2">
-        <v>46319.125</v>
+        <v>46319.041666666664</v>
       </c>
       <c r="L15" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1637,28 +1634,31 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" s="1">
+        <v>26168</v>
+      </c>
+      <c r="F16" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" t="s">
         <v>72</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="H16" t="s">
+        <v>72</v>
+      </c>
+      <c r="I16" t="s">
         <v>73</v>
       </c>
-      <c r="F16" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" t="s">
-        <v>40</v>
-      </c>
       <c r="J16" s="2">
-        <v>46318.583333333336</v>
+        <v>46318.625</v>
       </c>
       <c r="K16" s="2">
         <v>46319.041666666664</v>
@@ -1672,7 +1672,7 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
         <v>74</v>
@@ -1680,29 +1680,23 @@
       <c r="D17" t="s">
         <v>75</v>
       </c>
-      <c r="E17" s="1">
-        <v>26168</v>
+      <c r="E17" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="F17" t="s">
-        <v>44</v>
-      </c>
-      <c r="G17" t="s">
-        <v>45</v>
-      </c>
-      <c r="H17" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="I17" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="J17" s="2">
-        <v>46318.625</v>
+        <v>46318.704861111109</v>
       </c>
       <c r="K17" s="2">
-        <v>46319.041666666664</v>
+        <v>46319.204861111109</v>
       </c>
       <c r="L17" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1710,107 +1704,110 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D18" t="s">
-        <v>77</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>61</v>
+      </c>
+      <c r="G18" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" t="s">
+        <v>62</v>
       </c>
       <c r="I18" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J18" s="2">
-        <v>46318.704861111109</v>
+        <v>46318.833333333336</v>
       </c>
       <c r="K18" s="2">
-        <v>46319.204861111109</v>
+        <v>46319.791666666664</v>
       </c>
       <c r="L18" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" t="s">
+        <v>80</v>
+      </c>
+      <c r="G19" t="s">
+        <v>81</v>
+      </c>
+      <c r="H19" t="s">
         <v>53</v>
       </c>
-      <c r="C19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" t="s">
-        <v>65</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F19" t="s">
-        <v>67</v>
-      </c>
-      <c r="G19" t="s">
-        <v>17</v>
-      </c>
-      <c r="H19" t="s">
-        <v>68</v>
-      </c>
       <c r="I19" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J19" s="2">
-        <v>46318.833333333336</v>
+        <v>46318.916666666664</v>
       </c>
       <c r="K19" s="2">
-        <v>46319.791666666664</v>
+        <v>46320.083333333336</v>
       </c>
       <c r="L19" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="E20" s="1">
+        <v>21</v>
       </c>
       <c r="F20" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="G20" t="s">
-        <v>83</v>
-      </c>
-      <c r="H20" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="I20" t="s">
         <v>18</v>
       </c>
       <c r="J20" s="2">
-        <v>46318.916666666664</v>
+        <v>46319.208333333336</v>
       </c>
       <c r="K20" s="2">
-        <v>46320.083333333336</v>
+        <v>46325.75</v>
       </c>
       <c r="L20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1818,34 +1815,34 @@
         <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" t="s">
         <v>84</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E21" s="1">
-        <v>21</v>
-      </c>
       <c r="F21" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="G21" t="s">
         <v>17</v>
       </c>
       <c r="I21" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J21" s="2">
-        <v>46319.208333333336</v>
+        <v>46319.25</v>
       </c>
       <c r="K21" s="2">
-        <v>46325.75</v>
+        <v>46319.75</v>
       </c>
       <c r="L21" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1853,139 +1850,139 @@
         <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="D22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F22" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="G22" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="I22" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J22" s="2">
-        <v>46319.25</v>
+        <v>46319.666666666664</v>
       </c>
       <c r="K22" s="2">
-        <v>46319.75</v>
+        <v>46321.75</v>
       </c>
       <c r="L22" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F23" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="G23" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I23" t="s">
         <v>18</v>
       </c>
       <c r="J23" s="2">
-        <v>46319.666666666664</v>
+        <v>46320.625</v>
       </c>
       <c r="K23" s="2">
-        <v>46321.75</v>
+        <v>46322.75</v>
       </c>
       <c r="L23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F24" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G24" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="I24" t="s">
         <v>18</v>
       </c>
       <c r="J24" s="2">
-        <v>46320.625</v>
+        <v>46321.208333333336</v>
       </c>
       <c r="K24" s="2">
-        <v>46322.75</v>
+        <v>46322.166666666664</v>
       </c>
       <c r="L24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>96</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="E25" s="1">
+        <v>4</v>
       </c>
       <c r="F25" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="G25" t="s">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="I25" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J25" s="2">
-        <v>46321.208333333336</v>
+        <v>46321.25</v>
       </c>
       <c r="K25" s="2">
-        <v>46322.166666666664</v>
+        <v>46321.75</v>
       </c>
       <c r="L25" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -1993,34 +1990,34 @@
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D26" t="s">
+        <v>99</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E26" s="1">
-        <v>4</v>
-      </c>
       <c r="F26" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G26" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="I26" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J26" s="2">
         <v>46321.25</v>
       </c>
       <c r="K26" s="2">
-        <v>46321.75</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L26" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -2028,34 +2025,37 @@
         <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="D27" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F27" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="G27" t="s">
-        <v>25</v>
+        <v>104</v>
+      </c>
+      <c r="H27" t="s">
+        <v>105</v>
       </c>
       <c r="I27" t="s">
         <v>18</v>
       </c>
       <c r="J27" s="2">
-        <v>46321.25</v>
+        <v>46322.208333333336</v>
       </c>
       <c r="K27" s="2">
-        <v>46323.166666666664</v>
+        <v>46324.791666666664</v>
       </c>
       <c r="L27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -2063,37 +2063,37 @@
         <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F28" t="s">
-        <v>51</v>
+        <v>108</v>
       </c>
       <c r="G28" t="s">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="H28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I28" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J28" s="2">
-        <v>46322.208333333336</v>
+        <v>46322.25</v>
       </c>
       <c r="K28" s="2">
-        <v>46324.791666666664</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L28" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -2101,37 +2101,34 @@
         <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="C29" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D29" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F29" t="s">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="G29" t="s">
-        <v>25</v>
-      </c>
-      <c r="H29" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="I29" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J29" s="2">
-        <v>46322.25</v>
+        <v>46322.625</v>
       </c>
       <c r="K29" s="2">
-        <v>46323.166666666664</v>
+        <v>46325.75</v>
       </c>
       <c r="L29" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2139,34 +2136,34 @@
         <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
       <c r="C30" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>112</v>
-      </c>
-      <c r="E30" s="1" t="s">
         <v>113</v>
       </c>
       <c r="F30" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="G30" t="s">
-        <v>17</v>
+        <v>32</v>
+      </c>
+      <c r="H30" t="s">
+        <v>109</v>
       </c>
       <c r="I30" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J30" s="2">
-        <v>46322.625</v>
+        <v>46322.708333333336</v>
       </c>
       <c r="K30" s="2">
-        <v>46325.75</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L30" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -2174,34 +2171,34 @@
         <v>12</v>
       </c>
       <c r="B31" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" t="s">
+        <v>74</v>
+      </c>
+      <c r="D31" t="s">
         <v>114</v>
       </c>
-      <c r="C31" t="s">
-        <v>14</v>
-      </c>
-      <c r="D31" t="s">
-        <v>115</v>
-      </c>
       <c r="F31" t="s">
-        <v>110</v>
+        <v>52</v>
       </c>
       <c r="G31" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="H31" t="s">
-        <v>111</v>
+        <v>53</v>
       </c>
       <c r="I31" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J31" s="2">
-        <v>46322.708333333336</v>
+        <v>46323.104166666664</v>
       </c>
       <c r="K31" s="2">
-        <v>46323.166666666664</v>
+        <v>46323.916666666664</v>
       </c>
       <c r="L31" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -2209,45 +2206,42 @@
         <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="C32" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="D32" t="s">
+        <v>115</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>116</v>
       </c>
       <c r="F32" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="G32" t="s">
-        <v>58</v>
-      </c>
-      <c r="H32" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="I32" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J32" s="2">
-        <v>46323.104166666664</v>
+        <v>46323.25</v>
       </c>
       <c r="K32" s="2">
-        <v>46323.916666666664</v>
+        <v>46323.75</v>
       </c>
       <c r="L32" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="D33" t="s">
         <v>117</v>
@@ -2256,13 +2250,16 @@
         <v>118</v>
       </c>
       <c r="F33" t="s">
-        <v>16</v>
+        <v>119</v>
       </c>
       <c r="G33" t="s">
         <v>17</v>
       </c>
+      <c r="H33" t="s">
+        <v>53</v>
+      </c>
       <c r="I33" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J33" s="2">
         <v>46323.25</v>
@@ -2271,153 +2268,156 @@
         <v>46323.75</v>
       </c>
       <c r="L33" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>60</v>
+        <v>68</v>
+      </c>
+      <c r="C34" t="s">
+        <v>120</v>
       </c>
       <c r="D34" t="s">
-        <v>119</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="E34" s="1">
+        <v>26173</v>
       </c>
       <c r="F34" t="s">
-        <v>121</v>
+        <v>71</v>
       </c>
       <c r="G34" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="H34" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="I34" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="J34" s="2">
-        <v>46323.25</v>
+        <v>46323.625</v>
       </c>
       <c r="K34" s="2">
-        <v>46323.75</v>
+        <v>46324.041666666664</v>
       </c>
       <c r="L34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C35" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D35" t="s">
-        <v>43</v>
-      </c>
-      <c r="E35" s="1">
-        <v>26173</v>
+        <v>122</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="F35" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="G35" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H35" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="I35" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="J35" s="2">
-        <v>46323.625</v>
+        <v>46323.708333333336</v>
       </c>
       <c r="K35" s="2">
-        <v>46324.041666666664</v>
+        <v>46325.75</v>
       </c>
       <c r="L35" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="C36" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F36" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G36" t="s">
         <v>17</v>
       </c>
-      <c r="H36" t="s">
-        <v>59</v>
-      </c>
       <c r="I36" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J36" s="2">
-        <v>46323.708333333336</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="K36" s="2">
-        <v>46325.75</v>
+        <v>46324.75</v>
       </c>
       <c r="L36" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B37" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="C37" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="D37" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="F37" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="G37" t="s">
         <v>17</v>
       </c>
+      <c r="H37" t="s">
+        <v>53</v>
+      </c>
       <c r="I37" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J37" s="2">
-        <v>46323.791666666664</v>
+        <v>46324.25</v>
       </c>
       <c r="K37" s="2">
-        <v>46324.75</v>
+        <v>46325.166666666664</v>
       </c>
       <c r="L37" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -2425,16 +2425,16 @@
         <v>12</v>
       </c>
       <c r="B38" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D38" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F38" t="s">
         <v>16</v>
@@ -2452,45 +2452,36 @@
         <v>46326.166666666664</v>
       </c>
       <c r="L38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C39" t="s">
-        <v>126</v>
+        <v>74</v>
       </c>
       <c r="D39" t="s">
-        <v>127</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F39" t="s">
-        <v>94</v>
-      </c>
-      <c r="G39" t="s">
-        <v>17</v>
-      </c>
-      <c r="H39" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="I39" t="s">
         <v>18</v>
       </c>
       <c r="J39" s="2">
-        <v>46324.25</v>
+        <v>46325.333333333336</v>
       </c>
       <c r="K39" s="2">
-        <v>46325.166666666664</v>
+        <v>46325.833333333336</v>
       </c>
       <c r="L39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2498,28 +2489,37 @@
         <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C40" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D40" t="s">
-        <v>129</v>
+        <v>70</v>
+      </c>
+      <c r="E40" s="1">
+        <v>26172</v>
       </c>
       <c r="F40" t="s">
-        <v>58</v>
+        <v>71</v>
+      </c>
+      <c r="G40" t="s">
+        <v>72</v>
+      </c>
+      <c r="H40" t="s">
+        <v>72</v>
       </c>
       <c r="I40" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="J40" s="2">
-        <v>46325.333333333336</v>
+        <v>46325.625</v>
       </c>
       <c r="K40" s="2">
-        <v>46325.833333333336</v>
+        <v>46326.041666666664</v>
       </c>
       <c r="L40" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2529,14 +2529,11 @@
       <c r="B41" t="s">
         <v>41</v>
       </c>
-      <c r="C41" t="s">
-        <v>74</v>
-      </c>
       <c r="D41" t="s">
-        <v>75</v>
-      </c>
-      <c r="E41" s="1">
-        <v>26172</v>
+        <v>130</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="F41" t="s">
         <v>44</v>
@@ -2544,20 +2541,17 @@
       <c r="G41" t="s">
         <v>45</v>
       </c>
-      <c r="H41" t="s">
-        <v>45</v>
-      </c>
       <c r="I41" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="J41" s="2">
-        <v>46325.625</v>
+        <v>46325.708333333336</v>
       </c>
       <c r="K41" s="2">
-        <v>46326.041666666664</v>
+        <v>46327.208333333336</v>
       </c>
       <c r="L41" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2565,7 +2559,7 @@
         <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D42" t="s">
         <v>130</v>
@@ -2574,10 +2568,10 @@
         <v>131</v>
       </c>
       <c r="F42" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G42" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="I42" t="s">
         <v>18</v>
@@ -2589,74 +2583,77 @@
         <v>46327.208333333336</v>
       </c>
       <c r="L42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B43" t="s">
-        <v>48</v>
+        <v>54</v>
+      </c>
+      <c r="C43" t="s">
+        <v>132</v>
       </c>
       <c r="D43" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F43" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="I43" t="s">
         <v>18</v>
       </c>
       <c r="J43" s="2">
-        <v>46325.708333333336</v>
+        <v>46325.958333333336</v>
       </c>
       <c r="K43" s="2">
-        <v>46327.208333333336</v>
+        <v>46327.416666666664</v>
       </c>
       <c r="L43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="C44" t="s">
-        <v>132</v>
+        <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F44" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="G44" t="s">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="I44" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J44" s="2">
-        <v>46325.958333333336</v>
+        <v>46326.25</v>
       </c>
       <c r="K44" s="2">
-        <v>46327.416666666664</v>
+        <v>46326.75</v>
       </c>
       <c r="L44" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2664,98 +2661,95 @@
         <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="C45" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="D45" t="s">
-        <v>135</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F45" t="s">
-        <v>16</v>
-      </c>
-      <c r="G45" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="I45" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J45" s="2">
-        <v>46326.25</v>
+        <v>46326.416666666664</v>
       </c>
       <c r="K45" s="2">
         <v>46326.75</v>
       </c>
       <c r="L45" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C46" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="D46" t="s">
-        <v>137</v>
+        <v>138</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="F46" t="s">
-        <v>58</v>
+        <v>92</v>
+      </c>
+      <c r="G46" t="s">
+        <v>17</v>
       </c>
       <c r="I46" t="s">
         <v>18</v>
       </c>
       <c r="J46" s="2">
-        <v>46326.416666666664</v>
+        <v>46326.625</v>
       </c>
       <c r="K46" s="2">
-        <v>46326.75</v>
+        <v>46328.75</v>
       </c>
       <c r="L46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" t="s">
         <v>27</v>
       </c>
-      <c r="B47" t="s">
-        <v>60</v>
-      </c>
       <c r="C47" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D47" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F47" t="s">
-        <v>94</v>
-      </c>
-      <c r="G47" t="s">
-        <v>17</v>
+        <v>142</v>
       </c>
       <c r="I47" t="s">
         <v>18</v>
       </c>
       <c r="J47" s="2">
-        <v>46326.625</v>
+        <v>46326.833333333336</v>
       </c>
       <c r="K47" s="2">
-        <v>46328.75</v>
+        <v>46329.583333333336</v>
       </c>
       <c r="L47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2763,31 +2757,34 @@
         <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="C48" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F48" t="s">
-        <v>142</v>
+        <v>16</v>
+      </c>
+      <c r="G48" t="s">
+        <v>17</v>
       </c>
       <c r="I48" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J48" s="2">
-        <v>46326.833333333336</v>
+        <v>46327.25</v>
       </c>
       <c r="K48" s="2">
-        <v>46329.583333333336</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="L48" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2795,16 +2792,16 @@
         <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>114</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="D49" t="s">
-        <v>143</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
+      </c>
+      <c r="E49" s="1">
+        <v>2</v>
       </c>
       <c r="F49" t="s">
         <v>16</v>
@@ -2813,36 +2810,36 @@
         <v>17</v>
       </c>
       <c r="I49" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J49" s="2">
-        <v>46327.25</v>
+        <v>46327.625</v>
       </c>
       <c r="K49" s="2">
-        <v>46327.708333333336</v>
+        <v>46331.75</v>
       </c>
       <c r="L49" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C50" t="s">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="D50" t="s">
-        <v>145</v>
-      </c>
-      <c r="E50" s="1">
-        <v>2</v>
+        <v>147</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="F50" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G50" t="s">
         <v>17</v>
@@ -2851,33 +2848,33 @@
         <v>18</v>
       </c>
       <c r="J50" s="2">
-        <v>46327.625</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K50" s="2">
-        <v>46331.75</v>
+        <v>46328.75</v>
       </c>
       <c r="L50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B51" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C51" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D51" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F51" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G51" t="s">
         <v>17</v>
@@ -2892,109 +2889,112 @@
         <v>46329.75</v>
       </c>
       <c r="L51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" t="s">
         <v>27</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>28</v>
       </c>
-      <c r="C52" t="s">
-        <v>148</v>
-      </c>
       <c r="D52" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F52" t="s">
-        <v>32</v>
-      </c>
-      <c r="G52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I52" t="s">
         <v>18</v>
       </c>
       <c r="J52" s="2">
-        <v>46327.708333333336</v>
+        <v>46327.904861111114</v>
       </c>
       <c r="K52" s="2">
-        <v>46328.75</v>
+        <v>46331.196527777778</v>
       </c>
       <c r="L52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B53" t="s">
-        <v>20</v>
-      </c>
-      <c r="C53" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="D53" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F53" t="s">
-        <v>16</v>
+        <v>119</v>
+      </c>
+      <c r="G53" t="s">
+        <v>17</v>
+      </c>
+      <c r="H53" t="s">
+        <v>53</v>
       </c>
       <c r="I53" t="s">
         <v>18</v>
       </c>
       <c r="J53" s="2">
-        <v>46327.904861111114</v>
+        <v>46328.25</v>
       </c>
       <c r="K53" s="2">
-        <v>46331.196527777778</v>
+        <v>46328.75</v>
       </c>
       <c r="L53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>60</v>
+        <v>41</v>
+      </c>
+      <c r="C54" t="s">
+        <v>101</v>
       </c>
       <c r="D54" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F54" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="G54" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="H54" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="I54" t="s">
         <v>18</v>
       </c>
       <c r="J54" s="2">
-        <v>46328.25</v>
+        <v>46329.208333333336</v>
       </c>
       <c r="K54" s="2">
-        <v>46328.75</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="L54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -3002,37 +3002,31 @@
         <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>103</v>
+        <v>33</v>
       </c>
       <c r="D55" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F55" t="s">
-        <v>51</v>
-      </c>
-      <c r="G55" t="s">
-        <v>52</v>
-      </c>
-      <c r="H55" t="s">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="I55" t="s">
         <v>18</v>
       </c>
       <c r="J55" s="2">
-        <v>46329.208333333336</v>
+        <v>46329.333333333336</v>
       </c>
       <c r="K55" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.625</v>
       </c>
       <c r="L55" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -3043,28 +3037,28 @@
         <v>13</v>
       </c>
       <c r="C56" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="D56" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F56" t="s">
-        <v>142</v>
+        <v>16</v>
       </c>
       <c r="I56" t="s">
         <v>18</v>
       </c>
       <c r="J56" s="2">
-        <v>46329.333333333336</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K56" s="2">
-        <v>46332.625</v>
+        <v>46334</v>
       </c>
       <c r="L56" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -3075,7 +3069,7 @@
         <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D57" t="s">
         <v>159</v>
@@ -3096,74 +3090,71 @@
         <v>46334</v>
       </c>
       <c r="L57" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B58" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C58" t="s">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="D58" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F58" t="s">
-        <v>16</v>
+        <v>25</v>
+      </c>
+      <c r="G58" t="s">
+        <v>17</v>
       </c>
       <c r="I58" t="s">
         <v>18</v>
       </c>
       <c r="J58" s="2">
-        <v>46330.208333333336</v>
+        <v>46330.291666666664</v>
       </c>
       <c r="K58" s="2">
-        <v>46334</v>
+        <v>46331.166666666664</v>
       </c>
       <c r="L58" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="C59" t="s">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="D59" t="s">
-        <v>161</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="F59" t="s">
-        <v>32</v>
-      </c>
-      <c r="G59" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="I59" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="J59" s="2">
-        <v>46330.291666666664</v>
+        <v>46330.625</v>
       </c>
       <c r="K59" s="2">
-        <v>46331.166666666664</v>
+        <v>46331.125</v>
       </c>
       <c r="L59" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3171,28 +3162,31 @@
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D60" t="s">
-        <v>43</v>
+        <v>163</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="F60" t="s">
-        <v>44</v>
+        <v>142</v>
       </c>
       <c r="I60" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="J60" s="2">
-        <v>46330.625</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K60" s="2">
-        <v>46331.125</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3224,7 +3218,7 @@
         <v>46333.925000000003</v>
       </c>
       <c r="L61" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3232,31 +3226,28 @@
         <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="C62" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="D62" t="s">
-        <v>163</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>164</v>
+        <v>75</v>
       </c>
       <c r="F62" t="s">
-        <v>142</v>
+        <v>52</v>
       </c>
       <c r="I62" t="s">
         <v>18</v>
       </c>
       <c r="J62" s="2">
-        <v>46330.633333333331</v>
+        <v>46330.704861111109</v>
       </c>
       <c r="K62" s="2">
-        <v>46333.925000000003</v>
+        <v>46331.204861111109</v>
       </c>
       <c r="L62" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -3264,28 +3255,37 @@
         <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="C63" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>77</v>
+        <v>165</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="F63" t="s">
-        <v>58</v>
+        <v>61</v>
+      </c>
+      <c r="G63" t="s">
+        <v>17</v>
+      </c>
+      <c r="H63" t="s">
+        <v>167</v>
       </c>
       <c r="I63" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J63" s="2">
-        <v>46330.704861111109</v>
+        <v>46331.25</v>
       </c>
       <c r="K63" s="2">
-        <v>46331.204861111109</v>
+        <v>46331.75</v>
       </c>
       <c r="L63" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3299,20 +3299,17 @@
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>165</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
+      </c>
+      <c r="E64" s="1">
+        <v>10</v>
       </c>
       <c r="F64" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="G64" t="s">
         <v>17</v>
       </c>
-      <c r="H64" t="s">
-        <v>167</v>
-      </c>
       <c r="I64" t="s">
         <v>40</v>
       </c>
@@ -3320,7 +3317,7 @@
         <v>46331.25</v>
       </c>
       <c r="K64" s="2">
-        <v>46331.75</v>
+        <v>46331.666666666664</v>
       </c>
       <c r="L64" t="s">
         <v>19</v>
@@ -3328,57 +3325,57 @@
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B65" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C65" t="s">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="D65" t="s">
-        <v>168</v>
-      </c>
-      <c r="E65" s="1">
-        <v>10</v>
+        <v>169</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="F65" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G65" t="s">
         <v>17</v>
       </c>
       <c r="I65" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J65" s="2">
-        <v>46331.25</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K65" s="2">
-        <v>46331.666666666664</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L65" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B66" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C66" t="s">
-        <v>148</v>
+        <v>22</v>
       </c>
       <c r="D66" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F66" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G66" t="s">
         <v>17</v>
@@ -3390,45 +3387,42 @@
         <v>46331.291666666664</v>
       </c>
       <c r="K66" s="2">
-        <v>46332.166666666664</v>
+        <v>46333.166666666664</v>
       </c>
       <c r="L66" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
+        <v>12</v>
+      </c>
+      <c r="B67" t="s">
         <v>27</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" t="s">
         <v>28</v>
       </c>
-      <c r="C67" t="s">
-        <v>29</v>
-      </c>
       <c r="D67" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F67" t="s">
-        <v>32</v>
-      </c>
-      <c r="G67" t="s">
-        <v>17</v>
+        <v>142</v>
       </c>
       <c r="I67" t="s">
         <v>18</v>
       </c>
       <c r="J67" s="2">
-        <v>46331.291666666664</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K67" s="2">
-        <v>46333.166666666664</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L67" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -3436,10 +3430,10 @@
         <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C68" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D68" t="s">
         <v>173</v>
@@ -3460,7 +3454,7 @@
         <v>46334.746527777781</v>
       </c>
       <c r="L68" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3468,31 +3462,34 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="C69" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>173</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
+      </c>
+      <c r="E69" s="1">
+        <v>10</v>
       </c>
       <c r="F69" t="s">
-        <v>142</v>
+        <v>39</v>
+      </c>
+      <c r="G69" t="s">
+        <v>17</v>
       </c>
       <c r="I69" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J69" s="2">
-        <v>46331.496527777781</v>
+        <v>46331.708333333336</v>
       </c>
       <c r="K69" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L69" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3500,31 +3497,34 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>168</v>
-      </c>
-      <c r="E70" s="1">
-        <v>10</v>
+        <v>165</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="F70" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="G70" t="s">
         <v>17</v>
       </c>
+      <c r="H70" t="s">
+        <v>167</v>
+      </c>
       <c r="I70" t="s">
         <v>40</v>
       </c>
       <c r="J70" s="2">
-        <v>46331.708333333336</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K70" s="2">
-        <v>46332.166666666664</v>
+        <v>46332.75</v>
       </c>
       <c r="L70" t="s">
         <v>19</v>
@@ -3532,72 +3532,69 @@
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B71" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="C71" t="s">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="D71" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="F71" t="s">
-        <v>67</v>
-      </c>
-      <c r="G71" t="s">
-        <v>17</v>
-      </c>
-      <c r="H71" t="s">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="I71" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J71" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K71" s="2">
-        <v>46332.75</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L71" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C72" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="D72" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F72" t="s">
-        <v>82</v>
+        <v>61</v>
+      </c>
+      <c r="G72" t="s">
+        <v>17</v>
       </c>
       <c r="I72" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J72" s="2">
-        <v>46332.056250000001</v>
+        <v>46332.25</v>
       </c>
       <c r="K72" s="2">
-        <v>46332.597916666666</v>
+        <v>46332.75</v>
       </c>
       <c r="L72" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -3605,77 +3602,68 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C73" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="D73" t="s">
-        <v>177</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>178</v>
+        <v>114</v>
       </c>
       <c r="F73" t="s">
-        <v>67</v>
-      </c>
-      <c r="G73" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="I73" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J73" s="2">
-        <v>46332.25</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K73" s="2">
-        <v>46332.75</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="L73" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B74" t="s">
-        <v>56</v>
-      </c>
-      <c r="C74" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="D74" t="s">
-        <v>116</v>
+        <v>179</v>
       </c>
       <c r="F74" t="s">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="I74" t="s">
         <v>18</v>
       </c>
       <c r="J74" s="2">
-        <v>46332.291666666664</v>
+        <v>46332.375</v>
       </c>
       <c r="K74" s="2">
-        <v>46332.791666666664</v>
+        <v>46333.5</v>
       </c>
       <c r="L74" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B75" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D75" t="s">
         <v>179</v>
       </c>
       <c r="F75" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I75" t="s">
         <v>18</v>
@@ -3687,33 +3675,36 @@
         <v>46333.5</v>
       </c>
       <c r="L75" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>60</v>
+        <v>68</v>
+      </c>
+      <c r="C76" t="s">
+        <v>69</v>
       </c>
       <c r="D76" t="s">
-        <v>179</v>
+        <v>70</v>
       </c>
       <c r="F76" t="s">
-        <v>121</v>
+        <v>71</v>
       </c>
       <c r="I76" t="s">
         <v>18</v>
       </c>
       <c r="J76" s="2">
-        <v>46332.375</v>
+        <v>46332.541666666664</v>
       </c>
       <c r="K76" s="2">
-        <v>46333.5</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="L76" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -3721,25 +3712,31 @@
         <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="C77" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="D77" t="s">
-        <v>75</v>
+        <v>177</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>178</v>
       </c>
       <c r="F77" t="s">
-        <v>44</v>
+        <v>61</v>
+      </c>
+      <c r="G77" t="s">
+        <v>17</v>
       </c>
       <c r="I77" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J77" s="2">
-        <v>46332.541666666664</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="K77" s="2">
-        <v>46333.041666666664</v>
+        <v>46333.75</v>
       </c>
       <c r="L77" t="s">
         <v>19</v>
@@ -3747,101 +3744,95 @@
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B78" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="C78" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="D78" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F78" t="s">
-        <v>67</v>
-      </c>
-      <c r="G78" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="I78" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J78" s="2">
-        <v>46332.791666666664</v>
+        <v>46332.875</v>
       </c>
       <c r="K78" s="2">
-        <v>46333.75</v>
+        <v>46334.25</v>
       </c>
       <c r="L78" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B79" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C79" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="D79" t="s">
-        <v>180</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
+      </c>
+      <c r="E79" s="1">
+        <v>102</v>
       </c>
       <c r="F79" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="I79" t="s">
         <v>18</v>
       </c>
       <c r="J79" s="2">
-        <v>46332.875</v>
+        <v>46333</v>
       </c>
       <c r="K79" s="2">
-        <v>46334.25</v>
+        <v>46334</v>
       </c>
       <c r="L79" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>60</v>
-      </c>
-      <c r="C80" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="D80" t="s">
-        <v>182</v>
-      </c>
-      <c r="E80" s="1">
-        <v>102</v>
+        <v>183</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>184</v>
       </c>
       <c r="F80" t="s">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="I80" t="s">
         <v>18</v>
       </c>
       <c r="J80" s="2">
-        <v>46333</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="K80" s="2">
-        <v>46334</v>
+        <v>46335.041666666664</v>
       </c>
       <c r="L80" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -3849,28 +3840,34 @@
         <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>48</v>
+        <v>37</v>
+      </c>
+      <c r="C81" t="s">
+        <v>14</v>
       </c>
       <c r="D81" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F81" t="s">
-        <v>51</v>
+        <v>187</v>
+      </c>
+      <c r="G81" t="s">
+        <v>17</v>
       </c>
       <c r="I81" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J81" s="2">
-        <v>46333.041666666664</v>
+        <v>46333.25</v>
       </c>
       <c r="K81" s="2">
-        <v>46335.041666666664</v>
+        <v>46333.75</v>
       </c>
       <c r="L81" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -3878,95 +3875,95 @@
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C82" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="D82" t="s">
-        <v>185</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>186</v>
+        <v>64</v>
       </c>
       <c r="F82" t="s">
-        <v>187</v>
-      </c>
-      <c r="G82" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="I82" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J82" s="2">
-        <v>46333.25</v>
+        <v>46333.416666666664</v>
       </c>
       <c r="K82" s="2">
         <v>46333.75</v>
       </c>
       <c r="L82" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B83" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C83" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="D83" t="s">
-        <v>70</v>
+        <v>188</v>
+      </c>
+      <c r="E83" s="1">
+        <v>94</v>
       </c>
       <c r="F83" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="I83" t="s">
         <v>18</v>
       </c>
       <c r="J83" s="2">
-        <v>46333.416666666664</v>
+        <v>46333.666666666664</v>
       </c>
       <c r="K83" s="2">
-        <v>46333.75</v>
+        <v>46335.041666666664</v>
       </c>
       <c r="L83" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C84" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="D84" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E84" s="1">
-        <v>94</v>
+        <v>11</v>
       </c>
       <c r="F84" t="s">
-        <v>94</v>
+        <v>39</v>
+      </c>
+      <c r="G84" t="s">
+        <v>17</v>
       </c>
       <c r="I84" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J84" s="2">
-        <v>46333.666666666664</v>
+        <v>46334.25</v>
       </c>
       <c r="K84" s="2">
-        <v>46335.041666666664</v>
+        <v>46334.75</v>
       </c>
       <c r="L84" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -3980,10 +3977,10 @@
         <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F85" t="s">
         <v>16</v>
@@ -4009,19 +4006,19 @@
         <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="C86" t="s">
         <v>14</v>
       </c>
       <c r="D86" t="s">
+        <v>190</v>
+      </c>
+      <c r="E86" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="E86" s="1">
-        <v>11</v>
-      </c>
       <c r="F86" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="G86" t="s">
         <v>17</v>
@@ -4030,10 +4027,10 @@
         <v>40</v>
       </c>
       <c r="J86" s="2">
-        <v>46334.25</v>
+        <v>46334.791666666664</v>
       </c>
       <c r="K86" s="2">
-        <v>46334.75</v>
+        <v>46335.75</v>
       </c>
       <c r="L86" t="s">
         <v>19</v>
@@ -4044,34 +4041,31 @@
         <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c r="C87" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="D87" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F87" t="s">
         <v>16</v>
       </c>
-      <c r="G87" t="s">
-        <v>17</v>
-      </c>
       <c r="I87" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J87" s="2">
-        <v>46334.791666666664</v>
+        <v>46334.958333333336</v>
       </c>
       <c r="K87" s="2">
-        <v>46335.75</v>
+        <v>46337.708333333336</v>
       </c>
       <c r="L87" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -4079,31 +4073,34 @@
         <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="C88" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>192</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
+      </c>
+      <c r="E88" s="1">
+        <v>1</v>
       </c>
       <c r="F88" t="s">
-        <v>16</v>
+        <v>39</v>
+      </c>
+      <c r="G88" t="s">
+        <v>17</v>
       </c>
       <c r="I88" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J88" s="2">
-        <v>46334.958333333336</v>
+        <v>46335.25</v>
       </c>
       <c r="K88" s="2">
-        <v>46337.708333333336</v>
+        <v>46335.75</v>
       </c>
       <c r="L88" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -4111,7 +4108,7 @@
         <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="C89" t="s">
         <v>14</v>
@@ -4132,10 +4129,10 @@
         <v>40</v>
       </c>
       <c r="J89" s="2">
-        <v>46335.25</v>
+        <v>46335.791666666664</v>
       </c>
       <c r="K89" s="2">
-        <v>46335.75</v>
+        <v>46336.75</v>
       </c>
       <c r="L89" t="s">
         <v>19</v>
@@ -4146,34 +4143,31 @@
         <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C90" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="D90" t="s">
-        <v>194</v>
-      </c>
-      <c r="E90" s="1">
-        <v>1</v>
+        <v>195</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="F90" t="s">
-        <v>39</v>
-      </c>
-      <c r="G90" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="I90" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J90" s="2">
-        <v>46335.791666666664</v>
+        <v>46337</v>
       </c>
       <c r="K90" s="2">
-        <v>46336.75</v>
+        <v>46339</v>
       </c>
       <c r="L90" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -4181,48 +4175,48 @@
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C91" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="D91" t="s">
-        <v>195</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>196</v>
+        <v>129</v>
       </c>
       <c r="F91" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I91" t="s">
         <v>18</v>
       </c>
       <c r="J91" s="2">
-        <v>46337</v>
+        <v>46337.333333333336</v>
       </c>
       <c r="K91" s="2">
-        <v>46339</v>
+        <v>46337.833333333336</v>
       </c>
       <c r="L91" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B92" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="C92" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="D92" t="s">
-        <v>129</v>
+        <v>197</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="F92" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="I92" t="s">
         <v>18</v>
@@ -4231,42 +4225,39 @@
         <v>46337.333333333336</v>
       </c>
       <c r="K92" s="2">
-        <v>46337.833333333336</v>
+        <v>46339.333333333336</v>
       </c>
       <c r="L92" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="C93" t="s">
-        <v>29</v>
+        <v>120</v>
       </c>
       <c r="D93" t="s">
-        <v>197</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>198</v>
+        <v>121</v>
       </c>
       <c r="F93" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="I93" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="J93" s="2">
-        <v>46337.333333333336</v>
+        <v>46337.625</v>
       </c>
       <c r="K93" s="2">
-        <v>46339.333333333336</v>
+        <v>46338.125</v>
       </c>
       <c r="L93" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -4274,284 +4265,281 @@
         <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="C94" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="D94" t="s">
-        <v>43</v>
+        <v>199</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="F94" t="s">
-        <v>44</v>
+        <v>16</v>
+      </c>
+      <c r="G94" t="s">
+        <v>17</v>
       </c>
       <c r="I94" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="J94" s="2">
-        <v>46337.625</v>
+        <v>46338.25</v>
       </c>
       <c r="K94" s="2">
-        <v>46338.125</v>
+        <v>46338.75</v>
       </c>
       <c r="L94" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B95" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="C95" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
       <c r="D95" t="s">
-        <v>199</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F95" t="s">
-        <v>16</v>
-      </c>
-      <c r="G95" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="I95" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J95" s="2">
-        <v>46338.25</v>
+        <v>46338.431250000001</v>
       </c>
       <c r="K95" s="2">
-        <v>46338.75</v>
+        <v>46339.472916666666</v>
       </c>
       <c r="L95" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B96" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="C96" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="D96" t="s">
-        <v>201</v>
+        <v>202</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="F96" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="I96" t="s">
         <v>18</v>
       </c>
       <c r="J96" s="2">
-        <v>46338.431250000001</v>
+        <v>46338.709027777775</v>
       </c>
       <c r="K96" s="2">
-        <v>46339.472916666666</v>
+        <v>46339.584027777775</v>
       </c>
       <c r="L96" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
+        <v>12</v>
+      </c>
+      <c r="B97" t="s">
         <v>27</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
         <v>28</v>
       </c>
-      <c r="C97" t="s">
-        <v>148</v>
-      </c>
       <c r="D97" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F97" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I97" t="s">
         <v>18</v>
       </c>
       <c r="J97" s="2">
-        <v>46338.709027777775</v>
+        <v>46338.958333333336</v>
       </c>
       <c r="K97" s="2">
-        <v>46339.584027777775</v>
+        <v>46342.208333333336</v>
       </c>
       <c r="L97" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B98" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C98" t="s">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="D98" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F98" t="s">
-        <v>24</v>
+        <v>142</v>
       </c>
       <c r="I98" t="s">
         <v>18</v>
       </c>
       <c r="J98" s="2">
-        <v>46338.958333333336</v>
+        <v>46339.083333333336</v>
       </c>
       <c r="K98" s="2">
-        <v>46342.208333333336</v>
+        <v>46340.291666666664</v>
       </c>
       <c r="L98" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B99" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C99" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="D99" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F99" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="I99" t="s">
         <v>18</v>
       </c>
       <c r="J99" s="2">
-        <v>46338.958333333336</v>
+        <v>46339.291666666664</v>
       </c>
       <c r="K99" s="2">
-        <v>46342.208333333336</v>
+        <v>46340.666666666664</v>
       </c>
       <c r="L99" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B100" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C100" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="D100" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F100" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="I100" t="s">
         <v>18</v>
       </c>
       <c r="J100" s="2">
-        <v>46339.083333333336</v>
+        <v>46339.291666666664</v>
       </c>
       <c r="K100" s="2">
-        <v>46340.291666666664</v>
+        <v>46340.666666666664</v>
       </c>
       <c r="L100" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B101" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C101" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D101" t="s">
-        <v>208</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="F101" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="I101" t="s">
         <v>18</v>
       </c>
       <c r="J101" s="2">
-        <v>46339.291666666664</v>
+        <v>46339.704861111109</v>
       </c>
       <c r="K101" s="2">
-        <v>46340.666666666664</v>
+        <v>46340.204861111109</v>
       </c>
       <c r="L101" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C102" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D102" t="s">
-        <v>208</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>209</v>
+        <v>70</v>
       </c>
       <c r="F102" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="I102" t="s">
         <v>18</v>
       </c>
       <c r="J102" s="2">
-        <v>46339.291666666664</v>
+        <v>46339.541666666664</v>
       </c>
       <c r="K102" s="2">
-        <v>46340.666666666664</v>
+        <v>46340.041666666664</v>
       </c>
       <c r="L102" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="103" spans="1:12">
@@ -4559,57 +4547,31 @@
         <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C103" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="D103" t="s">
-        <v>75</v>
+        <v>204</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>205</v>
       </c>
       <c r="F103" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="I103" t="s">
         <v>18</v>
       </c>
       <c r="J103" s="2">
-        <v>46339.541666666664</v>
+        <v>46338.958333333336</v>
       </c>
       <c r="K103" s="2">
-        <v>46340.041666666664</v>
+        <v>46342.208333333336</v>
       </c>
       <c r="L103" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12">
-      <c r="A104" t="s">
-        <v>12</v>
-      </c>
-      <c r="B104" t="s">
-        <v>56</v>
-      </c>
-      <c r="C104" t="s">
-        <v>76</v>
-      </c>
-      <c r="D104" t="s">
-        <v>77</v>
-      </c>
-      <c r="F104" t="s">
-        <v>58</v>
-      </c>
-      <c r="I104" t="s">
-        <v>18</v>
-      </c>
-      <c r="J104" s="2">
-        <v>46339.704861111109</v>
-      </c>
-      <c r="K104" s="2">
-        <v>46340.204861111109</v>
-      </c>
-      <c r="L104" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -4621,12 +4583,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
+  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
+</scriptIds>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -4764,35 +4743,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
-  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
-</scriptIds>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>